--- a/demo/DEMO_SCI_EXEMPLE_valeurs_fictives.xlsx
+++ b/demo/DEMO_SCI_EXEMPLE_valeurs_fictives.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Indices'!$A$1:$H$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Révisions'!$A$1:$Y$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Révisions'!$A$1:$AC$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +139,12 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment/>
     </xf>
@@ -146,12 +152,23 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="1"/>
         <color rgb="00C00000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001F4E79"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DDEBF7"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -554,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G31"/>
+  <dimension ref="B2:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -782,82 +799,103 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renseigner « Appliqué ? » et la date d'application une fois la révision facturée : ces colonnes sont conservées au rafraîchissement.</t>
+          <t xml:space="preserve">   Colonne « Décision » : vide ou Appliquer = révision appliquée ; Geler = le client renonce à la révision (loyer inchangé). « Geler – rattrapage possible » permet de récupérer la variation à la révision suivante ; « sans rattrapage » l'abandonne.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>4. Feuille « Alertes » : vue de pilotage par bail (loyer actuel, prochaine échéance, action).</t>
+          <t xml:space="preserve">   Colonne « Consigne (à faire) » : instruction libre du dossier (ex. « Gel décidé par le client le 12/03, courrier à envoyer, ne pas facturer »). Reprise dans la feuille Alertes.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>5. Feuille « Pennylane » : corps de requête prêt pour POST /billing_subscriptions (mode aperçu ; l'envoi se fait par la commande  pennylane &lt;société&gt;).</t>
+          <t xml:space="preserve">   Renseigner « Appliqué ? », la date d'application et la date d'envoi du courrier : toutes les colonnes jaunes sont conservées au rafraîchissement.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trimestres : notation AAAA-Tn (2024-T2 = 2e trimestre 2024), équivalente au 2024-Q2 de l'INSEE.</t>
+          <t xml:space="preserve">   Courriers aux locataires : commande  python -m indexation_loyer courriers &lt;société&gt;  -&gt; un PDF par échéance à notifier (application ou gel), modèle dans config/courrier_modele.json.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Convention par défaut du trimestre de base : dernier indice publié à la date de prise d'effet (T-2). À caler sur la clause du bail.</t>
+          <t>4. Feuille « Alertes » : vue de pilotage par bail (loyer actuel, prochaine échéance, action).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5. Feuille « Pennylane » : corps de requête prêt pour POST /billing_subscriptions (mode aperçu ; l'envoi se fait par la commande  pennylane &lt;société&gt;).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Points de vigilance juridiques (à confirmer par le juriste du dossier)</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Trimestres : notation AAAA-Tn (2024-T2 = 2e trimestre 2024), équivalente au 2024-Q2 de l'INSEE.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>• Depuis la loi Pinel (n° 2014-626 du 18 juin 2014), l'ILC et l'ILAT sont les indices de référence des baux commerciaux (art. L145-34 et L145-38 C. com.) ; l'ICC subsiste dans les clauses des baux antérieurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>• Plafonnement légal de la variation de l'ILC à 3,5 % pour les PME (loi n° 2022-1158 du 16 août 2022, art. 14, puis prolongation) : période et champ à vérifier bail par bail ; utiliser la colonne « Plafond annuel (%) ».</t>
+          <t>Convention par défaut du trimestre de base : dernier indice publié à la date de prise d'effet (T-2). À caler sur la clause du bail.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>• Une clause d'indexation ne jouant qu'à la hausse est réputée non écrite (art. L112-1 C. mon. fin. et jurisprudence Cass. 3e civ.) : le classeur applique la baisse si l'indice recule.</t>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Points de vigilance juridiques (à confirmer par le juriste du dossier)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>• Révision légale triennale (L145-38) et déplafonnement : hors périmètre de la version actuelle, qui traite la clause d'échelle mobile contractuelle.</t>
+          <t>• Depuis la loi Pinel (n° 2014-626 du 18 juin 2014), l'ILC et l'ILAT sont les indices de référence des baux commerciaux (art. L145-34 et L145-38 C. com.) ; l'ICC subsiste dans les clauses des baux antérieurs.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
+          <t>• Plafonnement légal de la variation de l'ILC à 3,5 % pour les PME (loi n° 2022-1158 du 16 août 2022, art. 14, puis prolongation) : période et champ à vérifier bail par bail ; utiliser la colonne « Plafond annuel (%) ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>• Une clause d'indexation ne jouant qu'à la hausse est réputée non écrite (art. L112-1 C. mon. fin. et jurisprudence Cass. 3e civ.) : le classeur applique la baisse si l'indice recule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>• Révision légale triennale (L145-38) et déplafonnement : hors périmètre de la version actuelle, qui traite la clause d'échelle mobile contractuelle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
           <t>• Le classeur ne remplace pas la lecture du bail : trimestre de base, périodicité et méthode (chaînée / base fixe) doivent être relevés sur l'acte.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="2" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Légende : fond jaune = saisie ; autres cellules = formules ; ne pas insérer de colonnes dans Baux, Indices, Révisions.</t>
         </is>
@@ -874,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -952,20 +990,69 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Date de génération</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>46274</v>
+          <t>Adresse du bailleur (courriers)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>1 place de la Bourse
+75002 Paris</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Signataire des courriers</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Mme Claire Exemple</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Qualité du signataire</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Gérante</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Ville de signature</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Date de génération</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>Mode démonstration</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
@@ -982,29 +1069,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -1025,85 +1113,90 @@
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
+          <t>Adresse du locataire (courrier)</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
           <t>Type de bail</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Date de prise d'effet</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Durée (ans)</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Date de fin</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Loyer initial annuel HT</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Charges annuelles HT</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>TVA (%)</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Périodicité de facturation</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Indice</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Trimestre indice de base</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Périodicité de révision (ans)</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Méthode</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Plafond annuel (%) – optionnel</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>Pennylane customer_id</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>Pennylane product_id</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="U1" s="10" t="inlineStr">
         <is>
           <t>Contrôles</t>
         </is>
@@ -1127,65 +1220,71 @@
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
+          <t>12 rue de la Paix
+75002 Paris</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="F2" s="12" t="n">
         <v>44287</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="G2" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G2" s="13">
-        <f>IF(OR(E2="",F2=""),"",EDATE(E2,12*F2))</f>
-        <v/>
-      </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="13">
+        <f>IF(OR(F2="",G2=""),"",EDATE(F2,12*G2))</f>
+        <v/>
+      </c>
+      <c r="I2" s="14" t="n">
         <v>24000</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="J2" s="14" t="n">
         <v>2400</v>
       </c>
-      <c r="J2" s="11" t="n">
+      <c r="K2" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>Mensuelle</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>ILC</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="N2" s="11" t="inlineStr">
         <is>
           <t>2020-T4</t>
         </is>
       </c>
-      <c r="N2" s="11" t="n">
+      <c r="O2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="P2" s="11" t="inlineStr">
         <is>
           <t>Chaînée</t>
         </is>
       </c>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="11" t="n"/>
+      <c r="R2" s="11" t="inlineStr">
         <is>
           <t>100001</t>
         </is>
       </c>
-      <c r="R2" s="11" t="n"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="11" t="inlineStr">
         <is>
           <t>Clause d'échelle mobile annuelle, ILC même trimestre</t>
         </is>
       </c>
-      <c r="T2" s="15">
-        <f>IF(A2="","",TRIM(IF(E2="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(H2)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,L2)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,L2,Indices!$B:$B,M2)=0,"Indice de base "&amp;M2&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(M2)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A2)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(P2&lt;&gt;"",NOT(ISNUMBER(P2))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A2)=1,"",""))&amp;IF(AND(E2&lt;&gt;"",ISNUMBER(H2),SUMIFS(Indices!$C:$C,Indices!$A:$A,L2,Indices!$B:$B,M2)&gt;0,LEN(M2)=7,COUNTIF($A$2:$A$200,A2)=1),"OK",""))</f>
+      <c r="U2" s="15">
+        <f>IF(A2="","",TRIM(IF(F2="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(I2)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,M2)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,M2,Indices!$B:$B,N2)=0,"Indice de base "&amp;N2&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(N2)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A2)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(Q2&lt;&gt;"",NOT(ISNUMBER(Q2))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A2)=1,"",""))&amp;IF(AND(F2&lt;&gt;"",ISNUMBER(I2),SUMIFS(Indices!$C:$C,Indices!$A:$A,M2,Indices!$B:$B,N2)&gt;0,LEN(N2)=7,COUNTIF($A$2:$A$200,A2)=1),"OK",""))</f>
         <v/>
       </c>
     </row>
@@ -1205,67 +1304,68 @@
           <t>Cabinet Martin (SELARL)</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="F3" s="12" t="n">
         <v>44835</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="G3" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="13">
-        <f>IF(OR(E3="",F3=""),"",EDATE(E3,12*F3))</f>
-        <v/>
-      </c>
-      <c r="H3" s="14" t="n">
+      <c r="H3" s="13">
+        <f>IF(OR(F3="",G3=""),"",EDATE(F3,12*G3))</f>
+        <v/>
+      </c>
+      <c r="I3" s="14" t="n">
         <v>36000</v>
       </c>
-      <c r="I3" s="14" t="n">
+      <c r="J3" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="K3" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>Trimestrielle</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>ILAT</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>2022-T2</t>
         </is>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="O3" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="P3" s="11" t="inlineStr">
         <is>
           <t>Base fixe</t>
         </is>
       </c>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="11" t="inlineStr">
         <is>
           <t>100002</t>
         </is>
       </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="S3" s="11" t="n"/>
+      <c r="T3" s="11" t="inlineStr">
         <is>
           <t>Révision triennale indexée ILAT, indice de base fixe</t>
         </is>
       </c>
-      <c r="T3" s="15">
-        <f>IF(A3="","",TRIM(IF(E3="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(H3)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,L3)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,L3,Indices!$B:$B,M3)=0,"Indice de base "&amp;M3&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(M3)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A3)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(P3&lt;&gt;"",NOT(ISNUMBER(P3))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A3)=1,"",""))&amp;IF(AND(E3&lt;&gt;"",ISNUMBER(H3),SUMIFS(Indices!$C:$C,Indices!$A:$A,L3,Indices!$B:$B,M3)&gt;0,LEN(M3)=7,COUNTIF($A$2:$A$200,A3)=1),"OK",""))</f>
+      <c r="U3" s="15">
+        <f>IF(A3="","",TRIM(IF(F3="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(I3)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,M3)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,M3,Indices!$B:$B,N3)=0,"Indice de base "&amp;N3&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(N3)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A3)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(Q3&lt;&gt;"",NOT(ISNUMBER(Q3))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A3)=1,"",""))&amp;IF(AND(F3&lt;&gt;"",ISNUMBER(I3),SUMIFS(Indices!$C:$C,Indices!$A:$A,M3,Indices!$B:$B,N3)&gt;0,LEN(N3)=7,COUNTIF($A$2:$A$200,A3)=1),"OK",""))</f>
         <v/>
       </c>
     </row>
@@ -1285,65 +1385,66 @@
           <t>Logistix SARL</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="F4" s="12" t="n">
         <v>43480</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="G4" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="13">
-        <f>IF(OR(E4="",F4=""),"",EDATE(E4,12*F4))</f>
-        <v/>
-      </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="13">
+        <f>IF(OR(F4="",G4=""),"",EDATE(F4,12*G4))</f>
+        <v/>
+      </c>
+      <c r="I4" s="14" t="n">
         <v>60000</v>
       </c>
-      <c r="I4" s="14" t="n">
+      <c r="J4" s="14" t="n">
         <v>6000</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="K4" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>Trimestrielle</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>ICC</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>2018-T3</t>
         </is>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="O4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>Chaînée</t>
         </is>
       </c>
-      <c r="P4" s="11" t="n">
+      <c r="Q4" s="11" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q4" s="11" t="n"/>
       <c r="R4" s="11" t="n"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="S4" s="11" t="n"/>
+      <c r="T4" s="11" t="inlineStr">
         <is>
           <t>Bail antérieur à 2014 renouvelé, clause ICC ; plafond contractuel 3,5 %</t>
         </is>
       </c>
-      <c r="T4" s="15">
-        <f>IF(A4="","",TRIM(IF(E4="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(H4)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,L4)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,L4,Indices!$B:$B,M4)=0,"Indice de base "&amp;M4&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(M4)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A4)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(P4&lt;&gt;"",NOT(ISNUMBER(P4))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A4)=1,"",""))&amp;IF(AND(E4&lt;&gt;"",ISNUMBER(H4),SUMIFS(Indices!$C:$C,Indices!$A:$A,L4,Indices!$B:$B,M4)&gt;0,LEN(M4)=7,COUNTIF($A$2:$A$200,A4)=1),"OK",""))</f>
+      <c r="U4" s="15">
+        <f>IF(A4="","",TRIM(IF(F4="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(I4)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,M4)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,M4,Indices!$B:$B,N4)=0,"Indice de base "&amp;N4&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(N4)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A4)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(Q4&lt;&gt;"",NOT(ISNUMBER(Q4))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A4)=1,"",""))&amp;IF(AND(F4&lt;&gt;"",ISNUMBER(I4),SUMIFS(Indices!$C:$C,Indices!$A:$A,M4,Indices!$B:$B,N4)&gt;0,LEN(N4)=7,COUNTIF($A$2:$A$200,A4)=1),"OK",""))</f>
         <v/>
       </c>
     </row>
@@ -1363,89 +1464,90 @@
           <t>Nouveau preneur (à compléter)</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="F5" s="12" t="n">
         <v>45839</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="G5" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="13">
-        <f>IF(OR(E5="",F5=""),"",EDATE(E5,12*F5))</f>
-        <v/>
-      </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="13">
+        <f>IF(OR(F5="",G5=""),"",EDATE(F5,12*G5))</f>
+        <v/>
+      </c>
+      <c r="I5" s="14" t="n">
         <v>18000</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="J5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="K5" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>Mensuelle</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>ILC</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>2025-T1</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="O5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Chaînée</t>
         </is>
       </c>
-      <c r="P5" s="11" t="n"/>
       <c r="Q5" s="11" t="n"/>
       <c r="R5" s="11" t="n"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="S5" s="11" t="n"/>
+      <c r="T5" s="11" t="inlineStr">
         <is>
           <t>customer_id Pennylane à créer</t>
         </is>
       </c>
-      <c r="T5" s="15">
-        <f>IF(A5="","",TRIM(IF(E5="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(H5)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,L5)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,L5,Indices!$B:$B,M5)=0,"Indice de base "&amp;M5&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(M5)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A5)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(P5&lt;&gt;"",NOT(ISNUMBER(P5))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A5)=1,"",""))&amp;IF(AND(E5&lt;&gt;"",ISNUMBER(H5),SUMIFS(Indices!$C:$C,Indices!$A:$A,L5,Indices!$B:$B,M5)&gt;0,LEN(M5)=7,COUNTIF($A$2:$A$200,A5)=1),"OK",""))</f>
+      <c r="U5" s="15">
+        <f>IF(A5="","",TRIM(IF(F5="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(I5)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,M5)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,M5,Indices!$B:$B,N5)=0,"Indice de base "&amp;N5&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(N5)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A5)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(Q5&lt;&gt;"",NOT(ISNUMBER(Q5))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A5)=1,"",""))&amp;IF(AND(F5&lt;&gt;"",ISNUMBER(I5),SUMIFS(Indices!$C:$C,Indices!$A:$A,M5,Indices!$B:$B,N5)&gt;0,LEN(N5)=7,COUNTIF($A$2:$A$200,A5)=1),"OK",""))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="T2:T200">
+  <conditionalFormatting sqref="U2:U200">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(T2&lt;&gt;"",T2&lt;&gt;"OK")</formula>
+      <formula>AND(U2&lt;&gt;"",U2&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Commercial,Professionnel,Habitation,Dérogatoire,Autre"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Mensuelle,Trimestrielle,Semestrielle,Annuelle"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ILC,ILAT,ICC,IRL"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chaînée,Base fixe"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(1990,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -6674,7 +6776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6687,21 +6789,25 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
-    <col hidden="1" width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="12" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="6" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -6757,77 +6863,97 @@
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
+          <t>Décision</t>
+        </is>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
           <t>Base de calcul (annuel HT)</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Loyer révisé brut</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Loyer retenu (annuel HT)</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Loyer précédent (annuel HT)</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Variation</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Loyer mensuel HT</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>Loyer / échéance HT</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>Charges / échéance HT</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>TVA / échéance</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="U1" s="10" t="inlineStr">
         <is>
           <t>Total TTC / échéance</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="V1" s="10" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="W1" s="10" t="inlineStr">
+        <is>
+          <t>Consigne (à faire)</t>
+        </is>
+      </c>
+      <c r="X1" s="10" t="inlineStr">
         <is>
           <t>Appliqué ? (Oui/Non)</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="Y1" s="10" t="inlineStr">
         <is>
           <t>Date d'application</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="Z1" s="10" t="inlineStr">
+        <is>
+          <t>Courrier envoyé le</t>
+        </is>
+      </c>
+      <c r="AA1" s="10" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="AB1" s="10" t="inlineStr">
         <is>
           <t>Clé</t>
+        </is>
+      </c>
+      <c r="AC1" s="10" t="inlineStr">
+        <is>
+          <t>Effectif</t>
         </is>
       </c>
     </row>
@@ -6845,15 +6971,15 @@
         <v>1</v>
       </c>
       <c r="D2" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A2,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A2,Baux!$A:$A,0))*C2)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A2,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A2,Baux!$A:$A,0))*C2)</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F2" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A2,Baux!$A:$A,0)),4))+C2*INDEX(Baux!$N:$N,MATCH($A2,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A2,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A2,Baux!$A:$A,0)),4))+C2*INDEX(Baux!$O:$O,MATCH($A2,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A2,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G2" s="18">
@@ -6861,7 +6987,7 @@
         <v/>
       </c>
       <c r="H2" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A2,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A2,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A2,Baux!$A:$A,0)),4))+(C2-1)*INDEX(Baux!$N:$N,MATCH($A2,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A2,Baux!$A:$A,0)),3))</f>
+        <f>INDEX(Baux!$N:$N,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="I2" s="18">
@@ -6872,55 +6998,66 @@
         <f>IF(OR(G2="",I2=""),"",G2/I2)</f>
         <v/>
       </c>
-      <c r="K2" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A2,Baux!$A:$A,0))</f>
-        <v/>
-      </c>
+      <c r="K2" s="11" t="n"/>
       <c r="L2" s="20">
-        <f>IF(OR(J2="",K2=""),"",ROUND(K2*J2,2))</f>
+        <f>INDEX(Baux!$I:$I,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="M2" s="20">
-        <f>IF(L2="","",IF(INDEX(Baux!$P:$P,MATCH($A2,Baux!$A:$A,0))="",L2,MIN(L2,ROUND(K2*(1+INDEX(Baux!$P:$P,MATCH($A2,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A2,Baux!$A:$A,0))="Base fixe",C2*INDEX(Baux!$N:$N,MATCH($A2,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A2,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J2="",L2=""),"",ROUND(L2*J2,2))</f>
         <v/>
       </c>
       <c r="N2" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A2,Baux!$A:$A,0))</f>
-        <v/>
-      </c>
-      <c r="O2" s="21">
-        <f>IF(OR(M2="",N2=""),"",M2/N2-1)</f>
-        <v/>
-      </c>
-      <c r="P2" s="20">
-        <f>IF(M2="","",M2/12)</f>
+        <f>IF(LEFT(K2,5)="Geler",O2,IF(M2="","",IF(INDEX(Baux!$Q:$Q,MATCH($A2,Baux!$A:$A,0))="",M2,MIN(M2,ROUND(L2*(1+INDEX(Baux!$Q:$Q,MATCH($A2,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A2,Baux!$A:$A,0))="Base fixe",C2*INDEX(Baux!$O:$O,MATCH($A2,Baux!$A:$A,0)),VALUE(LEFT(F2,4))-VALUE(LEFT(H2,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O2" s="20">
+        <f>INDEX(Baux!$I:$I,MATCH($A2,Baux!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="P2" s="21">
+        <f>IF(OR(N2="",O2=""),"",N2/O2-1)</f>
         <v/>
       </c>
       <c r="Q2" s="20">
-        <f>IF(M2="","",M2/IF(INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N2="","",N2/12)</f>
         <v/>
       </c>
       <c r="R2" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A2,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A2,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N2="","",N2/IF(INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S2" s="20">
-        <f>IF(Q2="","",(Q2+R2)*INDEX(Baux!$J:$J,MATCH($A2,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A2,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A2,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T2" s="20">
-        <f>IF(Q2="","",Q2+R2+S2)</f>
-        <v/>
-      </c>
-      <c r="U2" s="15">
-        <f>IF(G2="",IF(D2&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D2&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V2" s="11" t="n"/>
-      <c r="W2" s="12" t="n"/>
-      <c r="X2" s="11" t="n"/>
-      <c r="Y2" s="15">
+        <f>IF(R2="","",(R2+S2)*INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U2" s="20">
+        <f>IF(R2="","",R2+S2+T2)</f>
+        <v/>
+      </c>
+      <c r="V2" s="15">
+        <f>IF(LEFT(K2,5)="Geler","❄ Gelée",IF(G2="",IF(D2&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D2&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W2" s="22" t="n"/>
+      <c r="X2" s="11" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Y2" s="12" t="n"/>
+      <c r="Z2" s="12" t="n"/>
+      <c r="AA2" s="11" t="n"/>
+      <c r="AB2" s="15">
         <f>A2&amp;"#"&amp;C2</f>
+        <v/>
+      </c>
+      <c r="AC2" s="15">
+        <f>IF(AND(D2&lt;=TODAY(),N2&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -6938,15 +7075,15 @@
         <v>2</v>
       </c>
       <c r="D3" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A3,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A3,Baux!$A:$A,0))*C3)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A3,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A3,Baux!$A:$A,0))*C3)</f>
         <v/>
       </c>
       <c r="E3" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A3,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F3" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A3,Baux!$A:$A,0)),4))+C3*INDEX(Baux!$N:$N,MATCH($A3,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A3,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A3,Baux!$A:$A,0)),4))+C3*INDEX(Baux!$O:$O,MATCH($A3,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A3,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G3" s="18">
@@ -6954,7 +7091,7 @@
         <v/>
       </c>
       <c r="H3" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A3,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A3,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A3,Baux!$A:$A,0)),4))+(C3-1)*INDEX(Baux!$N:$N,MATCH($A3,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A3,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A3,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A3,Baux!$A:$A,0)),IF(K2="Geler – rattrapage possible",H2,F2))</f>
         <v/>
       </c>
       <c r="I3" s="18">
@@ -6965,55 +7102,66 @@
         <f>IF(OR(G3="",I3=""),"",G3/I3)</f>
         <v/>
       </c>
-      <c r="K3" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A3,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A3,Baux!$A:$A,0)),M2)</f>
-        <v/>
-      </c>
+      <c r="K3" s="11" t="n"/>
       <c r="L3" s="20">
-        <f>IF(OR(J3="",K3=""),"",ROUND(K3*J3,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A3,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A3,Baux!$A:$A,0)),N2)</f>
         <v/>
       </c>
       <c r="M3" s="20">
-        <f>IF(L3="","",IF(INDEX(Baux!$P:$P,MATCH($A3,Baux!$A:$A,0))="",L3,MIN(L3,ROUND(K3*(1+INDEX(Baux!$P:$P,MATCH($A3,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A3,Baux!$A:$A,0))="Base fixe",C3*INDEX(Baux!$N:$N,MATCH($A3,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A3,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J3="",L3=""),"",ROUND(L3*J3,2))</f>
         <v/>
       </c>
       <c r="N3" s="20">
-        <f>M2</f>
-        <v/>
-      </c>
-      <c r="O3" s="21">
-        <f>IF(OR(M3="",N3=""),"",M3/N3-1)</f>
-        <v/>
-      </c>
-      <c r="P3" s="20">
-        <f>IF(M3="","",M3/12)</f>
+        <f>IF(LEFT(K3,5)="Geler",O3,IF(M3="","",IF(INDEX(Baux!$Q:$Q,MATCH($A3,Baux!$A:$A,0))="",M3,MIN(M3,ROUND(L3*(1+INDEX(Baux!$Q:$Q,MATCH($A3,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A3,Baux!$A:$A,0))="Base fixe",C3*INDEX(Baux!$O:$O,MATCH($A3,Baux!$A:$A,0)),VALUE(LEFT(F3,4))-VALUE(LEFT(H3,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O3" s="20">
+        <f>N2</f>
+        <v/>
+      </c>
+      <c r="P3" s="21">
+        <f>IF(OR(N3="",O3=""),"",N3/O3-1)</f>
         <v/>
       </c>
       <c r="Q3" s="20">
-        <f>IF(M3="","",M3/IF(INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N3="","",N3/12)</f>
         <v/>
       </c>
       <c r="R3" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A3,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A3,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N3="","",N3/IF(INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S3" s="20">
-        <f>IF(Q3="","",(Q3+R3)*INDEX(Baux!$J:$J,MATCH($A3,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A3,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A3,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T3" s="20">
-        <f>IF(Q3="","",Q3+R3+S3)</f>
-        <v/>
-      </c>
-      <c r="U3" s="15">
-        <f>IF(G3="",IF(D3&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D3&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V3" s="11" t="n"/>
-      <c r="W3" s="12" t="n"/>
-      <c r="X3" s="11" t="n"/>
-      <c r="Y3" s="15">
+        <f>IF(R3="","",(R3+S3)*INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U3" s="20">
+        <f>IF(R3="","",R3+S3+T3)</f>
+        <v/>
+      </c>
+      <c r="V3" s="15">
+        <f>IF(LEFT(K3,5)="Geler","❄ Gelée",IF(G3="",IF(D3&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D3&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W3" s="22" t="n"/>
+      <c r="X3" s="11" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Y3" s="12" t="n"/>
+      <c r="Z3" s="12" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="15">
         <f>A3&amp;"#"&amp;C3</f>
+        <v/>
+      </c>
+      <c r="AC3" s="15">
+        <f>IF(AND(D3&lt;=TODAY(),N3&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7031,15 +7179,15 @@
         <v>3</v>
       </c>
       <c r="D4" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A4,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A4,Baux!$A:$A,0))*C4)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A4,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A4,Baux!$A:$A,0))*C4)</f>
         <v/>
       </c>
       <c r="E4" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A4,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F4" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A4,Baux!$A:$A,0)),4))+C4*INDEX(Baux!$N:$N,MATCH($A4,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A4,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A4,Baux!$A:$A,0)),4))+C4*INDEX(Baux!$O:$O,MATCH($A4,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A4,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G4" s="18">
@@ -7047,7 +7195,7 @@
         <v/>
       </c>
       <c r="H4" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A4,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A4,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A4,Baux!$A:$A,0)),4))+(C4-1)*INDEX(Baux!$N:$N,MATCH($A4,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A4,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A4,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A4,Baux!$A:$A,0)),IF(K3="Geler – rattrapage possible",H3,F3))</f>
         <v/>
       </c>
       <c r="I4" s="18">
@@ -7058,55 +7206,68 @@
         <f>IF(OR(G4="",I4=""),"",G4/I4)</f>
         <v/>
       </c>
-      <c r="K4" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A4,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A4,Baux!$A:$A,0)),M3)</f>
-        <v/>
-      </c>
+      <c r="K4" s="11" t="n"/>
       <c r="L4" s="20">
-        <f>IF(OR(J4="",K4=""),"",ROUND(K4*J4,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A4,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A4,Baux!$A:$A,0)),N3)</f>
         <v/>
       </c>
       <c r="M4" s="20">
-        <f>IF(L4="","",IF(INDEX(Baux!$P:$P,MATCH($A4,Baux!$A:$A,0))="",L4,MIN(L4,ROUND(K4*(1+INDEX(Baux!$P:$P,MATCH($A4,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A4,Baux!$A:$A,0))="Base fixe",C4*INDEX(Baux!$N:$N,MATCH($A4,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A4,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J4="",L4=""),"",ROUND(L4*J4,2))</f>
         <v/>
       </c>
       <c r="N4" s="20">
-        <f>M3</f>
-        <v/>
-      </c>
-      <c r="O4" s="21">
-        <f>IF(OR(M4="",N4=""),"",M4/N4-1)</f>
-        <v/>
-      </c>
-      <c r="P4" s="20">
-        <f>IF(M4="","",M4/12)</f>
+        <f>IF(LEFT(K4,5)="Geler",O4,IF(M4="","",IF(INDEX(Baux!$Q:$Q,MATCH($A4,Baux!$A:$A,0))="",M4,MIN(M4,ROUND(L4*(1+INDEX(Baux!$Q:$Q,MATCH($A4,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A4,Baux!$A:$A,0))="Base fixe",C4*INDEX(Baux!$O:$O,MATCH($A4,Baux!$A:$A,0)),VALUE(LEFT(F4,4))-VALUE(LEFT(H4,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O4" s="20">
+        <f>N3</f>
+        <v/>
+      </c>
+      <c r="P4" s="21">
+        <f>IF(OR(N4="",O4=""),"",N4/O4-1)</f>
         <v/>
       </c>
       <c r="Q4" s="20">
-        <f>IF(M4="","",M4/IF(INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N4="","",N4/12)</f>
         <v/>
       </c>
       <c r="R4" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A4,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A4,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N4="","",N4/IF(INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S4" s="20">
-        <f>IF(Q4="","",(Q4+R4)*INDEX(Baux!$J:$J,MATCH($A4,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A4,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A4,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T4" s="20">
-        <f>IF(Q4="","",Q4+R4+S4)</f>
-        <v/>
-      </c>
-      <c r="U4" s="15">
-        <f>IF(G4="",IF(D4&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D4&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V4" s="11" t="n"/>
-      <c r="W4" s="12" t="n"/>
-      <c r="X4" s="11" t="n"/>
-      <c r="Y4" s="15">
+        <f>IF(R4="","",(R4+S4)*INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U4" s="20">
+        <f>IF(R4="","",R4+S4+T4)</f>
+        <v/>
+      </c>
+      <c r="V4" s="15">
+        <f>IF(LEFT(K4,5)="Geler","❄ Gelée",IF(G4="",IF(D4&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D4&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W4" s="22" t="n"/>
+      <c r="X4" s="11" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Y4" s="12" t="n">
+        <v>45383</v>
+      </c>
+      <c r="Z4" s="12" t="n"/>
+      <c r="AA4" s="11" t="n"/>
+      <c r="AB4" s="15">
         <f>A4&amp;"#"&amp;C4</f>
+        <v/>
+      </c>
+      <c r="AC4" s="15">
+        <f>IF(AND(D4&lt;=TODAY(),N4&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7124,15 +7285,15 @@
         <v>4</v>
       </c>
       <c r="D5" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A5,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A5,Baux!$A:$A,0))*C5)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A5,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A5,Baux!$A:$A,0))*C5)</f>
         <v/>
       </c>
       <c r="E5" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A5,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F5" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A5,Baux!$A:$A,0)),4))+C5*INDEX(Baux!$N:$N,MATCH($A5,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A5,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A5,Baux!$A:$A,0)),4))+C5*INDEX(Baux!$O:$O,MATCH($A5,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A5,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G5" s="18">
@@ -7140,7 +7301,7 @@
         <v/>
       </c>
       <c r="H5" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A5,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A5,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A5,Baux!$A:$A,0)),4))+(C5-1)*INDEX(Baux!$N:$N,MATCH($A5,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A5,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A5,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A5,Baux!$A:$A,0)),IF(K4="Geler – rattrapage possible",H4,F4))</f>
         <v/>
       </c>
       <c r="I5" s="18">
@@ -7151,55 +7312,72 @@
         <f>IF(OR(G5="",I5=""),"",G5/I5)</f>
         <v/>
       </c>
-      <c r="K5" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A5,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A5,Baux!$A:$A,0)),M4)</f>
-        <v/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>Geler – sans rattrapage</t>
+        </is>
       </c>
       <c r="L5" s="20">
-        <f>IF(OR(J5="",K5=""),"",ROUND(K5*J5,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A5,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A5,Baux!$A:$A,0)),N4)</f>
         <v/>
       </c>
       <c r="M5" s="20">
-        <f>IF(L5="","",IF(INDEX(Baux!$P:$P,MATCH($A5,Baux!$A:$A,0))="",L5,MIN(L5,ROUND(K5*(1+INDEX(Baux!$P:$P,MATCH($A5,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A5,Baux!$A:$A,0))="Base fixe",C5*INDEX(Baux!$N:$N,MATCH($A5,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A5,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J5="",L5=""),"",ROUND(L5*J5,2))</f>
         <v/>
       </c>
       <c r="N5" s="20">
-        <f>M4</f>
-        <v/>
-      </c>
-      <c r="O5" s="21">
-        <f>IF(OR(M5="",N5=""),"",M5/N5-1)</f>
-        <v/>
-      </c>
-      <c r="P5" s="20">
-        <f>IF(M5="","",M5/12)</f>
+        <f>IF(LEFT(K5,5)="Geler",O5,IF(M5="","",IF(INDEX(Baux!$Q:$Q,MATCH($A5,Baux!$A:$A,0))="",M5,MIN(M5,ROUND(L5*(1+INDEX(Baux!$Q:$Q,MATCH($A5,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A5,Baux!$A:$A,0))="Base fixe",C5*INDEX(Baux!$O:$O,MATCH($A5,Baux!$A:$A,0)),VALUE(LEFT(F5,4))-VALUE(LEFT(H5,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O5" s="20">
+        <f>N4</f>
+        <v/>
+      </c>
+      <c r="P5" s="21">
+        <f>IF(OR(N5="",O5=""),"",N5/O5-1)</f>
         <v/>
       </c>
       <c r="Q5" s="20">
-        <f>IF(M5="","",M5/IF(INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N5="","",N5/12)</f>
         <v/>
       </c>
       <c r="R5" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A5,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A5,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N5="","",N5/IF(INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S5" s="20">
-        <f>IF(Q5="","",(Q5+R5)*INDEX(Baux!$J:$J,MATCH($A5,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A5,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A5,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T5" s="20">
-        <f>IF(Q5="","",Q5+R5+S5)</f>
-        <v/>
-      </c>
-      <c r="U5" s="15">
-        <f>IF(G5="",IF(D5&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D5&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V5" s="11" t="n"/>
-      <c r="W5" s="12" t="n"/>
+        <f>IF(R5="","",(R5+S5)*INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U5" s="20">
+        <f>IF(R5="","",R5+S5+T5)</f>
+        <v/>
+      </c>
+      <c r="V5" s="15">
+        <f>IF(LEFT(K5,5)="Geler","❄ Gelée",IF(G5="",IF(D5&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D5&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W5" s="22" t="inlineStr">
+        <is>
+          <t>Gel décidé par la gérance le 12/03/2025 (difficultés du preneur). Ne pas facturer la hausse. Courrier d'information envoyé.</t>
+        </is>
+      </c>
       <c r="X5" s="11" t="n"/>
-      <c r="Y5" s="15">
+      <c r="Y5" s="12" t="n"/>
+      <c r="Z5" s="12" t="n">
+        <v>45736</v>
+      </c>
+      <c r="AA5" s="11" t="n"/>
+      <c r="AB5" s="15">
         <f>A5&amp;"#"&amp;C5</f>
+        <v/>
+      </c>
+      <c r="AC5" s="15">
+        <f>IF(AND(D5&lt;=TODAY(),N5&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7217,15 +7395,15 @@
         <v>5</v>
       </c>
       <c r="D6" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A6,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A6,Baux!$A:$A,0))*C6)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A6,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A6,Baux!$A:$A,0))*C6)</f>
         <v/>
       </c>
       <c r="E6" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A6,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A6,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F6" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A6,Baux!$A:$A,0)),4))+C6*INDEX(Baux!$N:$N,MATCH($A6,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A6,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A6,Baux!$A:$A,0)),4))+C6*INDEX(Baux!$O:$O,MATCH($A6,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A6,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G6" s="18">
@@ -7233,7 +7411,7 @@
         <v/>
       </c>
       <c r="H6" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A6,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A6,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A6,Baux!$A:$A,0)),4))+(C6-1)*INDEX(Baux!$N:$N,MATCH($A6,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A6,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A6,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A6,Baux!$A:$A,0)),IF(K5="Geler – rattrapage possible",H5,F5))</f>
         <v/>
       </c>
       <c r="I6" s="18">
@@ -7244,55 +7422,62 @@
         <f>IF(OR(G6="",I6=""),"",G6/I6)</f>
         <v/>
       </c>
-      <c r="K6" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A6,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A6,Baux!$A:$A,0)),M5)</f>
-        <v/>
-      </c>
+      <c r="K6" s="11" t="n"/>
       <c r="L6" s="20">
-        <f>IF(OR(J6="",K6=""),"",ROUND(K6*J6,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A6,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A6,Baux!$A:$A,0)),N5)</f>
         <v/>
       </c>
       <c r="M6" s="20">
-        <f>IF(L6="","",IF(INDEX(Baux!$P:$P,MATCH($A6,Baux!$A:$A,0))="",L6,MIN(L6,ROUND(K6*(1+INDEX(Baux!$P:$P,MATCH($A6,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A6,Baux!$A:$A,0))="Base fixe",C6*INDEX(Baux!$N:$N,MATCH($A6,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A6,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J6="",L6=""),"",ROUND(L6*J6,2))</f>
         <v/>
       </c>
       <c r="N6" s="20">
-        <f>M5</f>
-        <v/>
-      </c>
-      <c r="O6" s="21">
-        <f>IF(OR(M6="",N6=""),"",M6/N6-1)</f>
-        <v/>
-      </c>
-      <c r="P6" s="20">
-        <f>IF(M6="","",M6/12)</f>
+        <f>IF(LEFT(K6,5)="Geler",O6,IF(M6="","",IF(INDEX(Baux!$Q:$Q,MATCH($A6,Baux!$A:$A,0))="",M6,MIN(M6,ROUND(L6*(1+INDEX(Baux!$Q:$Q,MATCH($A6,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A6,Baux!$A:$A,0))="Base fixe",C6*INDEX(Baux!$O:$O,MATCH($A6,Baux!$A:$A,0)),VALUE(LEFT(F6,4))-VALUE(LEFT(H6,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O6" s="20">
+        <f>N5</f>
+        <v/>
+      </c>
+      <c r="P6" s="21">
+        <f>IF(OR(N6="",O6=""),"",N6/O6-1)</f>
         <v/>
       </c>
       <c r="Q6" s="20">
-        <f>IF(M6="","",M6/IF(INDEX(Baux!$K:$K,MATCH($A6,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A6,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A6,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N6="","",N6/12)</f>
         <v/>
       </c>
       <c r="R6" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A6,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A6,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A6,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A6,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A6,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N6="","",N6/IF(INDEX(Baux!$L:$L,MATCH($A6,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A6,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A6,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S6" s="20">
-        <f>IF(Q6="","",(Q6+R6)*INDEX(Baux!$J:$J,MATCH($A6,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A6,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A6,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A6,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A6,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A6,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T6" s="20">
-        <f>IF(Q6="","",Q6+R6+S6)</f>
-        <v/>
-      </c>
-      <c r="U6" s="15">
-        <f>IF(G6="",IF(D6&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D6&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V6" s="11" t="n"/>
-      <c r="W6" s="12" t="n"/>
+        <f>IF(R6="","",(R6+S6)*INDEX(Baux!$K:$K,MATCH($A6,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U6" s="20">
+        <f>IF(R6="","",R6+S6+T6)</f>
+        <v/>
+      </c>
+      <c r="V6" s="15">
+        <f>IF(LEFT(K6,5)="Geler","❄ Gelée",IF(G6="",IF(D6&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D6&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W6" s="22" t="n"/>
       <c r="X6" s="11" t="n"/>
-      <c r="Y6" s="15">
+      <c r="Y6" s="12" t="n"/>
+      <c r="Z6" s="12" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="15">
         <f>A6&amp;"#"&amp;C6</f>
+        <v/>
+      </c>
+      <c r="AC6" s="15">
+        <f>IF(AND(D6&lt;=TODAY(),N6&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7310,15 +7495,15 @@
         <v>6</v>
       </c>
       <c r="D7" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A7,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A7,Baux!$A:$A,0))*C7)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A7,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A7,Baux!$A:$A,0))*C7)</f>
         <v/>
       </c>
       <c r="E7" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A7,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A7,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F7" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A7,Baux!$A:$A,0)),4))+C7*INDEX(Baux!$N:$N,MATCH($A7,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A7,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A7,Baux!$A:$A,0)),4))+C7*INDEX(Baux!$O:$O,MATCH($A7,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A7,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G7" s="18">
@@ -7326,7 +7511,7 @@
         <v/>
       </c>
       <c r="H7" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A7,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A7,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A7,Baux!$A:$A,0)),4))+(C7-1)*INDEX(Baux!$N:$N,MATCH($A7,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A7,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A7,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A7,Baux!$A:$A,0)),IF(K6="Geler – rattrapage possible",H6,F6))</f>
         <v/>
       </c>
       <c r="I7" s="18">
@@ -7337,55 +7522,62 @@
         <f>IF(OR(G7="",I7=""),"",G7/I7)</f>
         <v/>
       </c>
-      <c r="K7" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A7,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A7,Baux!$A:$A,0)),M6)</f>
-        <v/>
-      </c>
+      <c r="K7" s="11" t="n"/>
       <c r="L7" s="20">
-        <f>IF(OR(J7="",K7=""),"",ROUND(K7*J7,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A7,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A7,Baux!$A:$A,0)),N6)</f>
         <v/>
       </c>
       <c r="M7" s="20">
-        <f>IF(L7="","",IF(INDEX(Baux!$P:$P,MATCH($A7,Baux!$A:$A,0))="",L7,MIN(L7,ROUND(K7*(1+INDEX(Baux!$P:$P,MATCH($A7,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A7,Baux!$A:$A,0))="Base fixe",C7*INDEX(Baux!$N:$N,MATCH($A7,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A7,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J7="",L7=""),"",ROUND(L7*J7,2))</f>
         <v/>
       </c>
       <c r="N7" s="20">
-        <f>M6</f>
-        <v/>
-      </c>
-      <c r="O7" s="21">
-        <f>IF(OR(M7="",N7=""),"",M7/N7-1)</f>
-        <v/>
-      </c>
-      <c r="P7" s="20">
-        <f>IF(M7="","",M7/12)</f>
+        <f>IF(LEFT(K7,5)="Geler",O7,IF(M7="","",IF(INDEX(Baux!$Q:$Q,MATCH($A7,Baux!$A:$A,0))="",M7,MIN(M7,ROUND(L7*(1+INDEX(Baux!$Q:$Q,MATCH($A7,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A7,Baux!$A:$A,0))="Base fixe",C7*INDEX(Baux!$O:$O,MATCH($A7,Baux!$A:$A,0)),VALUE(LEFT(F7,4))-VALUE(LEFT(H7,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O7" s="20">
+        <f>N6</f>
+        <v/>
+      </c>
+      <c r="P7" s="21">
+        <f>IF(OR(N7="",O7=""),"",N7/O7-1)</f>
         <v/>
       </c>
       <c r="Q7" s="20">
-        <f>IF(M7="","",M7/IF(INDEX(Baux!$K:$K,MATCH($A7,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A7,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A7,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N7="","",N7/12)</f>
         <v/>
       </c>
       <c r="R7" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A7,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A7,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A7,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A7,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A7,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N7="","",N7/IF(INDEX(Baux!$L:$L,MATCH($A7,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A7,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A7,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S7" s="20">
-        <f>IF(Q7="","",(Q7+R7)*INDEX(Baux!$J:$J,MATCH($A7,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A7,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A7,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A7,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A7,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A7,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T7" s="20">
-        <f>IF(Q7="","",Q7+R7+S7)</f>
-        <v/>
-      </c>
-      <c r="U7" s="15">
-        <f>IF(G7="",IF(D7&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D7&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V7" s="11" t="n"/>
-      <c r="W7" s="12" t="n"/>
+        <f>IF(R7="","",(R7+S7)*INDEX(Baux!$K:$K,MATCH($A7,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U7" s="20">
+        <f>IF(R7="","",R7+S7+T7)</f>
+        <v/>
+      </c>
+      <c r="V7" s="15">
+        <f>IF(LEFT(K7,5)="Geler","❄ Gelée",IF(G7="",IF(D7&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D7&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W7" s="22" t="n"/>
       <c r="X7" s="11" t="n"/>
-      <c r="Y7" s="15">
+      <c r="Y7" s="12" t="n"/>
+      <c r="Z7" s="12" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="15">
         <f>A7&amp;"#"&amp;C7</f>
+        <v/>
+      </c>
+      <c r="AC7" s="15">
+        <f>IF(AND(D7&lt;=TODAY(),N7&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7403,15 +7595,15 @@
         <v>7</v>
       </c>
       <c r="D8" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A8,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A8,Baux!$A:$A,0))*C8)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A8,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A8,Baux!$A:$A,0))*C8)</f>
         <v/>
       </c>
       <c r="E8" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A8,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A8,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F8" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A8,Baux!$A:$A,0)),4))+C8*INDEX(Baux!$N:$N,MATCH($A8,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A8,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A8,Baux!$A:$A,0)),4))+C8*INDEX(Baux!$O:$O,MATCH($A8,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A8,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G8" s="18">
@@ -7419,7 +7611,7 @@
         <v/>
       </c>
       <c r="H8" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A8,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A8,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A8,Baux!$A:$A,0)),4))+(C8-1)*INDEX(Baux!$N:$N,MATCH($A8,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A8,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A8,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A8,Baux!$A:$A,0)),IF(K7="Geler – rattrapage possible",H7,F7))</f>
         <v/>
       </c>
       <c r="I8" s="18">
@@ -7430,55 +7622,62 @@
         <f>IF(OR(G8="",I8=""),"",G8/I8)</f>
         <v/>
       </c>
-      <c r="K8" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A8,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A8,Baux!$A:$A,0)),M7)</f>
-        <v/>
-      </c>
+      <c r="K8" s="11" t="n"/>
       <c r="L8" s="20">
-        <f>IF(OR(J8="",K8=""),"",ROUND(K8*J8,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A8,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A8,Baux!$A:$A,0)),N7)</f>
         <v/>
       </c>
       <c r="M8" s="20">
-        <f>IF(L8="","",IF(INDEX(Baux!$P:$P,MATCH($A8,Baux!$A:$A,0))="",L8,MIN(L8,ROUND(K8*(1+INDEX(Baux!$P:$P,MATCH($A8,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A8,Baux!$A:$A,0))="Base fixe",C8*INDEX(Baux!$N:$N,MATCH($A8,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A8,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J8="",L8=""),"",ROUND(L8*J8,2))</f>
         <v/>
       </c>
       <c r="N8" s="20">
-        <f>M7</f>
-        <v/>
-      </c>
-      <c r="O8" s="21">
-        <f>IF(OR(M8="",N8=""),"",M8/N8-1)</f>
-        <v/>
-      </c>
-      <c r="P8" s="20">
-        <f>IF(M8="","",M8/12)</f>
+        <f>IF(LEFT(K8,5)="Geler",O8,IF(M8="","",IF(INDEX(Baux!$Q:$Q,MATCH($A8,Baux!$A:$A,0))="",M8,MIN(M8,ROUND(L8*(1+INDEX(Baux!$Q:$Q,MATCH($A8,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A8,Baux!$A:$A,0))="Base fixe",C8*INDEX(Baux!$O:$O,MATCH($A8,Baux!$A:$A,0)),VALUE(LEFT(F8,4))-VALUE(LEFT(H8,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O8" s="20">
+        <f>N7</f>
+        <v/>
+      </c>
+      <c r="P8" s="21">
+        <f>IF(OR(N8="",O8=""),"",N8/O8-1)</f>
         <v/>
       </c>
       <c r="Q8" s="20">
-        <f>IF(M8="","",M8/IF(INDEX(Baux!$K:$K,MATCH($A8,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A8,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A8,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N8="","",N8/12)</f>
         <v/>
       </c>
       <c r="R8" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A8,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A8,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A8,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A8,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A8,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N8="","",N8/IF(INDEX(Baux!$L:$L,MATCH($A8,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A8,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A8,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S8" s="20">
-        <f>IF(Q8="","",(Q8+R8)*INDEX(Baux!$J:$J,MATCH($A8,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A8,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A8,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A8,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A8,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A8,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T8" s="20">
-        <f>IF(Q8="","",Q8+R8+S8)</f>
-        <v/>
-      </c>
-      <c r="U8" s="15">
-        <f>IF(G8="",IF(D8&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D8&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V8" s="11" t="n"/>
-      <c r="W8" s="12" t="n"/>
+        <f>IF(R8="","",(R8+S8)*INDEX(Baux!$K:$K,MATCH($A8,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U8" s="20">
+        <f>IF(R8="","",R8+S8+T8)</f>
+        <v/>
+      </c>
+      <c r="V8" s="15">
+        <f>IF(LEFT(K8,5)="Geler","❄ Gelée",IF(G8="",IF(D8&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D8&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W8" s="22" t="n"/>
       <c r="X8" s="11" t="n"/>
-      <c r="Y8" s="15">
+      <c r="Y8" s="12" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="15">
         <f>A8&amp;"#"&amp;C8</f>
+        <v/>
+      </c>
+      <c r="AC8" s="15">
+        <f>IF(AND(D8&lt;=TODAY(),N8&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7496,15 +7695,15 @@
         <v>8</v>
       </c>
       <c r="D9" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A9,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A9,Baux!$A:$A,0))*C9)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A9,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A9,Baux!$A:$A,0))*C9)</f>
         <v/>
       </c>
       <c r="E9" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A9,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A9,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F9" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A9,Baux!$A:$A,0)),4))+C9*INDEX(Baux!$N:$N,MATCH($A9,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A9,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A9,Baux!$A:$A,0)),4))+C9*INDEX(Baux!$O:$O,MATCH($A9,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A9,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G9" s="18">
@@ -7512,7 +7711,7 @@
         <v/>
       </c>
       <c r="H9" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A9,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A9,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A9,Baux!$A:$A,0)),4))+(C9-1)*INDEX(Baux!$N:$N,MATCH($A9,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A9,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A9,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A9,Baux!$A:$A,0)),IF(K8="Geler – rattrapage possible",H8,F8))</f>
         <v/>
       </c>
       <c r="I9" s="18">
@@ -7523,55 +7722,62 @@
         <f>IF(OR(G9="",I9=""),"",G9/I9)</f>
         <v/>
       </c>
-      <c r="K9" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A9,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A9,Baux!$A:$A,0)),M8)</f>
-        <v/>
-      </c>
+      <c r="K9" s="11" t="n"/>
       <c r="L9" s="20">
-        <f>IF(OR(J9="",K9=""),"",ROUND(K9*J9,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A9,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A9,Baux!$A:$A,0)),N8)</f>
         <v/>
       </c>
       <c r="M9" s="20">
-        <f>IF(L9="","",IF(INDEX(Baux!$P:$P,MATCH($A9,Baux!$A:$A,0))="",L9,MIN(L9,ROUND(K9*(1+INDEX(Baux!$P:$P,MATCH($A9,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A9,Baux!$A:$A,0))="Base fixe",C9*INDEX(Baux!$N:$N,MATCH($A9,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A9,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J9="",L9=""),"",ROUND(L9*J9,2))</f>
         <v/>
       </c>
       <c r="N9" s="20">
-        <f>M8</f>
-        <v/>
-      </c>
-      <c r="O9" s="21">
-        <f>IF(OR(M9="",N9=""),"",M9/N9-1)</f>
-        <v/>
-      </c>
-      <c r="P9" s="20">
-        <f>IF(M9="","",M9/12)</f>
+        <f>IF(LEFT(K9,5)="Geler",O9,IF(M9="","",IF(INDEX(Baux!$Q:$Q,MATCH($A9,Baux!$A:$A,0))="",M9,MIN(M9,ROUND(L9*(1+INDEX(Baux!$Q:$Q,MATCH($A9,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A9,Baux!$A:$A,0))="Base fixe",C9*INDEX(Baux!$O:$O,MATCH($A9,Baux!$A:$A,0)),VALUE(LEFT(F9,4))-VALUE(LEFT(H9,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O9" s="20">
+        <f>N8</f>
+        <v/>
+      </c>
+      <c r="P9" s="21">
+        <f>IF(OR(N9="",O9=""),"",N9/O9-1)</f>
         <v/>
       </c>
       <c r="Q9" s="20">
-        <f>IF(M9="","",M9/IF(INDEX(Baux!$K:$K,MATCH($A9,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A9,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A9,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N9="","",N9/12)</f>
         <v/>
       </c>
       <c r="R9" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A9,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A9,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A9,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A9,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A9,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N9="","",N9/IF(INDEX(Baux!$L:$L,MATCH($A9,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A9,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A9,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S9" s="20">
-        <f>IF(Q9="","",(Q9+R9)*INDEX(Baux!$J:$J,MATCH($A9,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A9,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A9,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A9,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A9,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A9,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T9" s="20">
-        <f>IF(Q9="","",Q9+R9+S9)</f>
-        <v/>
-      </c>
-      <c r="U9" s="15">
-        <f>IF(G9="",IF(D9&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D9&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V9" s="11" t="n"/>
-      <c r="W9" s="12" t="n"/>
+        <f>IF(R9="","",(R9+S9)*INDEX(Baux!$K:$K,MATCH($A9,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U9" s="20">
+        <f>IF(R9="","",R9+S9+T9)</f>
+        <v/>
+      </c>
+      <c r="V9" s="15">
+        <f>IF(LEFT(K9,5)="Geler","❄ Gelée",IF(G9="",IF(D9&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D9&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W9" s="22" t="n"/>
       <c r="X9" s="11" t="n"/>
-      <c r="Y9" s="15">
+      <c r="Y9" s="12" t="n"/>
+      <c r="Z9" s="12" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="15">
         <f>A9&amp;"#"&amp;C9</f>
+        <v/>
+      </c>
+      <c r="AC9" s="15">
+        <f>IF(AND(D9&lt;=TODAY(),N9&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7589,15 +7795,15 @@
         <v>9</v>
       </c>
       <c r="D10" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A10,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A10,Baux!$A:$A,0))*C10)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A10,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A10,Baux!$A:$A,0))*C10)</f>
         <v/>
       </c>
       <c r="E10" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A10,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A10,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F10" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A10,Baux!$A:$A,0)),4))+C10*INDEX(Baux!$N:$N,MATCH($A10,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A10,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A10,Baux!$A:$A,0)),4))+C10*INDEX(Baux!$O:$O,MATCH($A10,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A10,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G10" s="18">
@@ -7605,7 +7811,7 @@
         <v/>
       </c>
       <c r="H10" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A10,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A10,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A10,Baux!$A:$A,0)),4))+(C10-1)*INDEX(Baux!$N:$N,MATCH($A10,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A10,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A10,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A10,Baux!$A:$A,0)),IF(K9="Geler – rattrapage possible",H9,F9))</f>
         <v/>
       </c>
       <c r="I10" s="18">
@@ -7616,55 +7822,62 @@
         <f>IF(OR(G10="",I10=""),"",G10/I10)</f>
         <v/>
       </c>
-      <c r="K10" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A10,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A10,Baux!$A:$A,0)),M9)</f>
-        <v/>
-      </c>
+      <c r="K10" s="11" t="n"/>
       <c r="L10" s="20">
-        <f>IF(OR(J10="",K10=""),"",ROUND(K10*J10,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A10,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A10,Baux!$A:$A,0)),N9)</f>
         <v/>
       </c>
       <c r="M10" s="20">
-        <f>IF(L10="","",IF(INDEX(Baux!$P:$P,MATCH($A10,Baux!$A:$A,0))="",L10,MIN(L10,ROUND(K10*(1+INDEX(Baux!$P:$P,MATCH($A10,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A10,Baux!$A:$A,0))="Base fixe",C10*INDEX(Baux!$N:$N,MATCH($A10,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A10,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J10="",L10=""),"",ROUND(L10*J10,2))</f>
         <v/>
       </c>
       <c r="N10" s="20">
-        <f>M9</f>
-        <v/>
-      </c>
-      <c r="O10" s="21">
-        <f>IF(OR(M10="",N10=""),"",M10/N10-1)</f>
-        <v/>
-      </c>
-      <c r="P10" s="20">
-        <f>IF(M10="","",M10/12)</f>
+        <f>IF(LEFT(K10,5)="Geler",O10,IF(M10="","",IF(INDEX(Baux!$Q:$Q,MATCH($A10,Baux!$A:$A,0))="",M10,MIN(M10,ROUND(L10*(1+INDEX(Baux!$Q:$Q,MATCH($A10,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A10,Baux!$A:$A,0))="Base fixe",C10*INDEX(Baux!$O:$O,MATCH($A10,Baux!$A:$A,0)),VALUE(LEFT(F10,4))-VALUE(LEFT(H10,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="20">
+        <f>N9</f>
+        <v/>
+      </c>
+      <c r="P10" s="21">
+        <f>IF(OR(N10="",O10=""),"",N10/O10-1)</f>
         <v/>
       </c>
       <c r="Q10" s="20">
-        <f>IF(M10="","",M10/IF(INDEX(Baux!$K:$K,MATCH($A10,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A10,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A10,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N10="","",N10/12)</f>
         <v/>
       </c>
       <c r="R10" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A10,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A10,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A10,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A10,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A10,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N10="","",N10/IF(INDEX(Baux!$L:$L,MATCH($A10,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A10,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A10,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S10" s="20">
-        <f>IF(Q10="","",(Q10+R10)*INDEX(Baux!$J:$J,MATCH($A10,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A10,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A10,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A10,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A10,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A10,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T10" s="20">
-        <f>IF(Q10="","",Q10+R10+S10)</f>
-        <v/>
-      </c>
-      <c r="U10" s="15">
-        <f>IF(G10="",IF(D10&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D10&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V10" s="11" t="n"/>
-      <c r="W10" s="12" t="n"/>
+        <f>IF(R10="","",(R10+S10)*INDEX(Baux!$K:$K,MATCH($A10,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U10" s="20">
+        <f>IF(R10="","",R10+S10+T10)</f>
+        <v/>
+      </c>
+      <c r="V10" s="15">
+        <f>IF(LEFT(K10,5)="Geler","❄ Gelée",IF(G10="",IF(D10&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D10&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W10" s="22" t="n"/>
       <c r="X10" s="11" t="n"/>
-      <c r="Y10" s="15">
+      <c r="Y10" s="12" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="11" t="n"/>
+      <c r="AB10" s="15">
         <f>A10&amp;"#"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="AC10" s="15">
+        <f>IF(AND(D10&lt;=TODAY(),N10&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7682,15 +7895,15 @@
         <v>1</v>
       </c>
       <c r="D11" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A11,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A11,Baux!$A:$A,0))*C11)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A11,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A11,Baux!$A:$A,0))*C11)</f>
         <v/>
       </c>
       <c r="E11" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A11,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A11,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F11" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A11,Baux!$A:$A,0)),4))+C11*INDEX(Baux!$N:$N,MATCH($A11,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A11,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A11,Baux!$A:$A,0)),4))+C11*INDEX(Baux!$O:$O,MATCH($A11,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A11,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G11" s="18">
@@ -7698,7 +7911,7 @@
         <v/>
       </c>
       <c r="H11" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A11,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A11,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A11,Baux!$A:$A,0)),4))+(C11-1)*INDEX(Baux!$N:$N,MATCH($A11,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A11,Baux!$A:$A,0)),3))</f>
+        <f>INDEX(Baux!$N:$N,MATCH($A11,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="I11" s="18">
@@ -7709,55 +7922,62 @@
         <f>IF(OR(G11="",I11=""),"",G11/I11)</f>
         <v/>
       </c>
-      <c r="K11" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A11,Baux!$A:$A,0))</f>
-        <v/>
-      </c>
+      <c r="K11" s="11" t="n"/>
       <c r="L11" s="20">
-        <f>IF(OR(J11="",K11=""),"",ROUND(K11*J11,2))</f>
+        <f>INDEX(Baux!$I:$I,MATCH($A11,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="M11" s="20">
-        <f>IF(L11="","",IF(INDEX(Baux!$P:$P,MATCH($A11,Baux!$A:$A,0))="",L11,MIN(L11,ROUND(K11*(1+INDEX(Baux!$P:$P,MATCH($A11,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A11,Baux!$A:$A,0))="Base fixe",C11*INDEX(Baux!$N:$N,MATCH($A11,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A11,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J11="",L11=""),"",ROUND(L11*J11,2))</f>
         <v/>
       </c>
       <c r="N11" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A11,Baux!$A:$A,0))</f>
-        <v/>
-      </c>
-      <c r="O11" s="21">
-        <f>IF(OR(M11="",N11=""),"",M11/N11-1)</f>
-        <v/>
-      </c>
-      <c r="P11" s="20">
-        <f>IF(M11="","",M11/12)</f>
+        <f>IF(LEFT(K11,5)="Geler",O11,IF(M11="","",IF(INDEX(Baux!$Q:$Q,MATCH($A11,Baux!$A:$A,0))="",M11,MIN(M11,ROUND(L11*(1+INDEX(Baux!$Q:$Q,MATCH($A11,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A11,Baux!$A:$A,0))="Base fixe",C11*INDEX(Baux!$O:$O,MATCH($A11,Baux!$A:$A,0)),VALUE(LEFT(F11,4))-VALUE(LEFT(H11,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O11" s="20">
+        <f>INDEX(Baux!$I:$I,MATCH($A11,Baux!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="P11" s="21">
+        <f>IF(OR(N11="",O11=""),"",N11/O11-1)</f>
         <v/>
       </c>
       <c r="Q11" s="20">
-        <f>IF(M11="","",M11/IF(INDEX(Baux!$K:$K,MATCH($A11,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A11,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A11,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N11="","",N11/12)</f>
         <v/>
       </c>
       <c r="R11" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A11,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A11,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A11,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A11,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A11,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N11="","",N11/IF(INDEX(Baux!$L:$L,MATCH($A11,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A11,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A11,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S11" s="20">
-        <f>IF(Q11="","",(Q11+R11)*INDEX(Baux!$J:$J,MATCH($A11,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A11,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A11,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A11,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A11,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A11,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T11" s="20">
-        <f>IF(Q11="","",Q11+R11+S11)</f>
-        <v/>
-      </c>
-      <c r="U11" s="15">
-        <f>IF(G11="",IF(D11&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D11&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V11" s="11" t="n"/>
-      <c r="W11" s="12" t="n"/>
+        <f>IF(R11="","",(R11+S11)*INDEX(Baux!$K:$K,MATCH($A11,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U11" s="20">
+        <f>IF(R11="","",R11+S11+T11)</f>
+        <v/>
+      </c>
+      <c r="V11" s="15">
+        <f>IF(LEFT(K11,5)="Geler","❄ Gelée",IF(G11="",IF(D11&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D11&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W11" s="22" t="n"/>
       <c r="X11" s="11" t="n"/>
-      <c r="Y11" s="15">
+      <c r="Y11" s="12" t="n"/>
+      <c r="Z11" s="12" t="n"/>
+      <c r="AA11" s="11" t="n"/>
+      <c r="AB11" s="15">
         <f>A11&amp;"#"&amp;C11</f>
+        <v/>
+      </c>
+      <c r="AC11" s="15">
+        <f>IF(AND(D11&lt;=TODAY(),N11&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7775,15 +7995,15 @@
         <v>2</v>
       </c>
       <c r="D12" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A12,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A12,Baux!$A:$A,0))*C12)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A12,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A12,Baux!$A:$A,0))*C12)</f>
         <v/>
       </c>
       <c r="E12" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A12,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A12,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F12" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A12,Baux!$A:$A,0)),4))+C12*INDEX(Baux!$N:$N,MATCH($A12,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A12,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A12,Baux!$A:$A,0)),4))+C12*INDEX(Baux!$O:$O,MATCH($A12,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A12,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G12" s="18">
@@ -7791,7 +8011,7 @@
         <v/>
       </c>
       <c r="H12" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A12,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A12,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A12,Baux!$A:$A,0)),4))+(C12-1)*INDEX(Baux!$N:$N,MATCH($A12,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A12,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A12,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A12,Baux!$A:$A,0)),IF(K11="Geler – rattrapage possible",H11,F11))</f>
         <v/>
       </c>
       <c r="I12" s="18">
@@ -7802,55 +8022,62 @@
         <f>IF(OR(G12="",I12=""),"",G12/I12)</f>
         <v/>
       </c>
-      <c r="K12" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A12,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A12,Baux!$A:$A,0)),M11)</f>
-        <v/>
-      </c>
+      <c r="K12" s="11" t="n"/>
       <c r="L12" s="20">
-        <f>IF(OR(J12="",K12=""),"",ROUND(K12*J12,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A12,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A12,Baux!$A:$A,0)),N11)</f>
         <v/>
       </c>
       <c r="M12" s="20">
-        <f>IF(L12="","",IF(INDEX(Baux!$P:$P,MATCH($A12,Baux!$A:$A,0))="",L12,MIN(L12,ROUND(K12*(1+INDEX(Baux!$P:$P,MATCH($A12,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A12,Baux!$A:$A,0))="Base fixe",C12*INDEX(Baux!$N:$N,MATCH($A12,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A12,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J12="",L12=""),"",ROUND(L12*J12,2))</f>
         <v/>
       </c>
       <c r="N12" s="20">
-        <f>M11</f>
-        <v/>
-      </c>
-      <c r="O12" s="21">
-        <f>IF(OR(M12="",N12=""),"",M12/N12-1)</f>
-        <v/>
-      </c>
-      <c r="P12" s="20">
-        <f>IF(M12="","",M12/12)</f>
+        <f>IF(LEFT(K12,5)="Geler",O12,IF(M12="","",IF(INDEX(Baux!$Q:$Q,MATCH($A12,Baux!$A:$A,0))="",M12,MIN(M12,ROUND(L12*(1+INDEX(Baux!$Q:$Q,MATCH($A12,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A12,Baux!$A:$A,0))="Base fixe",C12*INDEX(Baux!$O:$O,MATCH($A12,Baux!$A:$A,0)),VALUE(LEFT(F12,4))-VALUE(LEFT(H12,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O12" s="20">
+        <f>N11</f>
+        <v/>
+      </c>
+      <c r="P12" s="21">
+        <f>IF(OR(N12="",O12=""),"",N12/O12-1)</f>
         <v/>
       </c>
       <c r="Q12" s="20">
-        <f>IF(M12="","",M12/IF(INDEX(Baux!$K:$K,MATCH($A12,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A12,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A12,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N12="","",N12/12)</f>
         <v/>
       </c>
       <c r="R12" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A12,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A12,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A12,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A12,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A12,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N12="","",N12/IF(INDEX(Baux!$L:$L,MATCH($A12,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A12,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A12,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S12" s="20">
-        <f>IF(Q12="","",(Q12+R12)*INDEX(Baux!$J:$J,MATCH($A12,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A12,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A12,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A12,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A12,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A12,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T12" s="20">
-        <f>IF(Q12="","",Q12+R12+S12)</f>
-        <v/>
-      </c>
-      <c r="U12" s="15">
-        <f>IF(G12="",IF(D12&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D12&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V12" s="11" t="n"/>
-      <c r="W12" s="12" t="n"/>
+        <f>IF(R12="","",(R12+S12)*INDEX(Baux!$K:$K,MATCH($A12,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U12" s="20">
+        <f>IF(R12="","",R12+S12+T12)</f>
+        <v/>
+      </c>
+      <c r="V12" s="15">
+        <f>IF(LEFT(K12,5)="Geler","❄ Gelée",IF(G12="",IF(D12&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D12&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W12" s="22" t="n"/>
       <c r="X12" s="11" t="n"/>
-      <c r="Y12" s="15">
+      <c r="Y12" s="12" t="n"/>
+      <c r="Z12" s="12" t="n"/>
+      <c r="AA12" s="11" t="n"/>
+      <c r="AB12" s="15">
         <f>A12&amp;"#"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="15">
+        <f>IF(AND(D12&lt;=TODAY(),N12&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7868,15 +8095,15 @@
         <v>3</v>
       </c>
       <c r="D13" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A13,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A13,Baux!$A:$A,0))*C13)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A13,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A13,Baux!$A:$A,0))*C13)</f>
         <v/>
       </c>
       <c r="E13" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A13,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A13,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A13,Baux!$A:$A,0)),4))+C13*INDEX(Baux!$N:$N,MATCH($A13,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A13,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A13,Baux!$A:$A,0)),4))+C13*INDEX(Baux!$O:$O,MATCH($A13,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A13,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G13" s="18">
@@ -7884,7 +8111,7 @@
         <v/>
       </c>
       <c r="H13" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A13,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A13,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A13,Baux!$A:$A,0)),4))+(C13-1)*INDEX(Baux!$N:$N,MATCH($A13,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A13,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A13,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A13,Baux!$A:$A,0)),IF(K12="Geler – rattrapage possible",H12,F12))</f>
         <v/>
       </c>
       <c r="I13" s="18">
@@ -7895,55 +8122,62 @@
         <f>IF(OR(G13="",I13=""),"",G13/I13)</f>
         <v/>
       </c>
-      <c r="K13" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A13,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A13,Baux!$A:$A,0)),M12)</f>
-        <v/>
-      </c>
+      <c r="K13" s="11" t="n"/>
       <c r="L13" s="20">
-        <f>IF(OR(J13="",K13=""),"",ROUND(K13*J13,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A13,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A13,Baux!$A:$A,0)),N12)</f>
         <v/>
       </c>
       <c r="M13" s="20">
-        <f>IF(L13="","",IF(INDEX(Baux!$P:$P,MATCH($A13,Baux!$A:$A,0))="",L13,MIN(L13,ROUND(K13*(1+INDEX(Baux!$P:$P,MATCH($A13,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A13,Baux!$A:$A,0))="Base fixe",C13*INDEX(Baux!$N:$N,MATCH($A13,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A13,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J13="",L13=""),"",ROUND(L13*J13,2))</f>
         <v/>
       </c>
       <c r="N13" s="20">
-        <f>M12</f>
-        <v/>
-      </c>
-      <c r="O13" s="21">
-        <f>IF(OR(M13="",N13=""),"",M13/N13-1)</f>
-        <v/>
-      </c>
-      <c r="P13" s="20">
-        <f>IF(M13="","",M13/12)</f>
+        <f>IF(LEFT(K13,5)="Geler",O13,IF(M13="","",IF(INDEX(Baux!$Q:$Q,MATCH($A13,Baux!$A:$A,0))="",M13,MIN(M13,ROUND(L13*(1+INDEX(Baux!$Q:$Q,MATCH($A13,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A13,Baux!$A:$A,0))="Base fixe",C13*INDEX(Baux!$O:$O,MATCH($A13,Baux!$A:$A,0)),VALUE(LEFT(F13,4))-VALUE(LEFT(H13,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O13" s="20">
+        <f>N12</f>
+        <v/>
+      </c>
+      <c r="P13" s="21">
+        <f>IF(OR(N13="",O13=""),"",N13/O13-1)</f>
         <v/>
       </c>
       <c r="Q13" s="20">
-        <f>IF(M13="","",M13/IF(INDEX(Baux!$K:$K,MATCH($A13,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A13,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A13,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N13="","",N13/12)</f>
         <v/>
       </c>
       <c r="R13" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A13,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A13,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A13,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A13,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A13,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N13="","",N13/IF(INDEX(Baux!$L:$L,MATCH($A13,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A13,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A13,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S13" s="20">
-        <f>IF(Q13="","",(Q13+R13)*INDEX(Baux!$J:$J,MATCH($A13,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A13,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A13,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A13,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A13,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A13,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T13" s="20">
-        <f>IF(Q13="","",Q13+R13+S13)</f>
-        <v/>
-      </c>
-      <c r="U13" s="15">
-        <f>IF(G13="",IF(D13&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D13&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V13" s="11" t="n"/>
-      <c r="W13" s="12" t="n"/>
+        <f>IF(R13="","",(R13+S13)*INDEX(Baux!$K:$K,MATCH($A13,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U13" s="20">
+        <f>IF(R13="","",R13+S13+T13)</f>
+        <v/>
+      </c>
+      <c r="V13" s="15">
+        <f>IF(LEFT(K13,5)="Geler","❄ Gelée",IF(G13="",IF(D13&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D13&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W13" s="22" t="n"/>
       <c r="X13" s="11" t="n"/>
-      <c r="Y13" s="15">
+      <c r="Y13" s="12" t="n"/>
+      <c r="Z13" s="12" t="n"/>
+      <c r="AA13" s="11" t="n"/>
+      <c r="AB13" s="15">
         <f>A13&amp;"#"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="15">
+        <f>IF(AND(D13&lt;=TODAY(),N13&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -7961,15 +8195,15 @@
         <v>1</v>
       </c>
       <c r="D14" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A14,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A14,Baux!$A:$A,0))*C14)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A14,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A14,Baux!$A:$A,0))*C14)</f>
         <v/>
       </c>
       <c r="E14" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A14,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A14,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A14,Baux!$A:$A,0)),4))+C14*INDEX(Baux!$N:$N,MATCH($A14,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A14,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A14,Baux!$A:$A,0)),4))+C14*INDEX(Baux!$O:$O,MATCH($A14,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A14,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G14" s="18">
@@ -7977,7 +8211,7 @@
         <v/>
       </c>
       <c r="H14" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A14,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A14,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A14,Baux!$A:$A,0)),4))+(C14-1)*INDEX(Baux!$N:$N,MATCH($A14,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A14,Baux!$A:$A,0)),3))</f>
+        <f>INDEX(Baux!$N:$N,MATCH($A14,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="I14" s="18">
@@ -7988,55 +8222,66 @@
         <f>IF(OR(G14="",I14=""),"",G14/I14)</f>
         <v/>
       </c>
-      <c r="K14" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A14,Baux!$A:$A,0))</f>
-        <v/>
-      </c>
+      <c r="K14" s="11" t="n"/>
       <c r="L14" s="20">
-        <f>IF(OR(J14="",K14=""),"",ROUND(K14*J14,2))</f>
+        <f>INDEX(Baux!$I:$I,MATCH($A14,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="M14" s="20">
-        <f>IF(L14="","",IF(INDEX(Baux!$P:$P,MATCH($A14,Baux!$A:$A,0))="",L14,MIN(L14,ROUND(K14*(1+INDEX(Baux!$P:$P,MATCH($A14,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A14,Baux!$A:$A,0))="Base fixe",C14*INDEX(Baux!$N:$N,MATCH($A14,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A14,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J14="",L14=""),"",ROUND(L14*J14,2))</f>
         <v/>
       </c>
       <c r="N14" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A14,Baux!$A:$A,0))</f>
-        <v/>
-      </c>
-      <c r="O14" s="21">
-        <f>IF(OR(M14="",N14=""),"",M14/N14-1)</f>
-        <v/>
-      </c>
-      <c r="P14" s="20">
-        <f>IF(M14="","",M14/12)</f>
+        <f>IF(LEFT(K14,5)="Geler",O14,IF(M14="","",IF(INDEX(Baux!$Q:$Q,MATCH($A14,Baux!$A:$A,0))="",M14,MIN(M14,ROUND(L14*(1+INDEX(Baux!$Q:$Q,MATCH($A14,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A14,Baux!$A:$A,0))="Base fixe",C14*INDEX(Baux!$O:$O,MATCH($A14,Baux!$A:$A,0)),VALUE(LEFT(F14,4))-VALUE(LEFT(H14,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O14" s="20">
+        <f>INDEX(Baux!$I:$I,MATCH($A14,Baux!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="P14" s="21">
+        <f>IF(OR(N14="",O14=""),"",N14/O14-1)</f>
         <v/>
       </c>
       <c r="Q14" s="20">
-        <f>IF(M14="","",M14/IF(INDEX(Baux!$K:$K,MATCH($A14,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A14,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A14,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N14="","",N14/12)</f>
         <v/>
       </c>
       <c r="R14" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A14,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A14,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A14,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A14,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A14,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N14="","",N14/IF(INDEX(Baux!$L:$L,MATCH($A14,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A14,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A14,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S14" s="20">
-        <f>IF(Q14="","",(Q14+R14)*INDEX(Baux!$J:$J,MATCH($A14,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A14,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A14,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A14,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A14,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A14,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T14" s="20">
-        <f>IF(Q14="","",Q14+R14+S14)</f>
-        <v/>
-      </c>
-      <c r="U14" s="15">
-        <f>IF(G14="",IF(D14&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D14&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V14" s="11" t="n"/>
-      <c r="W14" s="12" t="n"/>
-      <c r="X14" s="11" t="n"/>
-      <c r="Y14" s="15">
+        <f>IF(R14="","",(R14+S14)*INDEX(Baux!$K:$K,MATCH($A14,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U14" s="20">
+        <f>IF(R14="","",R14+S14+T14)</f>
+        <v/>
+      </c>
+      <c r="V14" s="15">
+        <f>IF(LEFT(K14,5)="Geler","❄ Gelée",IF(G14="",IF(D14&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D14&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W14" s="22" t="n"/>
+      <c r="X14" s="11" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Y14" s="12" t="n"/>
+      <c r="Z14" s="12" t="n"/>
+      <c r="AA14" s="11" t="n"/>
+      <c r="AB14" s="15">
         <f>A14&amp;"#"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="15">
+        <f>IF(AND(D14&lt;=TODAY(),N14&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8054,15 +8299,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A15,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A15,Baux!$A:$A,0))*C15)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A15,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A15,Baux!$A:$A,0))*C15)</f>
         <v/>
       </c>
       <c r="E15" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A15,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A15,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F15" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A15,Baux!$A:$A,0)),4))+C15*INDEX(Baux!$N:$N,MATCH($A15,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A15,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A15,Baux!$A:$A,0)),4))+C15*INDEX(Baux!$O:$O,MATCH($A15,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A15,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G15" s="18">
@@ -8070,7 +8315,7 @@
         <v/>
       </c>
       <c r="H15" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A15,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A15,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A15,Baux!$A:$A,0)),4))+(C15-1)*INDEX(Baux!$N:$N,MATCH($A15,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A15,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A15,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A15,Baux!$A:$A,0)),IF(K14="Geler – rattrapage possible",H14,F14))</f>
         <v/>
       </c>
       <c r="I15" s="18">
@@ -8081,55 +8326,66 @@
         <f>IF(OR(G15="",I15=""),"",G15/I15)</f>
         <v/>
       </c>
-      <c r="K15" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A15,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A15,Baux!$A:$A,0)),M14)</f>
-        <v/>
-      </c>
+      <c r="K15" s="11" t="n"/>
       <c r="L15" s="20">
-        <f>IF(OR(J15="",K15=""),"",ROUND(K15*J15,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A15,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A15,Baux!$A:$A,0)),N14)</f>
         <v/>
       </c>
       <c r="M15" s="20">
-        <f>IF(L15="","",IF(INDEX(Baux!$P:$P,MATCH($A15,Baux!$A:$A,0))="",L15,MIN(L15,ROUND(K15*(1+INDEX(Baux!$P:$P,MATCH($A15,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A15,Baux!$A:$A,0))="Base fixe",C15*INDEX(Baux!$N:$N,MATCH($A15,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A15,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J15="",L15=""),"",ROUND(L15*J15,2))</f>
         <v/>
       </c>
       <c r="N15" s="20">
-        <f>M14</f>
-        <v/>
-      </c>
-      <c r="O15" s="21">
-        <f>IF(OR(M15="",N15=""),"",M15/N15-1)</f>
-        <v/>
-      </c>
-      <c r="P15" s="20">
-        <f>IF(M15="","",M15/12)</f>
+        <f>IF(LEFT(K15,5)="Geler",O15,IF(M15="","",IF(INDEX(Baux!$Q:$Q,MATCH($A15,Baux!$A:$A,0))="",M15,MIN(M15,ROUND(L15*(1+INDEX(Baux!$Q:$Q,MATCH($A15,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A15,Baux!$A:$A,0))="Base fixe",C15*INDEX(Baux!$O:$O,MATCH($A15,Baux!$A:$A,0)),VALUE(LEFT(F15,4))-VALUE(LEFT(H15,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O15" s="20">
+        <f>N14</f>
+        <v/>
+      </c>
+      <c r="P15" s="21">
+        <f>IF(OR(N15="",O15=""),"",N15/O15-1)</f>
         <v/>
       </c>
       <c r="Q15" s="20">
-        <f>IF(M15="","",M15/IF(INDEX(Baux!$K:$K,MATCH($A15,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A15,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A15,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N15="","",N15/12)</f>
         <v/>
       </c>
       <c r="R15" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A15,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A15,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A15,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A15,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A15,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N15="","",N15/IF(INDEX(Baux!$L:$L,MATCH($A15,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A15,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A15,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S15" s="20">
-        <f>IF(Q15="","",(Q15+R15)*INDEX(Baux!$J:$J,MATCH($A15,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A15,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A15,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A15,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A15,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A15,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T15" s="20">
-        <f>IF(Q15="","",Q15+R15+S15)</f>
-        <v/>
-      </c>
-      <c r="U15" s="15">
-        <f>IF(G15="",IF(D15&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D15&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V15" s="11" t="n"/>
-      <c r="W15" s="12" t="n"/>
-      <c r="X15" s="11" t="n"/>
-      <c r="Y15" s="15">
+        <f>IF(R15="","",(R15+S15)*INDEX(Baux!$K:$K,MATCH($A15,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U15" s="20">
+        <f>IF(R15="","",R15+S15+T15)</f>
+        <v/>
+      </c>
+      <c r="V15" s="15">
+        <f>IF(LEFT(K15,5)="Geler","❄ Gelée",IF(G15="",IF(D15&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D15&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W15" s="22" t="n"/>
+      <c r="X15" s="11" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Y15" s="12" t="n"/>
+      <c r="Z15" s="12" t="n"/>
+      <c r="AA15" s="11" t="n"/>
+      <c r="AB15" s="15">
         <f>A15&amp;"#"&amp;C15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="15">
+        <f>IF(AND(D15&lt;=TODAY(),N15&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8147,15 +8403,15 @@
         <v>3</v>
       </c>
       <c r="D16" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A16,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A16,Baux!$A:$A,0))*C16)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A16,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A16,Baux!$A:$A,0))*C16)</f>
         <v/>
       </c>
       <c r="E16" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A16,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A16,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A16,Baux!$A:$A,0)),4))+C16*INDEX(Baux!$N:$N,MATCH($A16,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A16,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A16,Baux!$A:$A,0)),4))+C16*INDEX(Baux!$O:$O,MATCH($A16,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A16,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G16" s="18">
@@ -8163,7 +8419,7 @@
         <v/>
       </c>
       <c r="H16" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A16,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A16,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A16,Baux!$A:$A,0)),4))+(C16-1)*INDEX(Baux!$N:$N,MATCH($A16,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A16,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A16,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A16,Baux!$A:$A,0)),IF(K15="Geler – rattrapage possible",H15,F15))</f>
         <v/>
       </c>
       <c r="I16" s="18">
@@ -8174,55 +8430,66 @@
         <f>IF(OR(G16="",I16=""),"",G16/I16)</f>
         <v/>
       </c>
-      <c r="K16" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A16,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A16,Baux!$A:$A,0)),M15)</f>
-        <v/>
-      </c>
+      <c r="K16" s="11" t="n"/>
       <c r="L16" s="20">
-        <f>IF(OR(J16="",K16=""),"",ROUND(K16*J16,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A16,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A16,Baux!$A:$A,0)),N15)</f>
         <v/>
       </c>
       <c r="M16" s="20">
-        <f>IF(L16="","",IF(INDEX(Baux!$P:$P,MATCH($A16,Baux!$A:$A,0))="",L16,MIN(L16,ROUND(K16*(1+INDEX(Baux!$P:$P,MATCH($A16,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A16,Baux!$A:$A,0))="Base fixe",C16*INDEX(Baux!$N:$N,MATCH($A16,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A16,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J16="",L16=""),"",ROUND(L16*J16,2))</f>
         <v/>
       </c>
       <c r="N16" s="20">
-        <f>M15</f>
-        <v/>
-      </c>
-      <c r="O16" s="21">
-        <f>IF(OR(M16="",N16=""),"",M16/N16-1)</f>
-        <v/>
-      </c>
-      <c r="P16" s="20">
-        <f>IF(M16="","",M16/12)</f>
+        <f>IF(LEFT(K16,5)="Geler",O16,IF(M16="","",IF(INDEX(Baux!$Q:$Q,MATCH($A16,Baux!$A:$A,0))="",M16,MIN(M16,ROUND(L16*(1+INDEX(Baux!$Q:$Q,MATCH($A16,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A16,Baux!$A:$A,0))="Base fixe",C16*INDEX(Baux!$O:$O,MATCH($A16,Baux!$A:$A,0)),VALUE(LEFT(F16,4))-VALUE(LEFT(H16,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O16" s="20">
+        <f>N15</f>
+        <v/>
+      </c>
+      <c r="P16" s="21">
+        <f>IF(OR(N16="",O16=""),"",N16/O16-1)</f>
         <v/>
       </c>
       <c r="Q16" s="20">
-        <f>IF(M16="","",M16/IF(INDEX(Baux!$K:$K,MATCH($A16,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A16,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A16,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N16="","",N16/12)</f>
         <v/>
       </c>
       <c r="R16" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A16,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A16,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A16,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A16,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A16,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N16="","",N16/IF(INDEX(Baux!$L:$L,MATCH($A16,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A16,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A16,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S16" s="20">
-        <f>IF(Q16="","",(Q16+R16)*INDEX(Baux!$J:$J,MATCH($A16,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A16,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A16,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A16,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A16,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A16,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T16" s="20">
-        <f>IF(Q16="","",Q16+R16+S16)</f>
-        <v/>
-      </c>
-      <c r="U16" s="15">
-        <f>IF(G16="",IF(D16&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D16&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V16" s="11" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="11" t="n"/>
-      <c r="Y16" s="15">
+        <f>IF(R16="","",(R16+S16)*INDEX(Baux!$K:$K,MATCH($A16,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U16" s="20">
+        <f>IF(R16="","",R16+S16+T16)</f>
+        <v/>
+      </c>
+      <c r="V16" s="15">
+        <f>IF(LEFT(K16,5)="Geler","❄ Gelée",IF(G16="",IF(D16&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D16&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W16" s="22" t="n"/>
+      <c r="X16" s="11" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Y16" s="12" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="11" t="n"/>
+      <c r="AB16" s="15">
         <f>A16&amp;"#"&amp;C16</f>
+        <v/>
+      </c>
+      <c r="AC16" s="15">
+        <f>IF(AND(D16&lt;=TODAY(),N16&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8240,15 +8507,15 @@
         <v>4</v>
       </c>
       <c r="D17" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A17,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A17,Baux!$A:$A,0))*C17)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A17,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A17,Baux!$A:$A,0))*C17)</f>
         <v/>
       </c>
       <c r="E17" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A17,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A17,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F17" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A17,Baux!$A:$A,0)),4))+C17*INDEX(Baux!$N:$N,MATCH($A17,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A17,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A17,Baux!$A:$A,0)),4))+C17*INDEX(Baux!$O:$O,MATCH($A17,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A17,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G17" s="18">
@@ -8256,7 +8523,7 @@
         <v/>
       </c>
       <c r="H17" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A17,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A17,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A17,Baux!$A:$A,0)),4))+(C17-1)*INDEX(Baux!$N:$N,MATCH($A17,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A17,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A17,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A17,Baux!$A:$A,0)),IF(K16="Geler – rattrapage possible",H16,F16))</f>
         <v/>
       </c>
       <c r="I17" s="18">
@@ -8267,55 +8534,66 @@
         <f>IF(OR(G17="",I17=""),"",G17/I17)</f>
         <v/>
       </c>
-      <c r="K17" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A17,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A17,Baux!$A:$A,0)),M16)</f>
-        <v/>
-      </c>
+      <c r="K17" s="11" t="n"/>
       <c r="L17" s="20">
-        <f>IF(OR(J17="",K17=""),"",ROUND(K17*J17,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A17,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A17,Baux!$A:$A,0)),N16)</f>
         <v/>
       </c>
       <c r="M17" s="20">
-        <f>IF(L17="","",IF(INDEX(Baux!$P:$P,MATCH($A17,Baux!$A:$A,0))="",L17,MIN(L17,ROUND(K17*(1+INDEX(Baux!$P:$P,MATCH($A17,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A17,Baux!$A:$A,0))="Base fixe",C17*INDEX(Baux!$N:$N,MATCH($A17,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A17,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J17="",L17=""),"",ROUND(L17*J17,2))</f>
         <v/>
       </c>
       <c r="N17" s="20">
-        <f>M16</f>
-        <v/>
-      </c>
-      <c r="O17" s="21">
-        <f>IF(OR(M17="",N17=""),"",M17/N17-1)</f>
-        <v/>
-      </c>
-      <c r="P17" s="20">
-        <f>IF(M17="","",M17/12)</f>
+        <f>IF(LEFT(K17,5)="Geler",O17,IF(M17="","",IF(INDEX(Baux!$Q:$Q,MATCH($A17,Baux!$A:$A,0))="",M17,MIN(M17,ROUND(L17*(1+INDEX(Baux!$Q:$Q,MATCH($A17,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A17,Baux!$A:$A,0))="Base fixe",C17*INDEX(Baux!$O:$O,MATCH($A17,Baux!$A:$A,0)),VALUE(LEFT(F17,4))-VALUE(LEFT(H17,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O17" s="20">
+        <f>N16</f>
+        <v/>
+      </c>
+      <c r="P17" s="21">
+        <f>IF(OR(N17="",O17=""),"",N17/O17-1)</f>
         <v/>
       </c>
       <c r="Q17" s="20">
-        <f>IF(M17="","",M17/IF(INDEX(Baux!$K:$K,MATCH($A17,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A17,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A17,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N17="","",N17/12)</f>
         <v/>
       </c>
       <c r="R17" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A17,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A17,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A17,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A17,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A17,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N17="","",N17/IF(INDEX(Baux!$L:$L,MATCH($A17,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A17,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A17,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S17" s="20">
-        <f>IF(Q17="","",(Q17+R17)*INDEX(Baux!$J:$J,MATCH($A17,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A17,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A17,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A17,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A17,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A17,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T17" s="20">
-        <f>IF(Q17="","",Q17+R17+S17)</f>
-        <v/>
-      </c>
-      <c r="U17" s="15">
-        <f>IF(G17="",IF(D17&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D17&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V17" s="11" t="n"/>
-      <c r="W17" s="12" t="n"/>
-      <c r="X17" s="11" t="n"/>
-      <c r="Y17" s="15">
+        <f>IF(R17="","",(R17+S17)*INDEX(Baux!$K:$K,MATCH($A17,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U17" s="20">
+        <f>IF(R17="","",R17+S17+T17)</f>
+        <v/>
+      </c>
+      <c r="V17" s="15">
+        <f>IF(LEFT(K17,5)="Geler","❄ Gelée",IF(G17="",IF(D17&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D17&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W17" s="22" t="n"/>
+      <c r="X17" s="11" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Y17" s="12" t="n"/>
+      <c r="Z17" s="12" t="n"/>
+      <c r="AA17" s="11" t="n"/>
+      <c r="AB17" s="15">
         <f>A17&amp;"#"&amp;C17</f>
+        <v/>
+      </c>
+      <c r="AC17" s="15">
+        <f>IF(AND(D17&lt;=TODAY(),N17&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8333,15 +8611,15 @@
         <v>5</v>
       </c>
       <c r="D18" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A18,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A18,Baux!$A:$A,0))*C18)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A18,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A18,Baux!$A:$A,0))*C18)</f>
         <v/>
       </c>
       <c r="E18" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A18,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A18,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F18" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A18,Baux!$A:$A,0)),4))+C18*INDEX(Baux!$N:$N,MATCH($A18,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A18,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A18,Baux!$A:$A,0)),4))+C18*INDEX(Baux!$O:$O,MATCH($A18,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A18,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G18" s="18">
@@ -8349,7 +8627,7 @@
         <v/>
       </c>
       <c r="H18" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A18,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A18,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A18,Baux!$A:$A,0)),4))+(C18-1)*INDEX(Baux!$N:$N,MATCH($A18,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A18,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A18,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A18,Baux!$A:$A,0)),IF(K17="Geler – rattrapage possible",H17,F17))</f>
         <v/>
       </c>
       <c r="I18" s="18">
@@ -8360,55 +8638,66 @@
         <f>IF(OR(G18="",I18=""),"",G18/I18)</f>
         <v/>
       </c>
-      <c r="K18" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A18,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A18,Baux!$A:$A,0)),M17)</f>
-        <v/>
-      </c>
+      <c r="K18" s="11" t="n"/>
       <c r="L18" s="20">
-        <f>IF(OR(J18="",K18=""),"",ROUND(K18*J18,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A18,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A18,Baux!$A:$A,0)),N17)</f>
         <v/>
       </c>
       <c r="M18" s="20">
-        <f>IF(L18="","",IF(INDEX(Baux!$P:$P,MATCH($A18,Baux!$A:$A,0))="",L18,MIN(L18,ROUND(K18*(1+INDEX(Baux!$P:$P,MATCH($A18,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A18,Baux!$A:$A,0))="Base fixe",C18*INDEX(Baux!$N:$N,MATCH($A18,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A18,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J18="",L18=""),"",ROUND(L18*J18,2))</f>
         <v/>
       </c>
       <c r="N18" s="20">
-        <f>M17</f>
-        <v/>
-      </c>
-      <c r="O18" s="21">
-        <f>IF(OR(M18="",N18=""),"",M18/N18-1)</f>
-        <v/>
-      </c>
-      <c r="P18" s="20">
-        <f>IF(M18="","",M18/12)</f>
+        <f>IF(LEFT(K18,5)="Geler",O18,IF(M18="","",IF(INDEX(Baux!$Q:$Q,MATCH($A18,Baux!$A:$A,0))="",M18,MIN(M18,ROUND(L18*(1+INDEX(Baux!$Q:$Q,MATCH($A18,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A18,Baux!$A:$A,0))="Base fixe",C18*INDEX(Baux!$O:$O,MATCH($A18,Baux!$A:$A,0)),VALUE(LEFT(F18,4))-VALUE(LEFT(H18,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O18" s="20">
+        <f>N17</f>
+        <v/>
+      </c>
+      <c r="P18" s="21">
+        <f>IF(OR(N18="",O18=""),"",N18/O18-1)</f>
         <v/>
       </c>
       <c r="Q18" s="20">
-        <f>IF(M18="","",M18/IF(INDEX(Baux!$K:$K,MATCH($A18,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A18,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A18,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N18="","",N18/12)</f>
         <v/>
       </c>
       <c r="R18" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A18,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A18,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A18,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A18,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A18,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N18="","",N18/IF(INDEX(Baux!$L:$L,MATCH($A18,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A18,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A18,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S18" s="20">
-        <f>IF(Q18="","",(Q18+R18)*INDEX(Baux!$J:$J,MATCH($A18,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A18,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A18,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A18,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A18,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A18,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T18" s="20">
-        <f>IF(Q18="","",Q18+R18+S18)</f>
-        <v/>
-      </c>
-      <c r="U18" s="15">
-        <f>IF(G18="",IF(D18&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D18&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V18" s="11" t="n"/>
-      <c r="W18" s="12" t="n"/>
-      <c r="X18" s="11" t="n"/>
-      <c r="Y18" s="15">
+        <f>IF(R18="","",(R18+S18)*INDEX(Baux!$K:$K,MATCH($A18,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U18" s="20">
+        <f>IF(R18="","",R18+S18+T18)</f>
+        <v/>
+      </c>
+      <c r="V18" s="15">
+        <f>IF(LEFT(K18,5)="Geler","❄ Gelée",IF(G18="",IF(D18&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D18&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W18" s="22" t="n"/>
+      <c r="X18" s="11" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Y18" s="12" t="n"/>
+      <c r="Z18" s="12" t="n"/>
+      <c r="AA18" s="11" t="n"/>
+      <c r="AB18" s="15">
         <f>A18&amp;"#"&amp;C18</f>
+        <v/>
+      </c>
+      <c r="AC18" s="15">
+        <f>IF(AND(D18&lt;=TODAY(),N18&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8426,15 +8715,15 @@
         <v>6</v>
       </c>
       <c r="D19" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A19,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A19,Baux!$A:$A,0))*C19)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A19,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A19,Baux!$A:$A,0))*C19)</f>
         <v/>
       </c>
       <c r="E19" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A19,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A19,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F19" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A19,Baux!$A:$A,0)),4))+C19*INDEX(Baux!$N:$N,MATCH($A19,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A19,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A19,Baux!$A:$A,0)),4))+C19*INDEX(Baux!$O:$O,MATCH($A19,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A19,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G19" s="18">
@@ -8442,7 +8731,7 @@
         <v/>
       </c>
       <c r="H19" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A19,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A19,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A19,Baux!$A:$A,0)),4))+(C19-1)*INDEX(Baux!$N:$N,MATCH($A19,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A19,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A19,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A19,Baux!$A:$A,0)),IF(K18="Geler – rattrapage possible",H18,F18))</f>
         <v/>
       </c>
       <c r="I19" s="18">
@@ -8453,55 +8742,70 @@
         <f>IF(OR(G19="",I19=""),"",G19/I19)</f>
         <v/>
       </c>
-      <c r="K19" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A19,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A19,Baux!$A:$A,0)),M18)</f>
-        <v/>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>Geler – rattrapage possible</t>
+        </is>
       </c>
       <c r="L19" s="20">
-        <f>IF(OR(J19="",K19=""),"",ROUND(K19*J19,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A19,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A19,Baux!$A:$A,0)),N18)</f>
         <v/>
       </c>
       <c r="M19" s="20">
-        <f>IF(L19="","",IF(INDEX(Baux!$P:$P,MATCH($A19,Baux!$A:$A,0))="",L19,MIN(L19,ROUND(K19*(1+INDEX(Baux!$P:$P,MATCH($A19,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A19,Baux!$A:$A,0))="Base fixe",C19*INDEX(Baux!$N:$N,MATCH($A19,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A19,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J19="",L19=""),"",ROUND(L19*J19,2))</f>
         <v/>
       </c>
       <c r="N19" s="20">
-        <f>M18</f>
-        <v/>
-      </c>
-      <c r="O19" s="21">
-        <f>IF(OR(M19="",N19=""),"",M19/N19-1)</f>
-        <v/>
-      </c>
-      <c r="P19" s="20">
-        <f>IF(M19="","",M19/12)</f>
+        <f>IF(LEFT(K19,5)="Geler",O19,IF(M19="","",IF(INDEX(Baux!$Q:$Q,MATCH($A19,Baux!$A:$A,0))="",M19,MIN(M19,ROUND(L19*(1+INDEX(Baux!$Q:$Q,MATCH($A19,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A19,Baux!$A:$A,0))="Base fixe",C19*INDEX(Baux!$O:$O,MATCH($A19,Baux!$A:$A,0)),VALUE(LEFT(F19,4))-VALUE(LEFT(H19,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O19" s="20">
+        <f>N18</f>
+        <v/>
+      </c>
+      <c r="P19" s="21">
+        <f>IF(OR(N19="",O19=""),"",N19/O19-1)</f>
         <v/>
       </c>
       <c r="Q19" s="20">
-        <f>IF(M19="","",M19/IF(INDEX(Baux!$K:$K,MATCH($A19,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A19,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A19,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N19="","",N19/12)</f>
         <v/>
       </c>
       <c r="R19" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A19,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A19,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A19,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A19,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A19,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N19="","",N19/IF(INDEX(Baux!$L:$L,MATCH($A19,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A19,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A19,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S19" s="20">
-        <f>IF(Q19="","",(Q19+R19)*INDEX(Baux!$J:$J,MATCH($A19,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A19,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A19,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A19,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A19,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A19,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T19" s="20">
-        <f>IF(Q19="","",Q19+R19+S19)</f>
-        <v/>
-      </c>
-      <c r="U19" s="15">
-        <f>IF(G19="",IF(D19&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D19&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V19" s="11" t="n"/>
-      <c r="W19" s="12" t="n"/>
+        <f>IF(R19="","",(R19+S19)*INDEX(Baux!$K:$K,MATCH($A19,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U19" s="20">
+        <f>IF(R19="","",R19+S19+T19)</f>
+        <v/>
+      </c>
+      <c r="V19" s="15">
+        <f>IF(LEFT(K19,5)="Geler","❄ Gelée",IF(G19="",IF(D19&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D19&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W19" s="22" t="inlineStr">
+        <is>
+          <t>Gel d'un an négocié (avenant du 10/01/2025), rattrapage à la révision 2026 : recalculer sur l'indice 2023-T3.</t>
+        </is>
+      </c>
       <c r="X19" s="11" t="n"/>
-      <c r="Y19" s="15">
+      <c r="Y19" s="12" t="n"/>
+      <c r="Z19" s="12" t="n"/>
+      <c r="AA19" s="11" t="n"/>
+      <c r="AB19" s="15">
         <f>A19&amp;"#"&amp;C19</f>
+        <v/>
+      </c>
+      <c r="AC19" s="15">
+        <f>IF(AND(D19&lt;=TODAY(),N19&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8519,15 +8823,15 @@
         <v>7</v>
       </c>
       <c r="D20" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A20,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A20,Baux!$A:$A,0))*C20)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A20,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A20,Baux!$A:$A,0))*C20)</f>
         <v/>
       </c>
       <c r="E20" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A20,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A20,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F20" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A20,Baux!$A:$A,0)),4))+C20*INDEX(Baux!$N:$N,MATCH($A20,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A20,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A20,Baux!$A:$A,0)),4))+C20*INDEX(Baux!$O:$O,MATCH($A20,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A20,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G20" s="18">
@@ -8535,7 +8839,7 @@
         <v/>
       </c>
       <c r="H20" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A20,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A20,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A20,Baux!$A:$A,0)),4))+(C20-1)*INDEX(Baux!$N:$N,MATCH($A20,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A20,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A20,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A20,Baux!$A:$A,0)),IF(K19="Geler – rattrapage possible",H19,F19))</f>
         <v/>
       </c>
       <c r="I20" s="18">
@@ -8546,55 +8850,66 @@
         <f>IF(OR(G20="",I20=""),"",G20/I20)</f>
         <v/>
       </c>
-      <c r="K20" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A20,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A20,Baux!$A:$A,0)),M19)</f>
-        <v/>
-      </c>
+      <c r="K20" s="11" t="n"/>
       <c r="L20" s="20">
-        <f>IF(OR(J20="",K20=""),"",ROUND(K20*J20,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A20,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A20,Baux!$A:$A,0)),N19)</f>
         <v/>
       </c>
       <c r="M20" s="20">
-        <f>IF(L20="","",IF(INDEX(Baux!$P:$P,MATCH($A20,Baux!$A:$A,0))="",L20,MIN(L20,ROUND(K20*(1+INDEX(Baux!$P:$P,MATCH($A20,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A20,Baux!$A:$A,0))="Base fixe",C20*INDEX(Baux!$N:$N,MATCH($A20,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A20,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J20="",L20=""),"",ROUND(L20*J20,2))</f>
         <v/>
       </c>
       <c r="N20" s="20">
-        <f>M19</f>
-        <v/>
-      </c>
-      <c r="O20" s="21">
-        <f>IF(OR(M20="",N20=""),"",M20/N20-1)</f>
-        <v/>
-      </c>
-      <c r="P20" s="20">
-        <f>IF(M20="","",M20/12)</f>
+        <f>IF(LEFT(K20,5)="Geler",O20,IF(M20="","",IF(INDEX(Baux!$Q:$Q,MATCH($A20,Baux!$A:$A,0))="",M20,MIN(M20,ROUND(L20*(1+INDEX(Baux!$Q:$Q,MATCH($A20,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A20,Baux!$A:$A,0))="Base fixe",C20*INDEX(Baux!$O:$O,MATCH($A20,Baux!$A:$A,0)),VALUE(LEFT(F20,4))-VALUE(LEFT(H20,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O20" s="20">
+        <f>N19</f>
+        <v/>
+      </c>
+      <c r="P20" s="21">
+        <f>IF(OR(N20="",O20=""),"",N20/O20-1)</f>
         <v/>
       </c>
       <c r="Q20" s="20">
-        <f>IF(M20="","",M20/IF(INDEX(Baux!$K:$K,MATCH($A20,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A20,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A20,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N20="","",N20/12)</f>
         <v/>
       </c>
       <c r="R20" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A20,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A20,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A20,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A20,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A20,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N20="","",N20/IF(INDEX(Baux!$L:$L,MATCH($A20,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A20,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A20,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S20" s="20">
-        <f>IF(Q20="","",(Q20+R20)*INDEX(Baux!$J:$J,MATCH($A20,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A20,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A20,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A20,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A20,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A20,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T20" s="20">
-        <f>IF(Q20="","",Q20+R20+S20)</f>
-        <v/>
-      </c>
-      <c r="U20" s="15">
-        <f>IF(G20="",IF(D20&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D20&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V20" s="11" t="n"/>
-      <c r="W20" s="12" t="n"/>
+        <f>IF(R20="","",(R20+S20)*INDEX(Baux!$K:$K,MATCH($A20,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U20" s="20">
+        <f>IF(R20="","",R20+S20+T20)</f>
+        <v/>
+      </c>
+      <c r="V20" s="15">
+        <f>IF(LEFT(K20,5)="Geler","❄ Gelée",IF(G20="",IF(D20&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D20&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W20" s="22" t="inlineStr">
+        <is>
+          <t>Appliquer le rattrapage : coefficient calculé sur 2 ans d'indice. Prévenir le locataire avant facturation.</t>
+        </is>
+      </c>
       <c r="X20" s="11" t="n"/>
-      <c r="Y20" s="15">
+      <c r="Y20" s="12" t="n"/>
+      <c r="Z20" s="12" t="n"/>
+      <c r="AA20" s="11" t="n"/>
+      <c r="AB20" s="15">
         <f>A20&amp;"#"&amp;C20</f>
+        <v/>
+      </c>
+      <c r="AC20" s="15">
+        <f>IF(AND(D20&lt;=TODAY(),N20&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8612,15 +8927,15 @@
         <v>8</v>
       </c>
       <c r="D21" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A21,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A21,Baux!$A:$A,0))*C21)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A21,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A21,Baux!$A:$A,0))*C21)</f>
         <v/>
       </c>
       <c r="E21" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A21,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A21,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F21" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A21,Baux!$A:$A,0)),4))+C21*INDEX(Baux!$N:$N,MATCH($A21,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A21,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A21,Baux!$A:$A,0)),4))+C21*INDEX(Baux!$O:$O,MATCH($A21,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A21,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G21" s="18">
@@ -8628,7 +8943,7 @@
         <v/>
       </c>
       <c r="H21" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A21,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A21,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A21,Baux!$A:$A,0)),4))+(C21-1)*INDEX(Baux!$N:$N,MATCH($A21,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A21,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A21,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A21,Baux!$A:$A,0)),IF(K20="Geler – rattrapage possible",H20,F20))</f>
         <v/>
       </c>
       <c r="I21" s="18">
@@ -8639,55 +8954,62 @@
         <f>IF(OR(G21="",I21=""),"",G21/I21)</f>
         <v/>
       </c>
-      <c r="K21" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A21,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A21,Baux!$A:$A,0)),M20)</f>
-        <v/>
-      </c>
+      <c r="K21" s="11" t="n"/>
       <c r="L21" s="20">
-        <f>IF(OR(J21="",K21=""),"",ROUND(K21*J21,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A21,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A21,Baux!$A:$A,0)),N20)</f>
         <v/>
       </c>
       <c r="M21" s="20">
-        <f>IF(L21="","",IF(INDEX(Baux!$P:$P,MATCH($A21,Baux!$A:$A,0))="",L21,MIN(L21,ROUND(K21*(1+INDEX(Baux!$P:$P,MATCH($A21,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A21,Baux!$A:$A,0))="Base fixe",C21*INDEX(Baux!$N:$N,MATCH($A21,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A21,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J21="",L21=""),"",ROUND(L21*J21,2))</f>
         <v/>
       </c>
       <c r="N21" s="20">
-        <f>M20</f>
-        <v/>
-      </c>
-      <c r="O21" s="21">
-        <f>IF(OR(M21="",N21=""),"",M21/N21-1)</f>
-        <v/>
-      </c>
-      <c r="P21" s="20">
-        <f>IF(M21="","",M21/12)</f>
+        <f>IF(LEFT(K21,5)="Geler",O21,IF(M21="","",IF(INDEX(Baux!$Q:$Q,MATCH($A21,Baux!$A:$A,0))="",M21,MIN(M21,ROUND(L21*(1+INDEX(Baux!$Q:$Q,MATCH($A21,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A21,Baux!$A:$A,0))="Base fixe",C21*INDEX(Baux!$O:$O,MATCH($A21,Baux!$A:$A,0)),VALUE(LEFT(F21,4))-VALUE(LEFT(H21,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O21" s="20">
+        <f>N20</f>
+        <v/>
+      </c>
+      <c r="P21" s="21">
+        <f>IF(OR(N21="",O21=""),"",N21/O21-1)</f>
         <v/>
       </c>
       <c r="Q21" s="20">
-        <f>IF(M21="","",M21/IF(INDEX(Baux!$K:$K,MATCH($A21,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A21,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A21,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N21="","",N21/12)</f>
         <v/>
       </c>
       <c r="R21" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A21,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A21,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A21,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A21,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A21,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N21="","",N21/IF(INDEX(Baux!$L:$L,MATCH($A21,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A21,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A21,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S21" s="20">
-        <f>IF(Q21="","",(Q21+R21)*INDEX(Baux!$J:$J,MATCH($A21,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A21,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A21,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A21,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A21,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A21,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T21" s="20">
-        <f>IF(Q21="","",Q21+R21+S21)</f>
-        <v/>
-      </c>
-      <c r="U21" s="15">
-        <f>IF(G21="",IF(D21&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D21&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V21" s="11" t="n"/>
-      <c r="W21" s="12" t="n"/>
+        <f>IF(R21="","",(R21+S21)*INDEX(Baux!$K:$K,MATCH($A21,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U21" s="20">
+        <f>IF(R21="","",R21+S21+T21)</f>
+        <v/>
+      </c>
+      <c r="V21" s="15">
+        <f>IF(LEFT(K21,5)="Geler","❄ Gelée",IF(G21="",IF(D21&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D21&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W21" s="22" t="n"/>
       <c r="X21" s="11" t="n"/>
-      <c r="Y21" s="15">
+      <c r="Y21" s="12" t="n"/>
+      <c r="Z21" s="12" t="n"/>
+      <c r="AA21" s="11" t="n"/>
+      <c r="AB21" s="15">
         <f>A21&amp;"#"&amp;C21</f>
+        <v/>
+      </c>
+      <c r="AC21" s="15">
+        <f>IF(AND(D21&lt;=TODAY(),N21&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8705,15 +9027,15 @@
         <v>9</v>
       </c>
       <c r="D22" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A22,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A22,Baux!$A:$A,0))*C22)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A22,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A22,Baux!$A:$A,0))*C22)</f>
         <v/>
       </c>
       <c r="E22" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A22,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A22,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F22" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A22,Baux!$A:$A,0)),4))+C22*INDEX(Baux!$N:$N,MATCH($A22,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A22,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A22,Baux!$A:$A,0)),4))+C22*INDEX(Baux!$O:$O,MATCH($A22,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A22,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G22" s="18">
@@ -8721,7 +9043,7 @@
         <v/>
       </c>
       <c r="H22" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A22,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A22,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A22,Baux!$A:$A,0)),4))+(C22-1)*INDEX(Baux!$N:$N,MATCH($A22,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A22,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A22,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A22,Baux!$A:$A,0)),IF(K21="Geler – rattrapage possible",H21,F21))</f>
         <v/>
       </c>
       <c r="I22" s="18">
@@ -8732,55 +9054,62 @@
         <f>IF(OR(G22="",I22=""),"",G22/I22)</f>
         <v/>
       </c>
-      <c r="K22" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A22,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A22,Baux!$A:$A,0)),M21)</f>
-        <v/>
-      </c>
+      <c r="K22" s="11" t="n"/>
       <c r="L22" s="20">
-        <f>IF(OR(J22="",K22=""),"",ROUND(K22*J22,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A22,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A22,Baux!$A:$A,0)),N21)</f>
         <v/>
       </c>
       <c r="M22" s="20">
-        <f>IF(L22="","",IF(INDEX(Baux!$P:$P,MATCH($A22,Baux!$A:$A,0))="",L22,MIN(L22,ROUND(K22*(1+INDEX(Baux!$P:$P,MATCH($A22,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A22,Baux!$A:$A,0))="Base fixe",C22*INDEX(Baux!$N:$N,MATCH($A22,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A22,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J22="",L22=""),"",ROUND(L22*J22,2))</f>
         <v/>
       </c>
       <c r="N22" s="20">
-        <f>M21</f>
-        <v/>
-      </c>
-      <c r="O22" s="21">
-        <f>IF(OR(M22="",N22=""),"",M22/N22-1)</f>
-        <v/>
-      </c>
-      <c r="P22" s="20">
-        <f>IF(M22="","",M22/12)</f>
+        <f>IF(LEFT(K22,5)="Geler",O22,IF(M22="","",IF(INDEX(Baux!$Q:$Q,MATCH($A22,Baux!$A:$A,0))="",M22,MIN(M22,ROUND(L22*(1+INDEX(Baux!$Q:$Q,MATCH($A22,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A22,Baux!$A:$A,0))="Base fixe",C22*INDEX(Baux!$O:$O,MATCH($A22,Baux!$A:$A,0)),VALUE(LEFT(F22,4))-VALUE(LEFT(H22,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O22" s="20">
+        <f>N21</f>
+        <v/>
+      </c>
+      <c r="P22" s="21">
+        <f>IF(OR(N22="",O22=""),"",N22/O22-1)</f>
         <v/>
       </c>
       <c r="Q22" s="20">
-        <f>IF(M22="","",M22/IF(INDEX(Baux!$K:$K,MATCH($A22,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A22,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A22,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N22="","",N22/12)</f>
         <v/>
       </c>
       <c r="R22" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A22,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A22,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A22,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A22,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A22,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N22="","",N22/IF(INDEX(Baux!$L:$L,MATCH($A22,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A22,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A22,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S22" s="20">
-        <f>IF(Q22="","",(Q22+R22)*INDEX(Baux!$J:$J,MATCH($A22,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A22,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A22,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A22,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A22,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A22,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T22" s="20">
-        <f>IF(Q22="","",Q22+R22+S22)</f>
-        <v/>
-      </c>
-      <c r="U22" s="15">
-        <f>IF(G22="",IF(D22&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D22&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V22" s="11" t="n"/>
-      <c r="W22" s="12" t="n"/>
+        <f>IF(R22="","",(R22+S22)*INDEX(Baux!$K:$K,MATCH($A22,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U22" s="20">
+        <f>IF(R22="","",R22+S22+T22)</f>
+        <v/>
+      </c>
+      <c r="V22" s="15">
+        <f>IF(LEFT(K22,5)="Geler","❄ Gelée",IF(G22="",IF(D22&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D22&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W22" s="22" t="n"/>
       <c r="X22" s="11" t="n"/>
-      <c r="Y22" s="15">
+      <c r="Y22" s="12" t="n"/>
+      <c r="Z22" s="12" t="n"/>
+      <c r="AA22" s="11" t="n"/>
+      <c r="AB22" s="15">
         <f>A22&amp;"#"&amp;C22</f>
+        <v/>
+      </c>
+      <c r="AC22" s="15">
+        <f>IF(AND(D22&lt;=TODAY(),N22&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8798,15 +9127,15 @@
         <v>1</v>
       </c>
       <c r="D23" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A23,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A23,Baux!$A:$A,0))*C23)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A23,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A23,Baux!$A:$A,0))*C23)</f>
         <v/>
       </c>
       <c r="E23" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A23,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A23,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F23" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A23,Baux!$A:$A,0)),4))+C23*INDEX(Baux!$N:$N,MATCH($A23,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A23,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A23,Baux!$A:$A,0)),4))+C23*INDEX(Baux!$O:$O,MATCH($A23,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A23,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G23" s="18">
@@ -8814,7 +9143,7 @@
         <v/>
       </c>
       <c r="H23" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A23,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A23,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A23,Baux!$A:$A,0)),4))+(C23-1)*INDEX(Baux!$N:$N,MATCH($A23,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A23,Baux!$A:$A,0)),3))</f>
+        <f>INDEX(Baux!$N:$N,MATCH($A23,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="I23" s="18">
@@ -8825,55 +9154,62 @@
         <f>IF(OR(G23="",I23=""),"",G23/I23)</f>
         <v/>
       </c>
-      <c r="K23" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A23,Baux!$A:$A,0))</f>
-        <v/>
-      </c>
+      <c r="K23" s="11" t="n"/>
       <c r="L23" s="20">
-        <f>IF(OR(J23="",K23=""),"",ROUND(K23*J23,2))</f>
+        <f>INDEX(Baux!$I:$I,MATCH($A23,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="M23" s="20">
-        <f>IF(L23="","",IF(INDEX(Baux!$P:$P,MATCH($A23,Baux!$A:$A,0))="",L23,MIN(L23,ROUND(K23*(1+INDEX(Baux!$P:$P,MATCH($A23,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A23,Baux!$A:$A,0))="Base fixe",C23*INDEX(Baux!$N:$N,MATCH($A23,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A23,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J23="",L23=""),"",ROUND(L23*J23,2))</f>
         <v/>
       </c>
       <c r="N23" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A23,Baux!$A:$A,0))</f>
-        <v/>
-      </c>
-      <c r="O23" s="21">
-        <f>IF(OR(M23="",N23=""),"",M23/N23-1)</f>
-        <v/>
-      </c>
-      <c r="P23" s="20">
-        <f>IF(M23="","",M23/12)</f>
+        <f>IF(LEFT(K23,5)="Geler",O23,IF(M23="","",IF(INDEX(Baux!$Q:$Q,MATCH($A23,Baux!$A:$A,0))="",M23,MIN(M23,ROUND(L23*(1+INDEX(Baux!$Q:$Q,MATCH($A23,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A23,Baux!$A:$A,0))="Base fixe",C23*INDEX(Baux!$O:$O,MATCH($A23,Baux!$A:$A,0)),VALUE(LEFT(F23,4))-VALUE(LEFT(H23,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O23" s="20">
+        <f>INDEX(Baux!$I:$I,MATCH($A23,Baux!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="P23" s="21">
+        <f>IF(OR(N23="",O23=""),"",N23/O23-1)</f>
         <v/>
       </c>
       <c r="Q23" s="20">
-        <f>IF(M23="","",M23/IF(INDEX(Baux!$K:$K,MATCH($A23,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A23,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A23,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N23="","",N23/12)</f>
         <v/>
       </c>
       <c r="R23" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A23,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A23,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A23,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A23,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A23,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N23="","",N23/IF(INDEX(Baux!$L:$L,MATCH($A23,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A23,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A23,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S23" s="20">
-        <f>IF(Q23="","",(Q23+R23)*INDEX(Baux!$J:$J,MATCH($A23,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A23,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A23,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A23,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A23,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A23,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T23" s="20">
-        <f>IF(Q23="","",Q23+R23+S23)</f>
-        <v/>
-      </c>
-      <c r="U23" s="15">
-        <f>IF(G23="",IF(D23&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D23&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V23" s="11" t="n"/>
-      <c r="W23" s="12" t="n"/>
+        <f>IF(R23="","",(R23+S23)*INDEX(Baux!$K:$K,MATCH($A23,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U23" s="20">
+        <f>IF(R23="","",R23+S23+T23)</f>
+        <v/>
+      </c>
+      <c r="V23" s="15">
+        <f>IF(LEFT(K23,5)="Geler","❄ Gelée",IF(G23="",IF(D23&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D23&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W23" s="22" t="n"/>
       <c r="X23" s="11" t="n"/>
-      <c r="Y23" s="15">
+      <c r="Y23" s="12" t="n"/>
+      <c r="Z23" s="12" t="n"/>
+      <c r="AA23" s="11" t="n"/>
+      <c r="AB23" s="15">
         <f>A23&amp;"#"&amp;C23</f>
+        <v/>
+      </c>
+      <c r="AC23" s="15">
+        <f>IF(AND(D23&lt;=TODAY(),N23&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8891,15 +9227,15 @@
         <v>2</v>
       </c>
       <c r="D24" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A24,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A24,Baux!$A:$A,0))*C24)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A24,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A24,Baux!$A:$A,0))*C24)</f>
         <v/>
       </c>
       <c r="E24" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A24,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A24,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F24" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A24,Baux!$A:$A,0)),4))+C24*INDEX(Baux!$N:$N,MATCH($A24,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A24,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A24,Baux!$A:$A,0)),4))+C24*INDEX(Baux!$O:$O,MATCH($A24,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A24,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G24" s="18">
@@ -8907,7 +9243,7 @@
         <v/>
       </c>
       <c r="H24" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A24,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A24,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A24,Baux!$A:$A,0)),4))+(C24-1)*INDEX(Baux!$N:$N,MATCH($A24,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A24,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A24,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A24,Baux!$A:$A,0)),IF(K23="Geler – rattrapage possible",H23,F23))</f>
         <v/>
       </c>
       <c r="I24" s="18">
@@ -8918,55 +9254,62 @@
         <f>IF(OR(G24="",I24=""),"",G24/I24)</f>
         <v/>
       </c>
-      <c r="K24" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A24,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A24,Baux!$A:$A,0)),M23)</f>
-        <v/>
-      </c>
+      <c r="K24" s="11" t="n"/>
       <c r="L24" s="20">
-        <f>IF(OR(J24="",K24=""),"",ROUND(K24*J24,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A24,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A24,Baux!$A:$A,0)),N23)</f>
         <v/>
       </c>
       <c r="M24" s="20">
-        <f>IF(L24="","",IF(INDEX(Baux!$P:$P,MATCH($A24,Baux!$A:$A,0))="",L24,MIN(L24,ROUND(K24*(1+INDEX(Baux!$P:$P,MATCH($A24,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A24,Baux!$A:$A,0))="Base fixe",C24*INDEX(Baux!$N:$N,MATCH($A24,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A24,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J24="",L24=""),"",ROUND(L24*J24,2))</f>
         <v/>
       </c>
       <c r="N24" s="20">
-        <f>M23</f>
-        <v/>
-      </c>
-      <c r="O24" s="21">
-        <f>IF(OR(M24="",N24=""),"",M24/N24-1)</f>
-        <v/>
-      </c>
-      <c r="P24" s="20">
-        <f>IF(M24="","",M24/12)</f>
+        <f>IF(LEFT(K24,5)="Geler",O24,IF(M24="","",IF(INDEX(Baux!$Q:$Q,MATCH($A24,Baux!$A:$A,0))="",M24,MIN(M24,ROUND(L24*(1+INDEX(Baux!$Q:$Q,MATCH($A24,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A24,Baux!$A:$A,0))="Base fixe",C24*INDEX(Baux!$O:$O,MATCH($A24,Baux!$A:$A,0)),VALUE(LEFT(F24,4))-VALUE(LEFT(H24,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O24" s="20">
+        <f>N23</f>
+        <v/>
+      </c>
+      <c r="P24" s="21">
+        <f>IF(OR(N24="",O24=""),"",N24/O24-1)</f>
         <v/>
       </c>
       <c r="Q24" s="20">
-        <f>IF(M24="","",M24/IF(INDEX(Baux!$K:$K,MATCH($A24,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A24,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A24,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N24="","",N24/12)</f>
         <v/>
       </c>
       <c r="R24" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A24,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A24,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A24,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A24,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A24,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N24="","",N24/IF(INDEX(Baux!$L:$L,MATCH($A24,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A24,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A24,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S24" s="20">
-        <f>IF(Q24="","",(Q24+R24)*INDEX(Baux!$J:$J,MATCH($A24,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A24,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A24,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A24,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A24,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A24,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T24" s="20">
-        <f>IF(Q24="","",Q24+R24+S24)</f>
-        <v/>
-      </c>
-      <c r="U24" s="15">
-        <f>IF(G24="",IF(D24&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D24&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V24" s="11" t="n"/>
-      <c r="W24" s="12" t="n"/>
+        <f>IF(R24="","",(R24+S24)*INDEX(Baux!$K:$K,MATCH($A24,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U24" s="20">
+        <f>IF(R24="","",R24+S24+T24)</f>
+        <v/>
+      </c>
+      <c r="V24" s="15">
+        <f>IF(LEFT(K24,5)="Geler","❄ Gelée",IF(G24="",IF(D24&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D24&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W24" s="22" t="n"/>
       <c r="X24" s="11" t="n"/>
-      <c r="Y24" s="15">
+      <c r="Y24" s="12" t="n"/>
+      <c r="Z24" s="12" t="n"/>
+      <c r="AA24" s="11" t="n"/>
+      <c r="AB24" s="15">
         <f>A24&amp;"#"&amp;C24</f>
+        <v/>
+      </c>
+      <c r="AC24" s="15">
+        <f>IF(AND(D24&lt;=TODAY(),N24&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -8984,15 +9327,15 @@
         <v>3</v>
       </c>
       <c r="D25" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A25,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A25,Baux!$A:$A,0))*C25)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A25,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A25,Baux!$A:$A,0))*C25)</f>
         <v/>
       </c>
       <c r="E25" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A25,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A25,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F25" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A25,Baux!$A:$A,0)),4))+C25*INDEX(Baux!$N:$N,MATCH($A25,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A25,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A25,Baux!$A:$A,0)),4))+C25*INDEX(Baux!$O:$O,MATCH($A25,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A25,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G25" s="18">
@@ -9000,7 +9343,7 @@
         <v/>
       </c>
       <c r="H25" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A25,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A25,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A25,Baux!$A:$A,0)),4))+(C25-1)*INDEX(Baux!$N:$N,MATCH($A25,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A25,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A25,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A25,Baux!$A:$A,0)),IF(K24="Geler – rattrapage possible",H24,F24))</f>
         <v/>
       </c>
       <c r="I25" s="18">
@@ -9011,55 +9354,62 @@
         <f>IF(OR(G25="",I25=""),"",G25/I25)</f>
         <v/>
       </c>
-      <c r="K25" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A25,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A25,Baux!$A:$A,0)),M24)</f>
-        <v/>
-      </c>
+      <c r="K25" s="11" t="n"/>
       <c r="L25" s="20">
-        <f>IF(OR(J25="",K25=""),"",ROUND(K25*J25,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A25,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A25,Baux!$A:$A,0)),N24)</f>
         <v/>
       </c>
       <c r="M25" s="20">
-        <f>IF(L25="","",IF(INDEX(Baux!$P:$P,MATCH($A25,Baux!$A:$A,0))="",L25,MIN(L25,ROUND(K25*(1+INDEX(Baux!$P:$P,MATCH($A25,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A25,Baux!$A:$A,0))="Base fixe",C25*INDEX(Baux!$N:$N,MATCH($A25,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A25,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J25="",L25=""),"",ROUND(L25*J25,2))</f>
         <v/>
       </c>
       <c r="N25" s="20">
-        <f>M24</f>
-        <v/>
-      </c>
-      <c r="O25" s="21">
-        <f>IF(OR(M25="",N25=""),"",M25/N25-1)</f>
-        <v/>
-      </c>
-      <c r="P25" s="20">
-        <f>IF(M25="","",M25/12)</f>
+        <f>IF(LEFT(K25,5)="Geler",O25,IF(M25="","",IF(INDEX(Baux!$Q:$Q,MATCH($A25,Baux!$A:$A,0))="",M25,MIN(M25,ROUND(L25*(1+INDEX(Baux!$Q:$Q,MATCH($A25,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A25,Baux!$A:$A,0))="Base fixe",C25*INDEX(Baux!$O:$O,MATCH($A25,Baux!$A:$A,0)),VALUE(LEFT(F25,4))-VALUE(LEFT(H25,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O25" s="20">
+        <f>N24</f>
+        <v/>
+      </c>
+      <c r="P25" s="21">
+        <f>IF(OR(N25="",O25=""),"",N25/O25-1)</f>
         <v/>
       </c>
       <c r="Q25" s="20">
-        <f>IF(M25="","",M25/IF(INDEX(Baux!$K:$K,MATCH($A25,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A25,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A25,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N25="","",N25/12)</f>
         <v/>
       </c>
       <c r="R25" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A25,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A25,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A25,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A25,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A25,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N25="","",N25/IF(INDEX(Baux!$L:$L,MATCH($A25,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A25,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A25,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S25" s="20">
-        <f>IF(Q25="","",(Q25+R25)*INDEX(Baux!$J:$J,MATCH($A25,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A25,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A25,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A25,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A25,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A25,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T25" s="20">
-        <f>IF(Q25="","",Q25+R25+S25)</f>
-        <v/>
-      </c>
-      <c r="U25" s="15">
-        <f>IF(G25="",IF(D25&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D25&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V25" s="11" t="n"/>
-      <c r="W25" s="12" t="n"/>
+        <f>IF(R25="","",(R25+S25)*INDEX(Baux!$K:$K,MATCH($A25,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U25" s="20">
+        <f>IF(R25="","",R25+S25+T25)</f>
+        <v/>
+      </c>
+      <c r="V25" s="15">
+        <f>IF(LEFT(K25,5)="Geler","❄ Gelée",IF(G25="",IF(D25&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D25&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W25" s="22" t="n"/>
       <c r="X25" s="11" t="n"/>
-      <c r="Y25" s="15">
+      <c r="Y25" s="12" t="n"/>
+      <c r="Z25" s="12" t="n"/>
+      <c r="AA25" s="11" t="n"/>
+      <c r="AB25" s="15">
         <f>A25&amp;"#"&amp;C25</f>
+        <v/>
+      </c>
+      <c r="AC25" s="15">
+        <f>IF(AND(D25&lt;=TODAY(),N25&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -9077,15 +9427,15 @@
         <v>4</v>
       </c>
       <c r="D26" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A26,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A26,Baux!$A:$A,0))*C26)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A26,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A26,Baux!$A:$A,0))*C26)</f>
         <v/>
       </c>
       <c r="E26" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A26,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A26,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F26" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A26,Baux!$A:$A,0)),4))+C26*INDEX(Baux!$N:$N,MATCH($A26,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A26,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A26,Baux!$A:$A,0)),4))+C26*INDEX(Baux!$O:$O,MATCH($A26,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A26,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G26" s="18">
@@ -9093,7 +9443,7 @@
         <v/>
       </c>
       <c r="H26" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A26,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A26,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A26,Baux!$A:$A,0)),4))+(C26-1)*INDEX(Baux!$N:$N,MATCH($A26,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A26,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A26,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A26,Baux!$A:$A,0)),IF(K25="Geler – rattrapage possible",H25,F25))</f>
         <v/>
       </c>
       <c r="I26" s="18">
@@ -9104,55 +9454,62 @@
         <f>IF(OR(G26="",I26=""),"",G26/I26)</f>
         <v/>
       </c>
-      <c r="K26" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A26,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A26,Baux!$A:$A,0)),M25)</f>
-        <v/>
-      </c>
+      <c r="K26" s="11" t="n"/>
       <c r="L26" s="20">
-        <f>IF(OR(J26="",K26=""),"",ROUND(K26*J26,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A26,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A26,Baux!$A:$A,0)),N25)</f>
         <v/>
       </c>
       <c r="M26" s="20">
-        <f>IF(L26="","",IF(INDEX(Baux!$P:$P,MATCH($A26,Baux!$A:$A,0))="",L26,MIN(L26,ROUND(K26*(1+INDEX(Baux!$P:$P,MATCH($A26,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A26,Baux!$A:$A,0))="Base fixe",C26*INDEX(Baux!$N:$N,MATCH($A26,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A26,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J26="",L26=""),"",ROUND(L26*J26,2))</f>
         <v/>
       </c>
       <c r="N26" s="20">
-        <f>M25</f>
-        <v/>
-      </c>
-      <c r="O26" s="21">
-        <f>IF(OR(M26="",N26=""),"",M26/N26-1)</f>
-        <v/>
-      </c>
-      <c r="P26" s="20">
-        <f>IF(M26="","",M26/12)</f>
+        <f>IF(LEFT(K26,5)="Geler",O26,IF(M26="","",IF(INDEX(Baux!$Q:$Q,MATCH($A26,Baux!$A:$A,0))="",M26,MIN(M26,ROUND(L26*(1+INDEX(Baux!$Q:$Q,MATCH($A26,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A26,Baux!$A:$A,0))="Base fixe",C26*INDEX(Baux!$O:$O,MATCH($A26,Baux!$A:$A,0)),VALUE(LEFT(F26,4))-VALUE(LEFT(H26,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O26" s="20">
+        <f>N25</f>
+        <v/>
+      </c>
+      <c r="P26" s="21">
+        <f>IF(OR(N26="",O26=""),"",N26/O26-1)</f>
         <v/>
       </c>
       <c r="Q26" s="20">
-        <f>IF(M26="","",M26/IF(INDEX(Baux!$K:$K,MATCH($A26,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A26,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A26,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N26="","",N26/12)</f>
         <v/>
       </c>
       <c r="R26" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A26,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A26,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A26,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A26,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A26,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N26="","",N26/IF(INDEX(Baux!$L:$L,MATCH($A26,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A26,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A26,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S26" s="20">
-        <f>IF(Q26="","",(Q26+R26)*INDEX(Baux!$J:$J,MATCH($A26,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A26,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A26,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A26,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A26,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A26,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T26" s="20">
-        <f>IF(Q26="","",Q26+R26+S26)</f>
-        <v/>
-      </c>
-      <c r="U26" s="15">
-        <f>IF(G26="",IF(D26&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D26&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V26" s="11" t="n"/>
-      <c r="W26" s="12" t="n"/>
+        <f>IF(R26="","",(R26+S26)*INDEX(Baux!$K:$K,MATCH($A26,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U26" s="20">
+        <f>IF(R26="","",R26+S26+T26)</f>
+        <v/>
+      </c>
+      <c r="V26" s="15">
+        <f>IF(LEFT(K26,5)="Geler","❄ Gelée",IF(G26="",IF(D26&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D26&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W26" s="22" t="n"/>
       <c r="X26" s="11" t="n"/>
-      <c r="Y26" s="15">
+      <c r="Y26" s="12" t="n"/>
+      <c r="Z26" s="12" t="n"/>
+      <c r="AA26" s="11" t="n"/>
+      <c r="AB26" s="15">
         <f>A26&amp;"#"&amp;C26</f>
+        <v/>
+      </c>
+      <c r="AC26" s="15">
+        <f>IF(AND(D26&lt;=TODAY(),N26&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -9170,15 +9527,15 @@
         <v>5</v>
       </c>
       <c r="D27" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A27,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A27,Baux!$A:$A,0))*C27)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A27,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A27,Baux!$A:$A,0))*C27)</f>
         <v/>
       </c>
       <c r="E27" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A27,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A27,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F27" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A27,Baux!$A:$A,0)),4))+C27*INDEX(Baux!$N:$N,MATCH($A27,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A27,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A27,Baux!$A:$A,0)),4))+C27*INDEX(Baux!$O:$O,MATCH($A27,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A27,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G27" s="18">
@@ -9186,7 +9543,7 @@
         <v/>
       </c>
       <c r="H27" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A27,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A27,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A27,Baux!$A:$A,0)),4))+(C27-1)*INDEX(Baux!$N:$N,MATCH($A27,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A27,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A27,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A27,Baux!$A:$A,0)),IF(K26="Geler – rattrapage possible",H26,F26))</f>
         <v/>
       </c>
       <c r="I27" s="18">
@@ -9197,55 +9554,62 @@
         <f>IF(OR(G27="",I27=""),"",G27/I27)</f>
         <v/>
       </c>
-      <c r="K27" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A27,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A27,Baux!$A:$A,0)),M26)</f>
-        <v/>
-      </c>
+      <c r="K27" s="11" t="n"/>
       <c r="L27" s="20">
-        <f>IF(OR(J27="",K27=""),"",ROUND(K27*J27,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A27,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A27,Baux!$A:$A,0)),N26)</f>
         <v/>
       </c>
       <c r="M27" s="20">
-        <f>IF(L27="","",IF(INDEX(Baux!$P:$P,MATCH($A27,Baux!$A:$A,0))="",L27,MIN(L27,ROUND(K27*(1+INDEX(Baux!$P:$P,MATCH($A27,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A27,Baux!$A:$A,0))="Base fixe",C27*INDEX(Baux!$N:$N,MATCH($A27,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A27,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J27="",L27=""),"",ROUND(L27*J27,2))</f>
         <v/>
       </c>
       <c r="N27" s="20">
-        <f>M26</f>
-        <v/>
-      </c>
-      <c r="O27" s="21">
-        <f>IF(OR(M27="",N27=""),"",M27/N27-1)</f>
-        <v/>
-      </c>
-      <c r="P27" s="20">
-        <f>IF(M27="","",M27/12)</f>
+        <f>IF(LEFT(K27,5)="Geler",O27,IF(M27="","",IF(INDEX(Baux!$Q:$Q,MATCH($A27,Baux!$A:$A,0))="",M27,MIN(M27,ROUND(L27*(1+INDEX(Baux!$Q:$Q,MATCH($A27,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A27,Baux!$A:$A,0))="Base fixe",C27*INDEX(Baux!$O:$O,MATCH($A27,Baux!$A:$A,0)),VALUE(LEFT(F27,4))-VALUE(LEFT(H27,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O27" s="20">
+        <f>N26</f>
+        <v/>
+      </c>
+      <c r="P27" s="21">
+        <f>IF(OR(N27="",O27=""),"",N27/O27-1)</f>
         <v/>
       </c>
       <c r="Q27" s="20">
-        <f>IF(M27="","",M27/IF(INDEX(Baux!$K:$K,MATCH($A27,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A27,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A27,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N27="","",N27/12)</f>
         <v/>
       </c>
       <c r="R27" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A27,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A27,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A27,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A27,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A27,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N27="","",N27/IF(INDEX(Baux!$L:$L,MATCH($A27,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A27,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A27,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S27" s="20">
-        <f>IF(Q27="","",(Q27+R27)*INDEX(Baux!$J:$J,MATCH($A27,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A27,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A27,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A27,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A27,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A27,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T27" s="20">
-        <f>IF(Q27="","",Q27+R27+S27)</f>
-        <v/>
-      </c>
-      <c r="U27" s="15">
-        <f>IF(G27="",IF(D27&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D27&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V27" s="11" t="n"/>
-      <c r="W27" s="12" t="n"/>
+        <f>IF(R27="","",(R27+S27)*INDEX(Baux!$K:$K,MATCH($A27,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U27" s="20">
+        <f>IF(R27="","",R27+S27+T27)</f>
+        <v/>
+      </c>
+      <c r="V27" s="15">
+        <f>IF(LEFT(K27,5)="Geler","❄ Gelée",IF(G27="",IF(D27&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D27&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W27" s="22" t="n"/>
       <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="15">
+      <c r="Y27" s="12" t="n"/>
+      <c r="Z27" s="12" t="n"/>
+      <c r="AA27" s="11" t="n"/>
+      <c r="AB27" s="15">
         <f>A27&amp;"#"&amp;C27</f>
+        <v/>
+      </c>
+      <c r="AC27" s="15">
+        <f>IF(AND(D27&lt;=TODAY(),N27&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -9263,15 +9627,15 @@
         <v>6</v>
       </c>
       <c r="D28" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A28,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A28,Baux!$A:$A,0))*C28)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A28,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A28,Baux!$A:$A,0))*C28)</f>
         <v/>
       </c>
       <c r="E28" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A28,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A28,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F28" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A28,Baux!$A:$A,0)),4))+C28*INDEX(Baux!$N:$N,MATCH($A28,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A28,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A28,Baux!$A:$A,0)),4))+C28*INDEX(Baux!$O:$O,MATCH($A28,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A28,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G28" s="18">
@@ -9279,7 +9643,7 @@
         <v/>
       </c>
       <c r="H28" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A28,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A28,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A28,Baux!$A:$A,0)),4))+(C28-1)*INDEX(Baux!$N:$N,MATCH($A28,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A28,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A28,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A28,Baux!$A:$A,0)),IF(K27="Geler – rattrapage possible",H27,F27))</f>
         <v/>
       </c>
       <c r="I28" s="18">
@@ -9290,55 +9654,62 @@
         <f>IF(OR(G28="",I28=""),"",G28/I28)</f>
         <v/>
       </c>
-      <c r="K28" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A28,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A28,Baux!$A:$A,0)),M27)</f>
-        <v/>
-      </c>
+      <c r="K28" s="11" t="n"/>
       <c r="L28" s="20">
-        <f>IF(OR(J28="",K28=""),"",ROUND(K28*J28,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A28,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A28,Baux!$A:$A,0)),N27)</f>
         <v/>
       </c>
       <c r="M28" s="20">
-        <f>IF(L28="","",IF(INDEX(Baux!$P:$P,MATCH($A28,Baux!$A:$A,0))="",L28,MIN(L28,ROUND(K28*(1+INDEX(Baux!$P:$P,MATCH($A28,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A28,Baux!$A:$A,0))="Base fixe",C28*INDEX(Baux!$N:$N,MATCH($A28,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A28,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J28="",L28=""),"",ROUND(L28*J28,2))</f>
         <v/>
       </c>
       <c r="N28" s="20">
-        <f>M27</f>
-        <v/>
-      </c>
-      <c r="O28" s="21">
-        <f>IF(OR(M28="",N28=""),"",M28/N28-1)</f>
-        <v/>
-      </c>
-      <c r="P28" s="20">
-        <f>IF(M28="","",M28/12)</f>
+        <f>IF(LEFT(K28,5)="Geler",O28,IF(M28="","",IF(INDEX(Baux!$Q:$Q,MATCH($A28,Baux!$A:$A,0))="",M28,MIN(M28,ROUND(L28*(1+INDEX(Baux!$Q:$Q,MATCH($A28,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A28,Baux!$A:$A,0))="Base fixe",C28*INDEX(Baux!$O:$O,MATCH($A28,Baux!$A:$A,0)),VALUE(LEFT(F28,4))-VALUE(LEFT(H28,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O28" s="20">
+        <f>N27</f>
+        <v/>
+      </c>
+      <c r="P28" s="21">
+        <f>IF(OR(N28="",O28=""),"",N28/O28-1)</f>
         <v/>
       </c>
       <c r="Q28" s="20">
-        <f>IF(M28="","",M28/IF(INDEX(Baux!$K:$K,MATCH($A28,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A28,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A28,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N28="","",N28/12)</f>
         <v/>
       </c>
       <c r="R28" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A28,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A28,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A28,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A28,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A28,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N28="","",N28/IF(INDEX(Baux!$L:$L,MATCH($A28,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A28,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A28,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S28" s="20">
-        <f>IF(Q28="","",(Q28+R28)*INDEX(Baux!$J:$J,MATCH($A28,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A28,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A28,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A28,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A28,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A28,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T28" s="20">
-        <f>IF(Q28="","",Q28+R28+S28)</f>
-        <v/>
-      </c>
-      <c r="U28" s="15">
-        <f>IF(G28="",IF(D28&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D28&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V28" s="11" t="n"/>
-      <c r="W28" s="12" t="n"/>
+        <f>IF(R28="","",(R28+S28)*INDEX(Baux!$K:$K,MATCH($A28,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U28" s="20">
+        <f>IF(R28="","",R28+S28+T28)</f>
+        <v/>
+      </c>
+      <c r="V28" s="15">
+        <f>IF(LEFT(K28,5)="Geler","❄ Gelée",IF(G28="",IF(D28&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D28&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W28" s="22" t="n"/>
       <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="15">
+      <c r="Y28" s="12" t="n"/>
+      <c r="Z28" s="12" t="n"/>
+      <c r="AA28" s="11" t="n"/>
+      <c r="AB28" s="15">
         <f>A28&amp;"#"&amp;C28</f>
+        <v/>
+      </c>
+      <c r="AC28" s="15">
+        <f>IF(AND(D28&lt;=TODAY(),N28&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -9356,15 +9727,15 @@
         <v>7</v>
       </c>
       <c r="D29" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A29,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A29,Baux!$A:$A,0))*C29)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A29,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A29,Baux!$A:$A,0))*C29)</f>
         <v/>
       </c>
       <c r="E29" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A29,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A29,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F29" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A29,Baux!$A:$A,0)),4))+C29*INDEX(Baux!$N:$N,MATCH($A29,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A29,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A29,Baux!$A:$A,0)),4))+C29*INDEX(Baux!$O:$O,MATCH($A29,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A29,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G29" s="18">
@@ -9372,7 +9743,7 @@
         <v/>
       </c>
       <c r="H29" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A29,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A29,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A29,Baux!$A:$A,0)),4))+(C29-1)*INDEX(Baux!$N:$N,MATCH($A29,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A29,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A29,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A29,Baux!$A:$A,0)),IF(K28="Geler – rattrapage possible",H28,F28))</f>
         <v/>
       </c>
       <c r="I29" s="18">
@@ -9383,55 +9754,62 @@
         <f>IF(OR(G29="",I29=""),"",G29/I29)</f>
         <v/>
       </c>
-      <c r="K29" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A29,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A29,Baux!$A:$A,0)),M28)</f>
-        <v/>
-      </c>
+      <c r="K29" s="11" t="n"/>
       <c r="L29" s="20">
-        <f>IF(OR(J29="",K29=""),"",ROUND(K29*J29,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A29,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A29,Baux!$A:$A,0)),N28)</f>
         <v/>
       </c>
       <c r="M29" s="20">
-        <f>IF(L29="","",IF(INDEX(Baux!$P:$P,MATCH($A29,Baux!$A:$A,0))="",L29,MIN(L29,ROUND(K29*(1+INDEX(Baux!$P:$P,MATCH($A29,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A29,Baux!$A:$A,0))="Base fixe",C29*INDEX(Baux!$N:$N,MATCH($A29,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A29,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J29="",L29=""),"",ROUND(L29*J29,2))</f>
         <v/>
       </c>
       <c r="N29" s="20">
-        <f>M28</f>
-        <v/>
-      </c>
-      <c r="O29" s="21">
-        <f>IF(OR(M29="",N29=""),"",M29/N29-1)</f>
-        <v/>
-      </c>
-      <c r="P29" s="20">
-        <f>IF(M29="","",M29/12)</f>
+        <f>IF(LEFT(K29,5)="Geler",O29,IF(M29="","",IF(INDEX(Baux!$Q:$Q,MATCH($A29,Baux!$A:$A,0))="",M29,MIN(M29,ROUND(L29*(1+INDEX(Baux!$Q:$Q,MATCH($A29,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A29,Baux!$A:$A,0))="Base fixe",C29*INDEX(Baux!$O:$O,MATCH($A29,Baux!$A:$A,0)),VALUE(LEFT(F29,4))-VALUE(LEFT(H29,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O29" s="20">
+        <f>N28</f>
+        <v/>
+      </c>
+      <c r="P29" s="21">
+        <f>IF(OR(N29="",O29=""),"",N29/O29-1)</f>
         <v/>
       </c>
       <c r="Q29" s="20">
-        <f>IF(M29="","",M29/IF(INDEX(Baux!$K:$K,MATCH($A29,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A29,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A29,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N29="","",N29/12)</f>
         <v/>
       </c>
       <c r="R29" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A29,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A29,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A29,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A29,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A29,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N29="","",N29/IF(INDEX(Baux!$L:$L,MATCH($A29,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A29,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A29,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S29" s="20">
-        <f>IF(Q29="","",(Q29+R29)*INDEX(Baux!$J:$J,MATCH($A29,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A29,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A29,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A29,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A29,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A29,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T29" s="20">
-        <f>IF(Q29="","",Q29+R29+S29)</f>
-        <v/>
-      </c>
-      <c r="U29" s="15">
-        <f>IF(G29="",IF(D29&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D29&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V29" s="11" t="n"/>
-      <c r="W29" s="12" t="n"/>
+        <f>IF(R29="","",(R29+S29)*INDEX(Baux!$K:$K,MATCH($A29,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U29" s="20">
+        <f>IF(R29="","",R29+S29+T29)</f>
+        <v/>
+      </c>
+      <c r="V29" s="15">
+        <f>IF(LEFT(K29,5)="Geler","❄ Gelée",IF(G29="",IF(D29&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D29&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W29" s="22" t="n"/>
       <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="15">
+      <c r="Y29" s="12" t="n"/>
+      <c r="Z29" s="12" t="n"/>
+      <c r="AA29" s="11" t="n"/>
+      <c r="AB29" s="15">
         <f>A29&amp;"#"&amp;C29</f>
+        <v/>
+      </c>
+      <c r="AC29" s="15">
+        <f>IF(AND(D29&lt;=TODAY(),N29&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -9449,15 +9827,15 @@
         <v>8</v>
       </c>
       <c r="D30" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A30,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A30,Baux!$A:$A,0))*C30)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A30,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A30,Baux!$A:$A,0))*C30)</f>
         <v/>
       </c>
       <c r="E30" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A30,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A30,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F30" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A30,Baux!$A:$A,0)),4))+C30*INDEX(Baux!$N:$N,MATCH($A30,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A30,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A30,Baux!$A:$A,0)),4))+C30*INDEX(Baux!$O:$O,MATCH($A30,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A30,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G30" s="18">
@@ -9465,7 +9843,7 @@
         <v/>
       </c>
       <c r="H30" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A30,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A30,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A30,Baux!$A:$A,0)),4))+(C30-1)*INDEX(Baux!$N:$N,MATCH($A30,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A30,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A30,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A30,Baux!$A:$A,0)),IF(K29="Geler – rattrapage possible",H29,F29))</f>
         <v/>
       </c>
       <c r="I30" s="18">
@@ -9476,55 +9854,62 @@
         <f>IF(OR(G30="",I30=""),"",G30/I30)</f>
         <v/>
       </c>
-      <c r="K30" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A30,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A30,Baux!$A:$A,0)),M29)</f>
-        <v/>
-      </c>
+      <c r="K30" s="11" t="n"/>
       <c r="L30" s="20">
-        <f>IF(OR(J30="",K30=""),"",ROUND(K30*J30,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A30,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A30,Baux!$A:$A,0)),N29)</f>
         <v/>
       </c>
       <c r="M30" s="20">
-        <f>IF(L30="","",IF(INDEX(Baux!$P:$P,MATCH($A30,Baux!$A:$A,0))="",L30,MIN(L30,ROUND(K30*(1+INDEX(Baux!$P:$P,MATCH($A30,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A30,Baux!$A:$A,0))="Base fixe",C30*INDEX(Baux!$N:$N,MATCH($A30,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A30,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J30="",L30=""),"",ROUND(L30*J30,2))</f>
         <v/>
       </c>
       <c r="N30" s="20">
-        <f>M29</f>
-        <v/>
-      </c>
-      <c r="O30" s="21">
-        <f>IF(OR(M30="",N30=""),"",M30/N30-1)</f>
-        <v/>
-      </c>
-      <c r="P30" s="20">
-        <f>IF(M30="","",M30/12)</f>
+        <f>IF(LEFT(K30,5)="Geler",O30,IF(M30="","",IF(INDEX(Baux!$Q:$Q,MATCH($A30,Baux!$A:$A,0))="",M30,MIN(M30,ROUND(L30*(1+INDEX(Baux!$Q:$Q,MATCH($A30,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A30,Baux!$A:$A,0))="Base fixe",C30*INDEX(Baux!$O:$O,MATCH($A30,Baux!$A:$A,0)),VALUE(LEFT(F30,4))-VALUE(LEFT(H30,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O30" s="20">
+        <f>N29</f>
+        <v/>
+      </c>
+      <c r="P30" s="21">
+        <f>IF(OR(N30="",O30=""),"",N30/O30-1)</f>
         <v/>
       </c>
       <c r="Q30" s="20">
-        <f>IF(M30="","",M30/IF(INDEX(Baux!$K:$K,MATCH($A30,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A30,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A30,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N30="","",N30/12)</f>
         <v/>
       </c>
       <c r="R30" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A30,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A30,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A30,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A30,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A30,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N30="","",N30/IF(INDEX(Baux!$L:$L,MATCH($A30,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A30,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A30,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S30" s="20">
-        <f>IF(Q30="","",(Q30+R30)*INDEX(Baux!$J:$J,MATCH($A30,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A30,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A30,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A30,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A30,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A30,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T30" s="20">
-        <f>IF(Q30="","",Q30+R30+S30)</f>
-        <v/>
-      </c>
-      <c r="U30" s="15">
-        <f>IF(G30="",IF(D30&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D30&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V30" s="11" t="n"/>
-      <c r="W30" s="12" t="n"/>
+        <f>IF(R30="","",(R30+S30)*INDEX(Baux!$K:$K,MATCH($A30,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U30" s="20">
+        <f>IF(R30="","",R30+S30+T30)</f>
+        <v/>
+      </c>
+      <c r="V30" s="15">
+        <f>IF(LEFT(K30,5)="Geler","❄ Gelée",IF(G30="",IF(D30&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D30&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W30" s="22" t="n"/>
       <c r="X30" s="11" t="n"/>
-      <c r="Y30" s="15">
+      <c r="Y30" s="12" t="n"/>
+      <c r="Z30" s="12" t="n"/>
+      <c r="AA30" s="11" t="n"/>
+      <c r="AB30" s="15">
         <f>A30&amp;"#"&amp;C30</f>
+        <v/>
+      </c>
+      <c r="AC30" s="15">
+        <f>IF(AND(D30&lt;=TODAY(),N30&lt;&gt;""),1,0)</f>
         <v/>
       </c>
     </row>
@@ -9542,15 +9927,15 @@
         <v>9</v>
       </c>
       <c r="D31" s="13">
-        <f>EDATE(INDEX(Baux!$E:$E,MATCH($A31,Baux!$A:$A,0)),12*INDEX(Baux!$N:$N,MATCH($A31,Baux!$A:$A,0))*C31)</f>
+        <f>EDATE(INDEX(Baux!$F:$F,MATCH($A31,Baux!$A:$A,0)),12*INDEX(Baux!$O:$O,MATCH($A31,Baux!$A:$A,0))*C31)</f>
         <v/>
       </c>
       <c r="E31" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A31,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A31,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F31" s="15">
-        <f>TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A31,Baux!$A:$A,0)),4))+C31*INDEX(Baux!$N:$N,MATCH($A31,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A31,Baux!$A:$A,0)),3)</f>
+        <f>TEXT(VALUE(LEFT(INDEX(Baux!$N:$N,MATCH($A31,Baux!$A:$A,0)),4))+C31*INDEX(Baux!$O:$O,MATCH($A31,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$N:$N,MATCH($A31,Baux!$A:$A,0)),3)</f>
         <v/>
       </c>
       <c r="G31" s="18">
@@ -9558,7 +9943,7 @@
         <v/>
       </c>
       <c r="H31" s="15">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A31,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$M:$M,MATCH($A31,Baux!$A:$A,0)),TEXT(VALUE(LEFT(INDEX(Baux!$M:$M,MATCH($A31,Baux!$A:$A,0)),4))+(C31-1)*INDEX(Baux!$N:$N,MATCH($A31,Baux!$A:$A,0)),"0")&amp;RIGHT(INDEX(Baux!$M:$M,MATCH($A31,Baux!$A:$A,0)),3))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A31,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$N:$N,MATCH($A31,Baux!$A:$A,0)),IF(K30="Geler – rattrapage possible",H30,F30))</f>
         <v/>
       </c>
       <c r="I31" s="18">
@@ -9569,74 +9954,87 @@
         <f>IF(OR(G31="",I31=""),"",G31/I31)</f>
         <v/>
       </c>
-      <c r="K31" s="20">
-        <f>IF(INDEX(Baux!$O:$O,MATCH($A31,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$H:$H,MATCH($A31,Baux!$A:$A,0)),M30)</f>
-        <v/>
-      </c>
+      <c r="K31" s="11" t="n"/>
       <c r="L31" s="20">
-        <f>IF(OR(J31="",K31=""),"",ROUND(K31*J31,2))</f>
+        <f>IF(INDEX(Baux!$P:$P,MATCH($A31,Baux!$A:$A,0))="Base fixe",INDEX(Baux!$I:$I,MATCH($A31,Baux!$A:$A,0)),N30)</f>
         <v/>
       </c>
       <c r="M31" s="20">
-        <f>IF(L31="","",IF(INDEX(Baux!$P:$P,MATCH($A31,Baux!$A:$A,0))="",L31,MIN(L31,ROUND(K31*(1+INDEX(Baux!$P:$P,MATCH($A31,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$O:$O,MATCH($A31,Baux!$A:$A,0))="Base fixe",C31*INDEX(Baux!$N:$N,MATCH($A31,Baux!$A:$A,0)),INDEX(Baux!$N:$N,MATCH($A31,Baux!$A:$A,0))),2))))</f>
+        <f>IF(OR(J31="",L31=""),"",ROUND(L31*J31,2))</f>
         <v/>
       </c>
       <c r="N31" s="20">
-        <f>M30</f>
-        <v/>
-      </c>
-      <c r="O31" s="21">
-        <f>IF(OR(M31="",N31=""),"",M31/N31-1)</f>
-        <v/>
-      </c>
-      <c r="P31" s="20">
-        <f>IF(M31="","",M31/12)</f>
+        <f>IF(LEFT(K31,5)="Geler",O31,IF(M31="","",IF(INDEX(Baux!$Q:$Q,MATCH($A31,Baux!$A:$A,0))="",M31,MIN(M31,ROUND(L31*(1+INDEX(Baux!$Q:$Q,MATCH($A31,Baux!$A:$A,0))/100)^IF(INDEX(Baux!$P:$P,MATCH($A31,Baux!$A:$A,0))="Base fixe",C31*INDEX(Baux!$O:$O,MATCH($A31,Baux!$A:$A,0)),VALUE(LEFT(F31,4))-VALUE(LEFT(H31,4))),2)))))</f>
+        <v/>
+      </c>
+      <c r="O31" s="20">
+        <f>N30</f>
+        <v/>
+      </c>
+      <c r="P31" s="21">
+        <f>IF(OR(N31="",O31=""),"",N31/O31-1)</f>
         <v/>
       </c>
       <c r="Q31" s="20">
-        <f>IF(M31="","",M31/IF(INDEX(Baux!$K:$K,MATCH($A31,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A31,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A31,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
+        <f>IF(N31="","",N31/12)</f>
         <v/>
       </c>
       <c r="R31" s="20">
-        <f>IF(INDEX(Baux!$I:$I,MATCH($A31,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A31,Baux!$A:$A,0)))/IF(INDEX(Baux!$K:$K,MATCH($A31,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$K:$K,MATCH($A31,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$K:$K,MATCH($A31,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
+        <f>IF(N31="","",N31/IF(INDEX(Baux!$L:$L,MATCH($A31,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A31,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A31,Baux!$A:$A,0))="Semestrielle",2,1))))</f>
         <v/>
       </c>
       <c r="S31" s="20">
-        <f>IF(Q31="","",(Q31+R31)*INDEX(Baux!$J:$J,MATCH($A31,Baux!$A:$A,0))/100)</f>
+        <f>IF(INDEX(Baux!$J:$J,MATCH($A31,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A31,Baux!$A:$A,0)))/IF(INDEX(Baux!$L:$L,MATCH($A31,Baux!$A:$A,0))="Mensuelle",12,IF(INDEX(Baux!$L:$L,MATCH($A31,Baux!$A:$A,0))="Trimestrielle",4,IF(INDEX(Baux!$L:$L,MATCH($A31,Baux!$A:$A,0))="Semestrielle",2,1)))</f>
         <v/>
       </c>
       <c r="T31" s="20">
-        <f>IF(Q31="","",Q31+R31+S31)</f>
-        <v/>
-      </c>
-      <c r="U31" s="15">
-        <f>IF(G31="",IF(D31&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D31&lt;=TODAY(),"✔ Calculable","Indice connu – à venir"))</f>
-        <v/>
-      </c>
-      <c r="V31" s="11" t="n"/>
-      <c r="W31" s="12" t="n"/>
+        <f>IF(R31="","",(R31+S31)*INDEX(Baux!$K:$K,MATCH($A31,Baux!$A:$A,0))/100)</f>
+        <v/>
+      </c>
+      <c r="U31" s="20">
+        <f>IF(R31="","",R31+S31+T31)</f>
+        <v/>
+      </c>
+      <c r="V31" s="15">
+        <f>IF(LEFT(K31,5)="Geler","❄ Gelée",IF(G31="",IF(D31&lt;=TODAY(),"⚠ Indice attendu","À venir"),IF(D31&lt;=TODAY(),"✔ Calculable","Indice connu – à venir")))</f>
+        <v/>
+      </c>
+      <c r="W31" s="22" t="n"/>
       <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="15">
+      <c r="Y31" s="12" t="n"/>
+      <c r="Z31" s="12" t="n"/>
+      <c r="AA31" s="11" t="n"/>
+      <c r="AB31" s="15">
         <f>A31&amp;"#"&amp;C31</f>
         <v/>
       </c>
+      <c r="AC31" s="15">
+        <f>IF(AND(D31&lt;=TODAY(),N31&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y31"/>
-  <conditionalFormatting sqref="U2:U531">
+  <autoFilter ref="A1:AC31"/>
+  <conditionalFormatting sqref="V2:V531">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>LEFT(U2,1)="⚠"</formula>
+      <formula>LEFT(V2,1)="❄"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="2">
-      <formula>AND(LEFT(U2,1)="✔",V2&lt;&gt;"Oui")</formula>
+      <formula>LEFT(V2,1)="⚠"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="3">
-      <formula>AND(LEFT(U2,1)="✔",V2="Oui")</formula>
+      <formula>AND(LEFT(V2,1)="✔",X2&lt;&gt;"Oui")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="4">
+      <formula>AND(LEFT(V2,1)="✔",X2="Oui")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="V2:V531" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="X2:X531" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oui,Non"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K531" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Décision du bailleur" prompt="Vide ou Appliquer = révision appliquée. Geler = loyer inchangé ; « rattrapage possible » repart de l'indice de la dernière révision appliquée." type="list">
+      <formula1>"Appliquer,Geler – sans rattrapage,Geler – rattrapage possible"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9649,7 +10047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9664,7 +10062,9 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -9695,7 +10095,7 @@
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>N° dernière révision calculable</t>
+          <t>N° dernière révision effective</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
@@ -9730,7 +10130,17 @@
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
+          <t>Révisions gelées</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
           <t>Action</t>
+        </is>
+      </c>
+      <c r="O1" s="10" t="inlineStr">
+        <is>
+          <t>Consigne prochaine révision</t>
         </is>
       </c>
     </row>
@@ -9749,19 +10159,19 @@
         <v/>
       </c>
       <c r="D2" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="E2" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A2,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$I:$I,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F2" s="15">
-        <f>_xlfn.MAXIFS(Révisions!$C:$C,Révisions!$A:$A,A2,Révisions!$U:$U,"✔ Calculable")</f>
+        <f>_xlfn.MAXIFS(Révisions!$C:$C,Révisions!$A:$A,A2,Révisions!$AC:$AC,1)</f>
         <v/>
       </c>
       <c r="G2" s="20">
-        <f>IF(F2=0,E2,SUMIFS(Révisions!$M:$M,Révisions!$A:$A,A2,Révisions!$C:$C,F2))</f>
+        <f>IF(F2=0,E2,SUMIFS(Révisions!$N:$N,Révisions!$A:$A,A2,Révisions!$C:$C,F2))</f>
         <v/>
       </c>
       <c r="H2" s="20">
@@ -9773,7 +10183,7 @@
         <v/>
       </c>
       <c r="J2" s="15">
-        <f>IFERROR(INDEX(Révisions!$F:$F,MATCH(A2&amp;"#"&amp;(F2+1),Révisions!$Y:$Y,0)),"—")</f>
+        <f>IFERROR(INDEX(Révisions!$F:$F,MATCH(A2&amp;"#"&amp;(F2+1),Révisions!$AB:$AB,0)),"—")</f>
         <v/>
       </c>
       <c r="K2" s="15">
@@ -9781,11 +10191,19 @@
         <v/>
       </c>
       <c r="L2" s="15">
-        <f>COUNTIFS(Révisions!$A:$A,A2,Révisions!$U:$U,"✔ Calculable",Révisions!$V:$V,"&lt;&gt;Oui")</f>
+        <f>COUNTIFS(Révisions!$A:$A,A2,Révisions!$V:$V,"✔ Calculable",Révisions!$X:$X,"&lt;&gt;Oui")</f>
         <v/>
       </c>
       <c r="M2" s="15">
+        <f>COUNTIFS(Révisions!$A:$A,A2,Révisions!$V:$V,"❄ Gelée")</f>
+        <v/>
+      </c>
+      <c r="N2" s="15">
         <f>IF(L2&gt;0,"⚠ Facturer la révision ("&amp;L2&amp;" en attente)",IF(AND(I2&lt;&gt;"—",I2-TODAY()&lt;=60),IF(K2="Oui","Révision dans "&amp;INT(I2-TODAY())&amp;" j – indice publié","Révision dans "&amp;INT(I2-TODAY())&amp;" j – indice non publié"),"RAS"))</f>
+        <v/>
+      </c>
+      <c r="O2" s="23">
+        <f>IFERROR(INDEX(Révisions!$W:$W,MATCH(A2&amp;"#"&amp;(F2+1),Révisions!$AB:$AB,0))&amp;"","")</f>
         <v/>
       </c>
     </row>
@@ -9804,19 +10222,19 @@
         <v/>
       </c>
       <c r="D3" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A3,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="E3" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A3,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$I:$I,MATCH($A3,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F3" s="15">
-        <f>_xlfn.MAXIFS(Révisions!$C:$C,Révisions!$A:$A,A3,Révisions!$U:$U,"✔ Calculable")</f>
+        <f>_xlfn.MAXIFS(Révisions!$C:$C,Révisions!$A:$A,A3,Révisions!$AC:$AC,1)</f>
         <v/>
       </c>
       <c r="G3" s="20">
-        <f>IF(F3=0,E3,SUMIFS(Révisions!$M:$M,Révisions!$A:$A,A3,Révisions!$C:$C,F3))</f>
+        <f>IF(F3=0,E3,SUMIFS(Révisions!$N:$N,Révisions!$A:$A,A3,Révisions!$C:$C,F3))</f>
         <v/>
       </c>
       <c r="H3" s="20">
@@ -9828,7 +10246,7 @@
         <v/>
       </c>
       <c r="J3" s="15">
-        <f>IFERROR(INDEX(Révisions!$F:$F,MATCH(A3&amp;"#"&amp;(F3+1),Révisions!$Y:$Y,0)),"—")</f>
+        <f>IFERROR(INDEX(Révisions!$F:$F,MATCH(A3&amp;"#"&amp;(F3+1),Révisions!$AB:$AB,0)),"—")</f>
         <v/>
       </c>
       <c r="K3" s="15">
@@ -9836,11 +10254,19 @@
         <v/>
       </c>
       <c r="L3" s="15">
-        <f>COUNTIFS(Révisions!$A:$A,A3,Révisions!$U:$U,"✔ Calculable",Révisions!$V:$V,"&lt;&gt;Oui")</f>
+        <f>COUNTIFS(Révisions!$A:$A,A3,Révisions!$V:$V,"✔ Calculable",Révisions!$X:$X,"&lt;&gt;Oui")</f>
         <v/>
       </c>
       <c r="M3" s="15">
+        <f>COUNTIFS(Révisions!$A:$A,A3,Révisions!$V:$V,"❄ Gelée")</f>
+        <v/>
+      </c>
+      <c r="N3" s="15">
         <f>IF(L3&gt;0,"⚠ Facturer la révision ("&amp;L3&amp;" en attente)",IF(AND(I3&lt;&gt;"—",I3-TODAY()&lt;=60),IF(K3="Oui","Révision dans "&amp;INT(I3-TODAY())&amp;" j – indice publié","Révision dans "&amp;INT(I3-TODAY())&amp;" j – indice non publié"),"RAS"))</f>
+        <v/>
+      </c>
+      <c r="O3" s="23">
+        <f>IFERROR(INDEX(Révisions!$W:$W,MATCH(A3&amp;"#"&amp;(F3+1),Révisions!$AB:$AB,0))&amp;"","")</f>
         <v/>
       </c>
     </row>
@@ -9859,19 +10285,19 @@
         <v/>
       </c>
       <c r="D4" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A4,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="E4" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A4,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$I:$I,MATCH($A4,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F4" s="15">
-        <f>_xlfn.MAXIFS(Révisions!$C:$C,Révisions!$A:$A,A4,Révisions!$U:$U,"✔ Calculable")</f>
+        <f>_xlfn.MAXIFS(Révisions!$C:$C,Révisions!$A:$A,A4,Révisions!$AC:$AC,1)</f>
         <v/>
       </c>
       <c r="G4" s="20">
-        <f>IF(F4=0,E4,SUMIFS(Révisions!$M:$M,Révisions!$A:$A,A4,Révisions!$C:$C,F4))</f>
+        <f>IF(F4=0,E4,SUMIFS(Révisions!$N:$N,Révisions!$A:$A,A4,Révisions!$C:$C,F4))</f>
         <v/>
       </c>
       <c r="H4" s="20">
@@ -9883,7 +10309,7 @@
         <v/>
       </c>
       <c r="J4" s="15">
-        <f>IFERROR(INDEX(Révisions!$F:$F,MATCH(A4&amp;"#"&amp;(F4+1),Révisions!$Y:$Y,0)),"—")</f>
+        <f>IFERROR(INDEX(Révisions!$F:$F,MATCH(A4&amp;"#"&amp;(F4+1),Révisions!$AB:$AB,0)),"—")</f>
         <v/>
       </c>
       <c r="K4" s="15">
@@ -9891,11 +10317,19 @@
         <v/>
       </c>
       <c r="L4" s="15">
-        <f>COUNTIFS(Révisions!$A:$A,A4,Révisions!$U:$U,"✔ Calculable",Révisions!$V:$V,"&lt;&gt;Oui")</f>
+        <f>COUNTIFS(Révisions!$A:$A,A4,Révisions!$V:$V,"✔ Calculable",Révisions!$X:$X,"&lt;&gt;Oui")</f>
         <v/>
       </c>
       <c r="M4" s="15">
+        <f>COUNTIFS(Révisions!$A:$A,A4,Révisions!$V:$V,"❄ Gelée")</f>
+        <v/>
+      </c>
+      <c r="N4" s="15">
         <f>IF(L4&gt;0,"⚠ Facturer la révision ("&amp;L4&amp;" en attente)",IF(AND(I4&lt;&gt;"—",I4-TODAY()&lt;=60),IF(K4="Oui","Révision dans "&amp;INT(I4-TODAY())&amp;" j – indice publié","Révision dans "&amp;INT(I4-TODAY())&amp;" j – indice non publié"),"RAS"))</f>
+        <v/>
+      </c>
+      <c r="O4" s="23">
+        <f>IFERROR(INDEX(Révisions!$W:$W,MATCH(A4&amp;"#"&amp;(F4+1),Révisions!$AB:$AB,0))&amp;"","")</f>
         <v/>
       </c>
     </row>
@@ -9914,19 +10348,19 @@
         <v/>
       </c>
       <c r="D5" s="15">
-        <f>INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$M:$M,MATCH($A5,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="E5" s="20">
-        <f>INDEX(Baux!$H:$H,MATCH($A5,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$I:$I,MATCH($A5,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F5" s="15">
-        <f>_xlfn.MAXIFS(Révisions!$C:$C,Révisions!$A:$A,A5,Révisions!$U:$U,"✔ Calculable")</f>
+        <f>_xlfn.MAXIFS(Révisions!$C:$C,Révisions!$A:$A,A5,Révisions!$AC:$AC,1)</f>
         <v/>
       </c>
       <c r="G5" s="20">
-        <f>IF(F5=0,E5,SUMIFS(Révisions!$M:$M,Révisions!$A:$A,A5,Révisions!$C:$C,F5))</f>
+        <f>IF(F5=0,E5,SUMIFS(Révisions!$N:$N,Révisions!$A:$A,A5,Révisions!$C:$C,F5))</f>
         <v/>
       </c>
       <c r="H5" s="20">
@@ -9938,7 +10372,7 @@
         <v/>
       </c>
       <c r="J5" s="15">
-        <f>IFERROR(INDEX(Révisions!$F:$F,MATCH(A5&amp;"#"&amp;(F5+1),Révisions!$Y:$Y,0)),"—")</f>
+        <f>IFERROR(INDEX(Révisions!$F:$F,MATCH(A5&amp;"#"&amp;(F5+1),Révisions!$AB:$AB,0)),"—")</f>
         <v/>
       </c>
       <c r="K5" s="15">
@@ -9946,21 +10380,29 @@
         <v/>
       </c>
       <c r="L5" s="15">
-        <f>COUNTIFS(Révisions!$A:$A,A5,Révisions!$U:$U,"✔ Calculable",Révisions!$V:$V,"&lt;&gt;Oui")</f>
+        <f>COUNTIFS(Révisions!$A:$A,A5,Révisions!$V:$V,"✔ Calculable",Révisions!$X:$X,"&lt;&gt;Oui")</f>
         <v/>
       </c>
       <c r="M5" s="15">
+        <f>COUNTIFS(Révisions!$A:$A,A5,Révisions!$V:$V,"❄ Gelée")</f>
+        <v/>
+      </c>
+      <c r="N5" s="15">
         <f>IF(L5&gt;0,"⚠ Facturer la révision ("&amp;L5&amp;" en attente)",IF(AND(I5&lt;&gt;"—",I5-TODAY()&lt;=60),IF(K5="Oui","Révision dans "&amp;INT(I5-TODAY())&amp;" j – indice publié","Révision dans "&amp;INT(I5-TODAY())&amp;" j – indice non publié"),"RAS"))</f>
         <v/>
       </c>
+      <c r="O5" s="23">
+        <f>IFERROR(INDEX(Révisions!$W:$W,MATCH(A5&amp;"#"&amp;(F5+1),Révisions!$AB:$AB,0))&amp;"","")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M5">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>LEFT(M2,1)="⚠"</formula>
+  <conditionalFormatting sqref="N2:N5">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>LEFT(N2,1)="⚠"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="4">
-      <formula>LEFT(M2,8)="Révision"</formula>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>LEFT(N2,8)="Révision"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10069,11 +10511,11 @@
         <v/>
       </c>
       <c r="C2" s="15">
-        <f>IF(INDEX(Baux!$Q:$Q,MATCH($A2,Baux!$A:$A,0))="","À RENSEIGNER",INDEX(Baux!$Q:$Q,MATCH($A2,Baux!$A:$A,0)))</f>
+        <f>IF(INDEX(Baux!$R:$R,MATCH($A2,Baux!$A:$A,0))="","À RENSEIGNER",INDEX(Baux!$R:$R,MATCH($A2,Baux!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="D2" s="15">
-        <f>IF(INDEX(Baux!$R:$R,MATCH($A2,Baux!$A:$A,0))="","",INDEX(Baux!$R:$R,MATCH($A2,Baux!$A:$A,0)))</f>
+        <f>IF(INDEX(Baux!$S:$S,MATCH($A2,Baux!$A:$A,0))="","",INDEX(Baux!$S:$S,MATCH($A2,Baux!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="E2" s="15">
@@ -10081,7 +10523,7 @@
         <v/>
       </c>
       <c r="F2" s="15">
-        <f>INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$L:$L,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="G2" s="15">
@@ -10093,11 +10535,11 @@
         <v/>
       </c>
       <c r="I2" s="20">
-        <f>ROUND(IF(INDEX(Baux!$I:$I,MATCH($A2,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A2,Baux!$A:$A,0)))/IF(F2="Mensuelle",12,IF(F2="Trimestrielle",4,IF(F2="Semestrielle",2,1))),2)</f>
+        <f>ROUND(IF(INDEX(Baux!$J:$J,MATCH($A2,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A2,Baux!$A:$A,0)))/IF(F2="Mensuelle",12,IF(F2="Trimestrielle",4,IF(F2="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
       <c r="J2" s="15">
-        <f>INDEX(Baux!$J:$J,MATCH($A2,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="K2" s="15">
@@ -10108,7 +10550,7 @@
         <f>DATE(YEAR(TODAY()),MONTH(TODAY())+1,1)</f>
         <v/>
       </c>
-      <c r="M2" s="22">
+      <c r="M2" s="24">
         <f>"{""customer_id"": "&amp;C2&amp;", ""start"": """&amp;YEAR(L2)&amp;"-"&amp;TEXT(MONTH(L2),"00")&amp;"-"&amp;TEXT(DAY(L2),"00")&amp;""", ""currency"": ""EUR"", ""recurrence"": {""type"": """&amp;G2&amp;""", ""day_of_month"": 1}, ""invoice_lines"": [{""label"": """&amp;E2&amp;""", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(H2,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K2&amp;""""&amp;IF(D2&lt;&gt;"",", ""product_id"": "&amp;D2,"")&amp;"}"&amp;IF(I2&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(I2,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K2&amp;"""}","")&amp;"]}"</f>
         <v/>
       </c>
@@ -10124,11 +10566,11 @@
         <v/>
       </c>
       <c r="C3" s="15">
-        <f>IF(INDEX(Baux!$Q:$Q,MATCH($A3,Baux!$A:$A,0))="","À RENSEIGNER",INDEX(Baux!$Q:$Q,MATCH($A3,Baux!$A:$A,0)))</f>
+        <f>IF(INDEX(Baux!$R:$R,MATCH($A3,Baux!$A:$A,0))="","À RENSEIGNER",INDEX(Baux!$R:$R,MATCH($A3,Baux!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="D3" s="15">
-        <f>IF(INDEX(Baux!$R:$R,MATCH($A3,Baux!$A:$A,0))="","",INDEX(Baux!$R:$R,MATCH($A3,Baux!$A:$A,0)))</f>
+        <f>IF(INDEX(Baux!$S:$S,MATCH($A3,Baux!$A:$A,0))="","",INDEX(Baux!$S:$S,MATCH($A3,Baux!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="E3" s="15">
@@ -10136,7 +10578,7 @@
         <v/>
       </c>
       <c r="F3" s="15">
-        <f>INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$L:$L,MATCH($A3,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="G3" s="15">
@@ -10148,11 +10590,11 @@
         <v/>
       </c>
       <c r="I3" s="20">
-        <f>ROUND(IF(INDEX(Baux!$I:$I,MATCH($A3,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A3,Baux!$A:$A,0)))/IF(F3="Mensuelle",12,IF(F3="Trimestrielle",4,IF(F3="Semestrielle",2,1))),2)</f>
+        <f>ROUND(IF(INDEX(Baux!$J:$J,MATCH($A3,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A3,Baux!$A:$A,0)))/IF(F3="Mensuelle",12,IF(F3="Trimestrielle",4,IF(F3="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
       <c r="J3" s="15">
-        <f>INDEX(Baux!$J:$J,MATCH($A3,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="K3" s="15">
@@ -10163,7 +10605,7 @@
         <f>DATE(YEAR(TODAY()),MONTH(TODAY())+1,1)</f>
         <v/>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="24">
         <f>"{""customer_id"": "&amp;C3&amp;", ""start"": """&amp;YEAR(L3)&amp;"-"&amp;TEXT(MONTH(L3),"00")&amp;"-"&amp;TEXT(DAY(L3),"00")&amp;""", ""currency"": ""EUR"", ""recurrence"": {""type"": """&amp;G3&amp;""", ""day_of_month"": 1}, ""invoice_lines"": [{""label"": """&amp;E3&amp;""", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(H3,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K3&amp;""""&amp;IF(D3&lt;&gt;"",", ""product_id"": "&amp;D3,"")&amp;"}"&amp;IF(I3&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(I3,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K3&amp;"""}","")&amp;"]}"</f>
         <v/>
       </c>
@@ -10179,11 +10621,11 @@
         <v/>
       </c>
       <c r="C4" s="15">
-        <f>IF(INDEX(Baux!$Q:$Q,MATCH($A4,Baux!$A:$A,0))="","À RENSEIGNER",INDEX(Baux!$Q:$Q,MATCH($A4,Baux!$A:$A,0)))</f>
+        <f>IF(INDEX(Baux!$R:$R,MATCH($A4,Baux!$A:$A,0))="","À RENSEIGNER",INDEX(Baux!$R:$R,MATCH($A4,Baux!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="D4" s="15">
-        <f>IF(INDEX(Baux!$R:$R,MATCH($A4,Baux!$A:$A,0))="","",INDEX(Baux!$R:$R,MATCH($A4,Baux!$A:$A,0)))</f>
+        <f>IF(INDEX(Baux!$S:$S,MATCH($A4,Baux!$A:$A,0))="","",INDEX(Baux!$S:$S,MATCH($A4,Baux!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="E4" s="15">
@@ -10191,7 +10633,7 @@
         <v/>
       </c>
       <c r="F4" s="15">
-        <f>INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$L:$L,MATCH($A4,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="G4" s="15">
@@ -10203,11 +10645,11 @@
         <v/>
       </c>
       <c r="I4" s="20">
-        <f>ROUND(IF(INDEX(Baux!$I:$I,MATCH($A4,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A4,Baux!$A:$A,0)))/IF(F4="Mensuelle",12,IF(F4="Trimestrielle",4,IF(F4="Semestrielle",2,1))),2)</f>
+        <f>ROUND(IF(INDEX(Baux!$J:$J,MATCH($A4,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A4,Baux!$A:$A,0)))/IF(F4="Mensuelle",12,IF(F4="Trimestrielle",4,IF(F4="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
       <c r="J4" s="15">
-        <f>INDEX(Baux!$J:$J,MATCH($A4,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="K4" s="15">
@@ -10218,7 +10660,7 @@
         <f>DATE(YEAR(TODAY()),MONTH(TODAY())+1,1)</f>
         <v/>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="24">
         <f>"{""customer_id"": "&amp;C4&amp;", ""start"": """&amp;YEAR(L4)&amp;"-"&amp;TEXT(MONTH(L4),"00")&amp;"-"&amp;TEXT(DAY(L4),"00")&amp;""", ""currency"": ""EUR"", ""recurrence"": {""type"": """&amp;G4&amp;""", ""day_of_month"": 1}, ""invoice_lines"": [{""label"": """&amp;E4&amp;""", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(H4,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K4&amp;""""&amp;IF(D4&lt;&gt;"",", ""product_id"": "&amp;D4,"")&amp;"}"&amp;IF(I4&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(I4,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K4&amp;"""}","")&amp;"]}"</f>
         <v/>
       </c>
@@ -10234,11 +10676,11 @@
         <v/>
       </c>
       <c r="C5" s="15">
-        <f>IF(INDEX(Baux!$Q:$Q,MATCH($A5,Baux!$A:$A,0))="","À RENSEIGNER",INDEX(Baux!$Q:$Q,MATCH($A5,Baux!$A:$A,0)))</f>
+        <f>IF(INDEX(Baux!$R:$R,MATCH($A5,Baux!$A:$A,0))="","À RENSEIGNER",INDEX(Baux!$R:$R,MATCH($A5,Baux!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="D5" s="15">
-        <f>IF(INDEX(Baux!$R:$R,MATCH($A5,Baux!$A:$A,0))="","",INDEX(Baux!$R:$R,MATCH($A5,Baux!$A:$A,0)))</f>
+        <f>IF(INDEX(Baux!$S:$S,MATCH($A5,Baux!$A:$A,0))="","",INDEX(Baux!$S:$S,MATCH($A5,Baux!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="E5" s="15">
@@ -10246,7 +10688,7 @@
         <v/>
       </c>
       <c r="F5" s="15">
-        <f>INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$L:$L,MATCH($A5,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="G5" s="15">
@@ -10258,11 +10700,11 @@
         <v/>
       </c>
       <c r="I5" s="20">
-        <f>ROUND(IF(INDEX(Baux!$I:$I,MATCH($A5,Baux!$A:$A,0))="",0,INDEX(Baux!$I:$I,MATCH($A5,Baux!$A:$A,0)))/IF(F5="Mensuelle",12,IF(F5="Trimestrielle",4,IF(F5="Semestrielle",2,1))),2)</f>
+        <f>ROUND(IF(INDEX(Baux!$J:$J,MATCH($A5,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A5,Baux!$A:$A,0)))/IF(F5="Mensuelle",12,IF(F5="Trimestrielle",4,IF(F5="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
       <c r="J5" s="15">
-        <f>INDEX(Baux!$J:$J,MATCH($A5,Baux!$A:$A,0))</f>
+        <f>INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="K5" s="15">
@@ -10273,7 +10715,7 @@
         <f>DATE(YEAR(TODAY()),MONTH(TODAY())+1,1)</f>
         <v/>
       </c>
-      <c r="M5" s="22">
+      <c r="M5" s="24">
         <f>"{""customer_id"": "&amp;C5&amp;", ""start"": """&amp;YEAR(L5)&amp;"-"&amp;TEXT(MONTH(L5),"00")&amp;"-"&amp;TEXT(DAY(L5),"00")&amp;""", ""currency"": ""EUR"", ""recurrence"": {""type"": """&amp;G5&amp;""", ""day_of_month"": 1}, ""invoice_lines"": [{""label"": """&amp;E5&amp;""", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(H5,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K5&amp;""""&amp;IF(D5&lt;&gt;"",", ""product_id"": "&amp;D5,"")&amp;"}"&amp;IF(I5&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(I5,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K5&amp;"""}","")&amp;"]}"</f>
         <v/>
       </c>

--- a/demo/DEMO_SCI_EXEMPLE_valeurs_fictives.xlsx
+++ b/demo/DEMO_SCI_EXEMPLE_valeurs_fictives.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,9 +144,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -912,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1039,26 +1036,73 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Date de génération</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>46274</v>
+          <t>Pennylane – mode des factures</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>awaiting_validation</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>Pennylane – conditions de paiement</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>upon_receipt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Pennylane – moyen de paiement</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Date de génération</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>Mode démonstration</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"awaiting_validation,finalized"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"upon_receipt,7_days,15_days,30_days,30_days_end_of_month,45_days,45_days_end_of_month,60_days"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"offline,gocardless_direct_debit,pro_account_sepa_core"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1069,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1091,8 +1135,9 @@
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -1193,10 +1238,15 @@
       </c>
       <c r="T1" s="10" t="inlineStr">
         <is>
+          <t>Pennylane subscription_id</t>
+        </is>
+      </c>
+      <c r="U1" s="10" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="V1" s="10" t="inlineStr">
         <is>
           <t>Contrôles</t>
         </is>
@@ -1278,12 +1328,13 @@
         </is>
       </c>
       <c r="S2" s="11" t="n"/>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="11" t="n"/>
+      <c r="U2" s="11" t="inlineStr">
         <is>
           <t>Clause d'échelle mobile annuelle, ILC même trimestre</t>
         </is>
       </c>
-      <c r="U2" s="15">
+      <c r="V2" s="15">
         <f>IF(A2="","",TRIM(IF(F2="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(I2)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,M2)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,M2,Indices!$B:$B,N2)=0,"Indice de base "&amp;N2&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(N2)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A2)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(Q2&lt;&gt;"",NOT(ISNUMBER(Q2))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A2)=1,"",""))&amp;IF(AND(F2&lt;&gt;"",ISNUMBER(I2),SUMIFS(Indices!$C:$C,Indices!$A:$A,M2,Indices!$B:$B,N2)&gt;0,LEN(N2)=7,COUNTIF($A$2:$A$200,A2)=1),"OK",""))</f>
         <v/>
       </c>
@@ -1359,12 +1410,13 @@
         </is>
       </c>
       <c r="S3" s="11" t="n"/>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="11" t="n"/>
+      <c r="U3" s="11" t="inlineStr">
         <is>
           <t>Révision triennale indexée ILAT, indice de base fixe</t>
         </is>
       </c>
-      <c r="U3" s="15">
+      <c r="V3" s="15">
         <f>IF(A3="","",TRIM(IF(F3="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(I3)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,M3)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,M3,Indices!$B:$B,N3)=0,"Indice de base "&amp;N3&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(N3)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A3)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(Q3&lt;&gt;"",NOT(ISNUMBER(Q3))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A3)=1,"",""))&amp;IF(AND(F3&lt;&gt;"",ISNUMBER(I3),SUMIFS(Indices!$C:$C,Indices!$A:$A,M3,Indices!$B:$B,N3)&gt;0,LEN(N3)=7,COUNTIF($A$2:$A$200,A3)=1),"OK",""))</f>
         <v/>
       </c>
@@ -1438,12 +1490,13 @@
       </c>
       <c r="R4" s="11" t="n"/>
       <c r="S4" s="11" t="n"/>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="11" t="n"/>
+      <c r="U4" s="11" t="inlineStr">
         <is>
           <t>Bail antérieur à 2014 renouvelé, clause ICC ; plafond contractuel 3,5 %</t>
         </is>
       </c>
-      <c r="U4" s="15">
+      <c r="V4" s="15">
         <f>IF(A4="","",TRIM(IF(F4="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(I4)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,M4)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,M4,Indices!$B:$B,N4)=0,"Indice de base "&amp;N4&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(N4)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A4)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(Q4&lt;&gt;"",NOT(ISNUMBER(Q4))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A4)=1,"",""))&amp;IF(AND(F4&lt;&gt;"",ISNUMBER(I4),SUMIFS(Indices!$C:$C,Indices!$A:$A,M4,Indices!$B:$B,N4)&gt;0,LEN(N4)=7,COUNTIF($A$2:$A$200,A4)=1),"OK",""))</f>
         <v/>
       </c>
@@ -1515,20 +1568,21 @@
       <c r="Q5" s="11" t="n"/>
       <c r="R5" s="11" t="n"/>
       <c r="S5" s="11" t="n"/>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="11" t="n"/>
+      <c r="U5" s="11" t="inlineStr">
         <is>
           <t>customer_id Pennylane à créer</t>
         </is>
       </c>
-      <c r="U5" s="15">
+      <c r="V5" s="15">
         <f>IF(A5="","",TRIM(IF(F5="","Date d'effet manquante. ","")&amp;IF(NOT(ISNUMBER(I5)),"Loyer initial manquant. ","")&amp;IF(COUNTIF(Indices!$A:$A,M5)=0,"Aucune valeur d'indice chargée pour cette série. ","")&amp;IF(SUMIFS(Indices!$C:$C,Indices!$A:$A,M5,Indices!$B:$B,N5)=0,"Indice de base "&amp;N5&amp;" absent de la feuille Indices. ","")&amp;IF(LEN(N5)&lt;&gt;7,"Trimestre de base au format AAAA-Tn. ","")&amp;IF(COUNTIF($A$2:$A$200,A5)&gt;1,"ID bail en doublon. ","")&amp;IF(AND(Q5&lt;&gt;"",NOT(ISNUMBER(Q5))),"Plafond non numérique. ","")&amp;IF(COUNTIF($A$2:$A$200,A5)=1,"",""))&amp;IF(AND(F5&lt;&gt;"",ISNUMBER(I5),SUMIFS(Indices!$C:$C,Indices!$A:$A,M5,Indices!$B:$B,N5)&gt;0,LEN(N5)=7,COUNTIF($A$2:$A$200,A5)=1),"OK",""))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="U2:U200">
+  <conditionalFormatting sqref="V2:V200">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(U2&lt;&gt;"",U2&lt;&gt;"OK")</formula>
+      <formula>AND(V2&lt;&gt;"",V2&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -10415,22 +10469,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="90" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="100" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -10456,7 +10516,7 @@
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>Libellé de ligne</t>
+          <t>label (abonnement)</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
@@ -10466,37 +10526,67 @@
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>recurrence.type</t>
+          <t>recurring_rule.type</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
+          <t>interval</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
           <t>Prix unitaire HT / échéance</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Charges HT / échéance</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>TVA (%)</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
-        <is>
-          <t>vat_rate (code Pennylane)</t>
-        </is>
-      </c>
-      <c r="L1" s="10" t="inlineStr">
-        <is>
-          <t>Date de début (1er du mois suivant)</t>
-        </is>
-      </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>Aperçu du corps JSON (POST /billing_subscriptions)</t>
+          <t>vat_rate</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="O1" s="10" t="inlineStr">
+        <is>
+          <t>payment_conditions</t>
+        </is>
+      </c>
+      <c r="P1" s="10" t="inlineStr">
+        <is>
+          <t>payment_method</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>start (1er du mois suivant)</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>subscription_id existant</t>
+        </is>
+      </c>
+      <c r="S1" s="10" t="inlineStr">
+        <is>
+          <t>Corps JSON – POST /api/external/v2/billing_subscriptions</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10609,7 @@
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>"Loyer "&amp;INDEX(Baux!$B:$B,MATCH($A2,Baux!$A:$A,0))&amp;" – échéance "&amp;LOWER(F2)</f>
+        <f>"Loyer "&amp;INDEX(Baux!$B:$B,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F2" s="15">
@@ -10527,31 +10617,55 @@
         <v/>
       </c>
       <c r="G2" s="15">
-        <f>IF(F2="Mensuelle","monthly",IF(F2="Trimestrielle","quarterly",IF(F2="Semestrielle","semiannual","yearly")))</f>
-        <v/>
-      </c>
-      <c r="H2" s="20">
+        <f>IF(F2="Annuelle","yearly","monthly")</f>
+        <v/>
+      </c>
+      <c r="H2" s="15">
+        <f>IF(F2="Mensuelle",1,IF(F2="Trimestrielle",3,IF(F2="Semestrielle",6,1)))</f>
+        <v/>
+      </c>
+      <c r="I2" s="15">
+        <f>IF(F2="Mensuelle","mois",IF(F2="Trimestrielle","trimestre",IF(F2="Semestrielle","semestre","an")))</f>
+        <v/>
+      </c>
+      <c r="J2" s="20">
         <f>ROUND(INDEX(Alertes!$G:$G,MATCH(A2,Alertes!$A:$A,0))/IF(F2="Mensuelle",12,IF(F2="Trimestrielle",4,IF(F2="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
-      <c r="I2" s="20">
+      <c r="K2" s="20">
         <f>ROUND(IF(INDEX(Baux!$J:$J,MATCH($A2,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A2,Baux!$A:$A,0)))/IF(F2="Mensuelle",12,IF(F2="Trimestrielle",4,IF(F2="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
-      <c r="J2" s="15">
+      <c r="L2" s="15">
         <f>INDEX(Baux!$K:$K,MATCH($A2,Baux!$A:$A,0))</f>
         <v/>
       </c>
-      <c r="K2" s="15">
-        <f>IF(J2=20,"FR_200",IF(J2=10,"FR_100",IF(J2=5.5,"FR_55",IF(J2=2.1,"FR_21","exempt"))))</f>
-        <v/>
-      </c>
-      <c r="L2" s="13">
+      <c r="M2" s="15">
+        <f>IF(L2=20,"FR_200",IF(L2=10,"FR_100",IF(L2=5.5,"FR_55",IF(L2=2.1,"FR_21","exempt"))))</f>
+        <v/>
+      </c>
+      <c r="N2" s="15">
+        <f>Société!$B$11</f>
+        <v/>
+      </c>
+      <c r="O2" s="15">
+        <f>Société!$B$12</f>
+        <v/>
+      </c>
+      <c r="P2" s="15">
+        <f>Société!$B$13</f>
+        <v/>
+      </c>
+      <c r="Q2" s="13">
         <f>DATE(YEAR(TODAY()),MONTH(TODAY())+1,1)</f>
         <v/>
       </c>
-      <c r="M2" s="24">
-        <f>"{""customer_id"": "&amp;C2&amp;", ""start"": """&amp;YEAR(L2)&amp;"-"&amp;TEXT(MONTH(L2),"00")&amp;"-"&amp;TEXT(DAY(L2),"00")&amp;""", ""currency"": ""EUR"", ""recurrence"": {""type"": """&amp;G2&amp;""", ""day_of_month"": 1}, ""invoice_lines"": [{""label"": """&amp;E2&amp;""", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(H2,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K2&amp;""""&amp;IF(D2&lt;&gt;"",", ""product_id"": "&amp;D2,"")&amp;"}"&amp;IF(I2&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(I2,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K2&amp;"""}","")&amp;"]}"</f>
+      <c r="R2" s="15">
+        <f>IF(INDEX(Baux!$T:$T,MATCH($A2,Baux!$A:$A,0))="","",INDEX(Baux!$T:$T,MATCH($A2,Baux!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="S2" s="15">
+        <f>"{""customer_id"": "&amp;C2&amp;", ""label"": """&amp;E2&amp;""", ""start"": """&amp;YEAR(Q2)&amp;"-"&amp;TEXT(MONTH(Q2),"00")&amp;"-"&amp;TEXT(DAY(Q2),"00")&amp;""", ""mode"": {""type"": """&amp;N2&amp;"""}, ""payment_conditions"": """&amp;O2&amp;""", ""payment_method"": """&amp;P2&amp;""", ""recurring_rule"": "&amp;"{""type"": """&amp;G2&amp;""", ""interval"": "&amp;H2&amp;IF(G2="monthly",", ""day_of_month"": 1","")&amp;"}"&amp;", ""customer_invoice_data"": {""currency"": ""EUR"", ""language"": ""fr_FR"", ""pdf_invoice_subject"": """&amp;E2&amp;""", ""invoice_lines"": ["&amp;"{""label"": ""Loyer "&amp;LOWER(F2)&amp;" – "&amp;INDEX(Baux!$B:$B,MATCH($A2,Baux!$A:$A,0))&amp;""", ""quantity"": 1, ""unit"": """&amp;I2&amp;""", ""raw_currency_unit_price"": """&amp;SUBSTITUTE(TEXT(J2,"0.00"),",",".")&amp;""", ""vat_rate"": """&amp;M2&amp;""""&amp;IF(D2&lt;&gt;"",", ""product_id"": "&amp;D2,"")&amp;"}"&amp;IF(K2&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""unit"": """&amp;I2&amp;""", ""raw_currency_unit_price"": """&amp;SUBSTITUTE(TEXT(K2,"0.00"),",",".")&amp;""", ""vat_rate"": """&amp;M2&amp;"""}","")&amp;"]}}"</f>
         <v/>
       </c>
     </row>
@@ -10574,7 +10688,7 @@
         <v/>
       </c>
       <c r="E3" s="15">
-        <f>"Loyer "&amp;INDEX(Baux!$B:$B,MATCH($A3,Baux!$A:$A,0))&amp;" – échéance "&amp;LOWER(F3)</f>
+        <f>"Loyer "&amp;INDEX(Baux!$B:$B,MATCH($A3,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F3" s="15">
@@ -10582,31 +10696,55 @@
         <v/>
       </c>
       <c r="G3" s="15">
-        <f>IF(F3="Mensuelle","monthly",IF(F3="Trimestrielle","quarterly",IF(F3="Semestrielle","semiannual","yearly")))</f>
-        <v/>
-      </c>
-      <c r="H3" s="20">
+        <f>IF(F3="Annuelle","yearly","monthly")</f>
+        <v/>
+      </c>
+      <c r="H3" s="15">
+        <f>IF(F3="Mensuelle",1,IF(F3="Trimestrielle",3,IF(F3="Semestrielle",6,1)))</f>
+        <v/>
+      </c>
+      <c r="I3" s="15">
+        <f>IF(F3="Mensuelle","mois",IF(F3="Trimestrielle","trimestre",IF(F3="Semestrielle","semestre","an")))</f>
+        <v/>
+      </c>
+      <c r="J3" s="20">
         <f>ROUND(INDEX(Alertes!$G:$G,MATCH(A3,Alertes!$A:$A,0))/IF(F3="Mensuelle",12,IF(F3="Trimestrielle",4,IF(F3="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
-      <c r="I3" s="20">
+      <c r="K3" s="20">
         <f>ROUND(IF(INDEX(Baux!$J:$J,MATCH($A3,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A3,Baux!$A:$A,0)))/IF(F3="Mensuelle",12,IF(F3="Trimestrielle",4,IF(F3="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
-      <c r="J3" s="15">
+      <c r="L3" s="15">
         <f>INDEX(Baux!$K:$K,MATCH($A3,Baux!$A:$A,0))</f>
         <v/>
       </c>
-      <c r="K3" s="15">
-        <f>IF(J3=20,"FR_200",IF(J3=10,"FR_100",IF(J3=5.5,"FR_55",IF(J3=2.1,"FR_21","exempt"))))</f>
-        <v/>
-      </c>
-      <c r="L3" s="13">
+      <c r="M3" s="15">
+        <f>IF(L3=20,"FR_200",IF(L3=10,"FR_100",IF(L3=5.5,"FR_55",IF(L3=2.1,"FR_21","exempt"))))</f>
+        <v/>
+      </c>
+      <c r="N3" s="15">
+        <f>Société!$B$11</f>
+        <v/>
+      </c>
+      <c r="O3" s="15">
+        <f>Société!$B$12</f>
+        <v/>
+      </c>
+      <c r="P3" s="15">
+        <f>Société!$B$13</f>
+        <v/>
+      </c>
+      <c r="Q3" s="13">
         <f>DATE(YEAR(TODAY()),MONTH(TODAY())+1,1)</f>
         <v/>
       </c>
-      <c r="M3" s="24">
-        <f>"{""customer_id"": "&amp;C3&amp;", ""start"": """&amp;YEAR(L3)&amp;"-"&amp;TEXT(MONTH(L3),"00")&amp;"-"&amp;TEXT(DAY(L3),"00")&amp;""", ""currency"": ""EUR"", ""recurrence"": {""type"": """&amp;G3&amp;""", ""day_of_month"": 1}, ""invoice_lines"": [{""label"": """&amp;E3&amp;""", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(H3,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K3&amp;""""&amp;IF(D3&lt;&gt;"",", ""product_id"": "&amp;D3,"")&amp;"}"&amp;IF(I3&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(I3,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K3&amp;"""}","")&amp;"]}"</f>
+      <c r="R3" s="15">
+        <f>IF(INDEX(Baux!$T:$T,MATCH($A3,Baux!$A:$A,0))="","",INDEX(Baux!$T:$T,MATCH($A3,Baux!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="S3" s="15">
+        <f>"{""customer_id"": "&amp;C3&amp;", ""label"": """&amp;E3&amp;""", ""start"": """&amp;YEAR(Q3)&amp;"-"&amp;TEXT(MONTH(Q3),"00")&amp;"-"&amp;TEXT(DAY(Q3),"00")&amp;""", ""mode"": {""type"": """&amp;N3&amp;"""}, ""payment_conditions"": """&amp;O3&amp;""", ""payment_method"": """&amp;P3&amp;""", ""recurring_rule"": "&amp;"{""type"": """&amp;G3&amp;""", ""interval"": "&amp;H3&amp;IF(G3="monthly",", ""day_of_month"": 1","")&amp;"}"&amp;", ""customer_invoice_data"": {""currency"": ""EUR"", ""language"": ""fr_FR"", ""pdf_invoice_subject"": """&amp;E3&amp;""", ""invoice_lines"": ["&amp;"{""label"": ""Loyer "&amp;LOWER(F3)&amp;" – "&amp;INDEX(Baux!$B:$B,MATCH($A3,Baux!$A:$A,0))&amp;""", ""quantity"": 1, ""unit"": """&amp;I3&amp;""", ""raw_currency_unit_price"": """&amp;SUBSTITUTE(TEXT(J3,"0.00"),",",".")&amp;""", ""vat_rate"": """&amp;M3&amp;""""&amp;IF(D3&lt;&gt;"",", ""product_id"": "&amp;D3,"")&amp;"}"&amp;IF(K3&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""unit"": """&amp;I3&amp;""", ""raw_currency_unit_price"": """&amp;SUBSTITUTE(TEXT(K3,"0.00"),",",".")&amp;""", ""vat_rate"": """&amp;M3&amp;"""}","")&amp;"]}}"</f>
         <v/>
       </c>
     </row>
@@ -10629,7 +10767,7 @@
         <v/>
       </c>
       <c r="E4" s="15">
-        <f>"Loyer "&amp;INDEX(Baux!$B:$B,MATCH($A4,Baux!$A:$A,0))&amp;" – échéance "&amp;LOWER(F4)</f>
+        <f>"Loyer "&amp;INDEX(Baux!$B:$B,MATCH($A4,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F4" s="15">
@@ -10637,31 +10775,55 @@
         <v/>
       </c>
       <c r="G4" s="15">
-        <f>IF(F4="Mensuelle","monthly",IF(F4="Trimestrielle","quarterly",IF(F4="Semestrielle","semiannual","yearly")))</f>
-        <v/>
-      </c>
-      <c r="H4" s="20">
+        <f>IF(F4="Annuelle","yearly","monthly")</f>
+        <v/>
+      </c>
+      <c r="H4" s="15">
+        <f>IF(F4="Mensuelle",1,IF(F4="Trimestrielle",3,IF(F4="Semestrielle",6,1)))</f>
+        <v/>
+      </c>
+      <c r="I4" s="15">
+        <f>IF(F4="Mensuelle","mois",IF(F4="Trimestrielle","trimestre",IF(F4="Semestrielle","semestre","an")))</f>
+        <v/>
+      </c>
+      <c r="J4" s="20">
         <f>ROUND(INDEX(Alertes!$G:$G,MATCH(A4,Alertes!$A:$A,0))/IF(F4="Mensuelle",12,IF(F4="Trimestrielle",4,IF(F4="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
-      <c r="I4" s="20">
+      <c r="K4" s="20">
         <f>ROUND(IF(INDEX(Baux!$J:$J,MATCH($A4,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A4,Baux!$A:$A,0)))/IF(F4="Mensuelle",12,IF(F4="Trimestrielle",4,IF(F4="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
-      <c r="J4" s="15">
+      <c r="L4" s="15">
         <f>INDEX(Baux!$K:$K,MATCH($A4,Baux!$A:$A,0))</f>
         <v/>
       </c>
-      <c r="K4" s="15">
-        <f>IF(J4=20,"FR_200",IF(J4=10,"FR_100",IF(J4=5.5,"FR_55",IF(J4=2.1,"FR_21","exempt"))))</f>
-        <v/>
-      </c>
-      <c r="L4" s="13">
+      <c r="M4" s="15">
+        <f>IF(L4=20,"FR_200",IF(L4=10,"FR_100",IF(L4=5.5,"FR_55",IF(L4=2.1,"FR_21","exempt"))))</f>
+        <v/>
+      </c>
+      <c r="N4" s="15">
+        <f>Société!$B$11</f>
+        <v/>
+      </c>
+      <c r="O4" s="15">
+        <f>Société!$B$12</f>
+        <v/>
+      </c>
+      <c r="P4" s="15">
+        <f>Société!$B$13</f>
+        <v/>
+      </c>
+      <c r="Q4" s="13">
         <f>DATE(YEAR(TODAY()),MONTH(TODAY())+1,1)</f>
         <v/>
       </c>
-      <c r="M4" s="24">
-        <f>"{""customer_id"": "&amp;C4&amp;", ""start"": """&amp;YEAR(L4)&amp;"-"&amp;TEXT(MONTH(L4),"00")&amp;"-"&amp;TEXT(DAY(L4),"00")&amp;""", ""currency"": ""EUR"", ""recurrence"": {""type"": """&amp;G4&amp;""", ""day_of_month"": 1}, ""invoice_lines"": [{""label"": """&amp;E4&amp;""", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(H4,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K4&amp;""""&amp;IF(D4&lt;&gt;"",", ""product_id"": "&amp;D4,"")&amp;"}"&amp;IF(I4&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(I4,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K4&amp;"""}","")&amp;"]}"</f>
+      <c r="R4" s="15">
+        <f>IF(INDEX(Baux!$T:$T,MATCH($A4,Baux!$A:$A,0))="","",INDEX(Baux!$T:$T,MATCH($A4,Baux!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="S4" s="15">
+        <f>"{""customer_id"": "&amp;C4&amp;", ""label"": """&amp;E4&amp;""", ""start"": """&amp;YEAR(Q4)&amp;"-"&amp;TEXT(MONTH(Q4),"00")&amp;"-"&amp;TEXT(DAY(Q4),"00")&amp;""", ""mode"": {""type"": """&amp;N4&amp;"""}, ""payment_conditions"": """&amp;O4&amp;""", ""payment_method"": """&amp;P4&amp;""", ""recurring_rule"": "&amp;"{""type"": """&amp;G4&amp;""", ""interval"": "&amp;H4&amp;IF(G4="monthly",", ""day_of_month"": 1","")&amp;"}"&amp;", ""customer_invoice_data"": {""currency"": ""EUR"", ""language"": ""fr_FR"", ""pdf_invoice_subject"": """&amp;E4&amp;""", ""invoice_lines"": ["&amp;"{""label"": ""Loyer "&amp;LOWER(F4)&amp;" – "&amp;INDEX(Baux!$B:$B,MATCH($A4,Baux!$A:$A,0))&amp;""", ""quantity"": 1, ""unit"": """&amp;I4&amp;""", ""raw_currency_unit_price"": """&amp;SUBSTITUTE(TEXT(J4,"0.00"),",",".")&amp;""", ""vat_rate"": """&amp;M4&amp;""""&amp;IF(D4&lt;&gt;"",", ""product_id"": "&amp;D4,"")&amp;"}"&amp;IF(K4&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""unit"": """&amp;I4&amp;""", ""raw_currency_unit_price"": """&amp;SUBSTITUTE(TEXT(K4,"0.00"),",",".")&amp;""", ""vat_rate"": """&amp;M4&amp;"""}","")&amp;"]}}"</f>
         <v/>
       </c>
     </row>
@@ -10684,7 +10846,7 @@
         <v/>
       </c>
       <c r="E5" s="15">
-        <f>"Loyer "&amp;INDEX(Baux!$B:$B,MATCH($A5,Baux!$A:$A,0))&amp;" – échéance "&amp;LOWER(F5)</f>
+        <f>"Loyer "&amp;INDEX(Baux!$B:$B,MATCH($A5,Baux!$A:$A,0))</f>
         <v/>
       </c>
       <c r="F5" s="15">
@@ -10692,38 +10854,62 @@
         <v/>
       </c>
       <c r="G5" s="15">
-        <f>IF(F5="Mensuelle","monthly",IF(F5="Trimestrielle","quarterly",IF(F5="Semestrielle","semiannual","yearly")))</f>
-        <v/>
-      </c>
-      <c r="H5" s="20">
+        <f>IF(F5="Annuelle","yearly","monthly")</f>
+        <v/>
+      </c>
+      <c r="H5" s="15">
+        <f>IF(F5="Mensuelle",1,IF(F5="Trimestrielle",3,IF(F5="Semestrielle",6,1)))</f>
+        <v/>
+      </c>
+      <c r="I5" s="15">
+        <f>IF(F5="Mensuelle","mois",IF(F5="Trimestrielle","trimestre",IF(F5="Semestrielle","semestre","an")))</f>
+        <v/>
+      </c>
+      <c r="J5" s="20">
         <f>ROUND(INDEX(Alertes!$G:$G,MATCH(A5,Alertes!$A:$A,0))/IF(F5="Mensuelle",12,IF(F5="Trimestrielle",4,IF(F5="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
-      <c r="I5" s="20">
+      <c r="K5" s="20">
         <f>ROUND(IF(INDEX(Baux!$J:$J,MATCH($A5,Baux!$A:$A,0))="",0,INDEX(Baux!$J:$J,MATCH($A5,Baux!$A:$A,0)))/IF(F5="Mensuelle",12,IF(F5="Trimestrielle",4,IF(F5="Semestrielle",2,1))),2)</f>
         <v/>
       </c>
-      <c r="J5" s="15">
+      <c r="L5" s="15">
         <f>INDEX(Baux!$K:$K,MATCH($A5,Baux!$A:$A,0))</f>
         <v/>
       </c>
-      <c r="K5" s="15">
-        <f>IF(J5=20,"FR_200",IF(J5=10,"FR_100",IF(J5=5.5,"FR_55",IF(J5=2.1,"FR_21","exempt"))))</f>
-        <v/>
-      </c>
-      <c r="L5" s="13">
+      <c r="M5" s="15">
+        <f>IF(L5=20,"FR_200",IF(L5=10,"FR_100",IF(L5=5.5,"FR_55",IF(L5=2.1,"FR_21","exempt"))))</f>
+        <v/>
+      </c>
+      <c r="N5" s="15">
+        <f>Société!$B$11</f>
+        <v/>
+      </c>
+      <c r="O5" s="15">
+        <f>Société!$B$12</f>
+        <v/>
+      </c>
+      <c r="P5" s="15">
+        <f>Société!$B$13</f>
+        <v/>
+      </c>
+      <c r="Q5" s="13">
         <f>DATE(YEAR(TODAY()),MONTH(TODAY())+1,1)</f>
         <v/>
       </c>
-      <c r="M5" s="24">
-        <f>"{""customer_id"": "&amp;C5&amp;", ""start"": """&amp;YEAR(L5)&amp;"-"&amp;TEXT(MONTH(L5),"00")&amp;"-"&amp;TEXT(DAY(L5),"00")&amp;""", ""currency"": ""EUR"", ""recurrence"": {""type"": """&amp;G5&amp;""", ""day_of_month"": 1}, ""invoice_lines"": [{""label"": """&amp;E5&amp;""", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(H5,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K5&amp;""""&amp;IF(D5&lt;&gt;"",", ""product_id"": "&amp;D5,"")&amp;"}"&amp;IF(I5&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""raw_currency_unit_price"": "&amp;SUBSTITUTE(TEXT(I5,"0.00"),",",".")&amp;", ""vat_rate"": """&amp;K5&amp;"""}","")&amp;"]}"</f>
+      <c r="R5" s="15">
+        <f>IF(INDEX(Baux!$T:$T,MATCH($A5,Baux!$A:$A,0))="","",INDEX(Baux!$T:$T,MATCH($A5,Baux!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="S5" s="15">
+        <f>"{""customer_id"": "&amp;C5&amp;", ""label"": """&amp;E5&amp;""", ""start"": """&amp;YEAR(Q5)&amp;"-"&amp;TEXT(MONTH(Q5),"00")&amp;"-"&amp;TEXT(DAY(Q5),"00")&amp;""", ""mode"": {""type"": """&amp;N5&amp;"""}, ""payment_conditions"": """&amp;O5&amp;""", ""payment_method"": """&amp;P5&amp;""", ""recurring_rule"": "&amp;"{""type"": """&amp;G5&amp;""", ""interval"": "&amp;H5&amp;IF(G5="monthly",", ""day_of_month"": 1","")&amp;"}"&amp;", ""customer_invoice_data"": {""currency"": ""EUR"", ""language"": ""fr_FR"", ""pdf_invoice_subject"": """&amp;E5&amp;""", ""invoice_lines"": ["&amp;"{""label"": ""Loyer "&amp;LOWER(F5)&amp;" – "&amp;INDEX(Baux!$B:$B,MATCH($A5,Baux!$A:$A,0))&amp;""", ""quantity"": 1, ""unit"": """&amp;I5&amp;""", ""raw_currency_unit_price"": """&amp;SUBSTITUTE(TEXT(J5,"0.00"),",",".")&amp;""", ""vat_rate"": """&amp;M5&amp;""""&amp;IF(D5&lt;&gt;"",", ""product_id"": "&amp;D5,"")&amp;"}"&amp;IF(K5&gt;0,", {""label"": ""Provision sur charges"", ""quantity"": 1, ""unit"": """&amp;I5&amp;""", ""raw_currency_unit_price"": """&amp;SUBSTITUTE(TEXT(K5,"0.00"),",",".")&amp;""", ""vat_rate"": """&amp;M5&amp;"""}","")&amp;"]}}"</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Schéma indicatif : les noms de champs (recurrence, invoice_lines, raw_currency_unit_price, vat_rate) sont à valider contre https://pennylane.readme.io/reference/postbillingsubscriptions avant tout envoi. Le mapping est modifiable dans config/pennylane_mapping.json.</t>
+          <t>Schéma : OpenAPI Pennylane Company V2 (POST /billing_subscriptions, mise à jour 2026-05-27). Mode, conditions et moyen de paiement se règlent dans la feuille Société. L'envoi se fait par la commande pennylane &lt;société&gt; --push ; l'identifiant créé est inscrit dans Baux (Pennylane subscription_id).</t>
         </is>
       </c>
     </row>
